--- a/Requirements.xlsx
+++ b/Requirements.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z004uysm\Documents\BA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E736C73-5F06-4E8C-BC90-AF112852A271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B365305-383D-4B66-8DD5-C38695AD295F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{9AFE01D9-9480-4035-82AC-131C794FF07E}"/>
   </bookViews>
   <sheets>
     <sheet name="Funktional" sheetId="1" r:id="rId1"/>
+    <sheet name="Nichtfunktional" sheetId="3" r:id="rId2"/>
+    <sheet name="Randbedingungen" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,12 +40,419 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="132">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Beschreibung</t>
+  </si>
+  <si>
+    <t>FA-01</t>
+  </si>
+  <si>
+    <t>FA-02</t>
+  </si>
+  <si>
+    <t>FA-03</t>
+  </si>
+  <si>
+    <t>FA-04</t>
+  </si>
+  <si>
+    <t>FA-05</t>
+  </si>
+  <si>
+    <t>FA-06</t>
+  </si>
+  <si>
+    <t>FA-07</t>
+  </si>
+  <si>
+    <t>FA-08</t>
+  </si>
+  <si>
+    <t>FA-09</t>
+  </si>
+  <si>
+    <t>FA-10</t>
+  </si>
+  <si>
+    <t>FA-11</t>
+  </si>
+  <si>
+    <t>FA-12</t>
+  </si>
+  <si>
+    <t>FA-13</t>
+  </si>
+  <si>
+    <t>FA-14</t>
+  </si>
+  <si>
+    <t>FA-15</t>
+  </si>
+  <si>
+    <t>FA-16</t>
+  </si>
+  <si>
+    <t>FA-17</t>
+  </si>
+  <si>
+    <t>FA-18</t>
+  </si>
+  <si>
+    <t>FA-19</t>
+  </si>
+  <si>
+    <t>FA-20</t>
+  </si>
+  <si>
+    <t>FA-21</t>
+  </si>
+  <si>
+    <t>FA-22</t>
+  </si>
+  <si>
+    <t>Die Kommunikation muss zyklisch erfolgen und Datenpunkte zyklisch übermitteln.</t>
+  </si>
+  <si>
+    <t>Alle relevanten Messwerte des ECPD müssen als Datenpunkte in Desigo CC sichtbar sein. Diese Messwerte müssen eine korrekte Beschriftung haben.</t>
+  </si>
+  <si>
+    <t>Das ECPD und Powercenter müssen über ein geeignetes Protokoll mit Desigo CC vebunden werden können. Dies setzt einen Import und eine Instanziierung in Desigo CC voraus.</t>
+  </si>
+  <si>
+    <t>Es muss möglich sein, über die gewählte Schnittstelle entsprechende Fernsteuerbefehle zu senden und alle verfügbaren Konfigurationen vorzunehmen.</t>
+  </si>
+  <si>
+    <t>Kommentar</t>
+  </si>
+  <si>
+    <t>Powecenter und ECPD? Sentron 1000 bereits in Desigo CC, soll das für Sentron 1100 auch gemacht werden?</t>
+  </si>
+  <si>
+    <t>Gehen die Alarme auch über Modbus oder werden die erst in Desigo CC anhand Messdaten erzeugt? Wie sieht da entsprechend die Integration aus?</t>
+  </si>
+  <si>
+    <t>Bei Sentron 1000 anscheinend nur in begrenztem Rahmen was die Features angeht, wie sieht das da aus?</t>
+  </si>
+  <si>
+    <t>Findet die Visualisierung im Objektmodell statt oder in Desigo CC? Ist das Teil der Aufgabe?</t>
+  </si>
+  <si>
+    <t>Automatische DGUV-Prüfung muss möglich sein über Desigo CC, diese Prüfung muss in Desigo CC dokumentiert werden.</t>
+  </si>
+  <si>
+    <t>Wie könnte das aussehen?</t>
+  </si>
+  <si>
+    <t>Es muss möglich sein, Statusmeldungen und Alarme in Desigo CC zu empfangen, anzeigen zu lassen, zu bearbeiten und zu quittieren. Das Verhalten soll hierbei gleich zu anderen Alarmen sein.</t>
+  </si>
+  <si>
+    <t>Die Alarme sollen den verschiedenen in Desigo CC vorhandenen Stufen passend zugeordnet werden.</t>
+  </si>
+  <si>
+    <t>Die initiale Konfiguration soll weiterhin über SENTRON Powerconfig möglich sein.</t>
+  </si>
+  <si>
+    <t>Software fehlt bei mir im Moment noch</t>
+  </si>
+  <si>
+    <t>Messwerte und Zustände der Geräte müssen in Dashboards visualisiert werden können. Historische Daten sollen aufgezeichnet werden und abrufbar sein.</t>
+  </si>
+  <si>
+    <t>NFA-01</t>
+  </si>
+  <si>
+    <t>Der gesamte Integrationsprozess muss vollständig dokumentiert sein</t>
+  </si>
+  <si>
+    <t>NFA-02</t>
+  </si>
+  <si>
+    <t>NFA-03</t>
+  </si>
+  <si>
+    <t>NFA-04</t>
+  </si>
+  <si>
+    <t>NFA-05</t>
+  </si>
+  <si>
+    <t>NFA-06</t>
+  </si>
+  <si>
+    <t>NFA-07</t>
+  </si>
+  <si>
+    <t>NFA-08</t>
+  </si>
+  <si>
+    <t>NFA-09</t>
+  </si>
+  <si>
+    <t>NFA-10</t>
+  </si>
+  <si>
+    <t>NFA-11</t>
+  </si>
+  <si>
+    <t>NFA-12</t>
+  </si>
+  <si>
+    <t>NFA-13</t>
+  </si>
+  <si>
+    <t>NFA-14</t>
+  </si>
+  <si>
+    <t>NFA-15</t>
+  </si>
+  <si>
+    <t>NFA-16</t>
+  </si>
+  <si>
+    <t>NFA-17</t>
+  </si>
+  <si>
+    <t>NFA-18</t>
+  </si>
+  <si>
+    <t>NFA-19</t>
+  </si>
+  <si>
+    <t>NFA-20</t>
+  </si>
+  <si>
+    <t>NFA-21</t>
+  </si>
+  <si>
+    <t>NFA-22</t>
+  </si>
+  <si>
+    <t>NFA-23</t>
+  </si>
+  <si>
+    <t>NFA-24</t>
+  </si>
+  <si>
+    <t>NFA-25</t>
+  </si>
+  <si>
+    <t>NFA-26</t>
+  </si>
+  <si>
+    <t>NFA-27</t>
+  </si>
+  <si>
+    <t>NFA-28</t>
+  </si>
+  <si>
+    <t>NFA-29</t>
+  </si>
+  <si>
+    <t>NFA-30</t>
+  </si>
+  <si>
+    <t>NFA-31</t>
+  </si>
+  <si>
+    <t>NFA-32</t>
+  </si>
+  <si>
+    <t>NFA-33</t>
+  </si>
+  <si>
+    <t>NFA-34</t>
+  </si>
+  <si>
+    <t>NFA-35</t>
+  </si>
+  <si>
+    <t>NFA-36</t>
+  </si>
+  <si>
+    <t>NFA-37</t>
+  </si>
+  <si>
+    <t>NFA-38</t>
+  </si>
+  <si>
+    <t>NFA-39</t>
+  </si>
+  <si>
+    <t>NFA-40</t>
+  </si>
+  <si>
+    <t>NFA-41</t>
+  </si>
+  <si>
+    <t>Bei Kommunikationsunterbrechung muss ein Alarm ausgelöst werden.</t>
+  </si>
+  <si>
+    <t>Desigo CC oder in ECPD Konfig?</t>
+  </si>
+  <si>
+    <t>Es muss eine Anleitung zur Integration des entwickelten Modells für Desigo CC geben.</t>
+  </si>
+  <si>
+    <t>Zusätzlich zu Bachelorarbeit</t>
+  </si>
+  <si>
+    <t>Das gesamte Modell muss so gestaltet sein, dass es bei Updates einfach angepasst werden kann.</t>
+  </si>
+  <si>
+    <t>RB-01</t>
+  </si>
+  <si>
+    <t>RB-02</t>
+  </si>
+  <si>
+    <t>RB-03</t>
+  </si>
+  <si>
+    <t>RB-04</t>
+  </si>
+  <si>
+    <t>RB-05</t>
+  </si>
+  <si>
+    <t>RB-06</t>
+  </si>
+  <si>
+    <t>RB-07</t>
+  </si>
+  <si>
+    <t>RB-08</t>
+  </si>
+  <si>
+    <t>RB-09</t>
+  </si>
+  <si>
+    <t>RB-10</t>
+  </si>
+  <si>
+    <t>RB-11</t>
+  </si>
+  <si>
+    <t>RB-12</t>
+  </si>
+  <si>
+    <t>RB-13</t>
+  </si>
+  <si>
+    <t>RB-14</t>
+  </si>
+  <si>
+    <t>RB-15</t>
+  </si>
+  <si>
+    <t>RB-16</t>
+  </si>
+  <si>
+    <t>RB-17</t>
+  </si>
+  <si>
+    <t>RB-18</t>
+  </si>
+  <si>
+    <t>RB-19</t>
+  </si>
+  <si>
+    <t>RB-20</t>
+  </si>
+  <si>
+    <t>RB-21</t>
+  </si>
+  <si>
+    <t>RB-22</t>
+  </si>
+  <si>
+    <t>RB-23</t>
+  </si>
+  <si>
+    <t>RB-24</t>
+  </si>
+  <si>
+    <t>RB-25</t>
+  </si>
+  <si>
+    <t>RB-26</t>
+  </si>
+  <si>
+    <t>RB-27</t>
+  </si>
+  <si>
+    <t>RB-28</t>
+  </si>
+  <si>
+    <t>RB-29</t>
+  </si>
+  <si>
+    <t>RB-30</t>
+  </si>
+  <si>
+    <t>RB-31</t>
+  </si>
+  <si>
+    <t>RB-32</t>
+  </si>
+  <si>
+    <t>RB-33</t>
+  </si>
+  <si>
+    <t>RB-34</t>
+  </si>
+  <si>
+    <t>RB-35</t>
+  </si>
+  <si>
+    <t>RB-36</t>
+  </si>
+  <si>
+    <t>RB-37</t>
+  </si>
+  <si>
+    <t>RB-38</t>
+  </si>
+  <si>
+    <t>RB-39</t>
+  </si>
+  <si>
+    <t>RB-40</t>
+  </si>
+  <si>
+    <t>RB-41</t>
+  </si>
+  <si>
+    <t>Zur Einrichtung: Installation der SENTRON Powerconfig Software und Desigo CC mit Konfigurationsrechten</t>
+  </si>
+  <si>
+    <t>Verfügbarkeit eines Powercenters 1100 oder 2000 mit einem Sentron ECPD</t>
+  </si>
+  <si>
+    <t>Netzwerkverbindung zum Powercenter mit entsprechenden Protokoll, Verbindung von ECPD und Powercenter mit Bluetooth LE</t>
+  </si>
+  <si>
+    <t>Unklar ob Powercenter 1000 die benötigten Funktionalitäten bereitstellt</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -69,8 +478,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -405,9 +817,849 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A47F84-D45D-4D83-8E6F-A400BE206714}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="48.7109375" customWidth="1"/>
+    <col min="3" max="3" width="38.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B85D5878-C431-4350-AFD6-92309A5E1C15}">
+  <dimension ref="A1:C42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="48.7109375" customWidth="1"/>
+    <col min="3" max="3" width="38.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="1"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C41" s="1"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECA61290-7F82-4B5E-94C7-2D8A84275AA6}">
+  <dimension ref="A1:C42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="48.7109375" customWidth="1"/>
+    <col min="3" max="3" width="38.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C40" s="1"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C41" s="1"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C42" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Requirements.xlsx
+++ b/Requirements.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z004uysm\Documents\BA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B365305-383D-4B66-8DD5-C38695AD295F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE626DFE-17E3-4385-820A-E055A2D8DF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{9AFE01D9-9480-4035-82AC-131C794FF07E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{9AFE01D9-9480-4035-82AC-131C794FF07E}"/>
   </bookViews>
   <sheets>
     <sheet name="Funktional" sheetId="1" r:id="rId1"/>
     <sheet name="Nichtfunktional" sheetId="3" r:id="rId2"/>
     <sheet name="Randbedingungen" sheetId="5" r:id="rId3"/>
+    <sheet name="Modbus Parameter Powercenter 11" sheetId="6" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="406">
   <si>
     <t>ID</t>
   </si>
@@ -49,36 +50,93 @@
     <t>Beschreibung</t>
   </si>
   <si>
+    <t>Kommentar</t>
+  </si>
+  <si>
     <t>FA-01</t>
   </si>
   <si>
+    <t>Das ECPD und Powercenter müssen über ein geeignetes Protokoll mit Desigo CC vebunden werden können. Dies setzt einen Import und eine Instanziierung in Desigo CC voraus.</t>
+  </si>
+  <si>
+    <t>Powecenter und ECPD? Sentron 1000 bereits in Desigo CC, soll das für Sentron 1100 auch gemacht werden?</t>
+  </si>
+  <si>
     <t>FA-02</t>
   </si>
   <si>
+    <t>Die Kommunikation muss zyklisch erfolgen und Datenpunkte zyklisch übermitteln. Die Frequenz soll konfigurierbar sein.</t>
+  </si>
+  <si>
     <t>FA-03</t>
   </si>
   <si>
+    <t>Alle Messwerte des ECPD müssen als Datenpunkte in Desigo CC sichtbar sein. Diese Messwerte müssen eine korrekte Beschriftung haben.</t>
+  </si>
+  <si>
     <t>FA-04</t>
   </si>
   <si>
+    <t>Es muss möglich sein, Statusmeldungen und Alarme in Desigo CC zu empfangen, anzeigen zu lassen, zu bearbeiten und zu quittieren. Das Verhalten soll hierbei gleich zu anderen Alarmen sein.</t>
+  </si>
+  <si>
+    <t>Gehen die Alarme auch über Modbus oder werden die erst in Desigo CC anhand Messdaten erzeugt? Wie sieht da entsprechend die Integration aus?</t>
+  </si>
+  <si>
     <t>FA-05</t>
   </si>
   <si>
+    <t>Die Alarme sollen den verschiedenen in Desigo CC vorhandenen Alarmkategorien passend zugeordnet werden.</t>
+  </si>
+  <si>
+    <t>Bei Sentron Powermanager: Alarm Zustand wird über Modbus übertragen, wo kann Interpretation stattfinden?</t>
+  </si>
+  <si>
     <t>FA-06</t>
   </si>
   <si>
+    <t>Es muss möglich sein, über die gewählte Schnittstelle entsprechende Fernsteuerbefehle zu senden und alle verfügbaren Konfigurationen vorzunehmen.</t>
+  </si>
+  <si>
+    <t>Bei Sentron 1000 anscheinend nur in begrenztem Rahmen was die Features angeht, wie sieht das da aus?</t>
+  </si>
+  <si>
     <t>FA-07</t>
   </si>
   <si>
+    <t>Messwerte und Zustände der Geräte müssen in Dashboards visualisiert werden können. Dazu müssen die zu visualisierenden Werte in entsprechende Archivgruppen eingeteilt werden.</t>
+  </si>
+  <si>
+    <t>Findet die Visualisierung im Objektmodell statt oder in Desigo CC? Ist das Teil der Aufgabe?</t>
+  </si>
+  <si>
     <t>FA-08</t>
   </si>
   <si>
+    <t>Automatische DGUV-Prüfung muss möglich sein über Desigo CC, diese Prüfung muss in Desigo CC dokumentiert werden.</t>
+  </si>
+  <si>
+    <t>Wie könnte das aussehen?</t>
+  </si>
+  <si>
     <t>FA-09</t>
   </si>
   <si>
+    <t>Die initiale Konfiguration soll weiterhin über SENTRON Powerconfig möglich sein.</t>
+  </si>
+  <si>
+    <t>Software fehlt bei mir im Moment noch</t>
+  </si>
+  <si>
     <t>FA-10</t>
   </si>
   <si>
+    <t>Bei Kommunikationsunterbrechung muss ein Alarm ausgelöst werden.</t>
+  </si>
+  <si>
+    <t>Desigo CC oder in ECPD Konfig?</t>
+  </si>
+  <si>
     <t>FA-11</t>
   </si>
   <si>
@@ -115,72 +173,39 @@
     <t>FA-22</t>
   </si>
   <si>
-    <t>Die Kommunikation muss zyklisch erfolgen und Datenpunkte zyklisch übermitteln.</t>
-  </si>
-  <si>
-    <t>Alle relevanten Messwerte des ECPD müssen als Datenpunkte in Desigo CC sichtbar sein. Diese Messwerte müssen eine korrekte Beschriftung haben.</t>
-  </si>
-  <si>
-    <t>Das ECPD und Powercenter müssen über ein geeignetes Protokoll mit Desigo CC vebunden werden können. Dies setzt einen Import und eine Instanziierung in Desigo CC voraus.</t>
-  </si>
-  <si>
-    <t>Es muss möglich sein, über die gewählte Schnittstelle entsprechende Fernsteuerbefehle zu senden und alle verfügbaren Konfigurationen vorzunehmen.</t>
-  </si>
-  <si>
-    <t>Kommentar</t>
-  </si>
-  <si>
-    <t>Powecenter und ECPD? Sentron 1000 bereits in Desigo CC, soll das für Sentron 1100 auch gemacht werden?</t>
-  </si>
-  <si>
-    <t>Gehen die Alarme auch über Modbus oder werden die erst in Desigo CC anhand Messdaten erzeugt? Wie sieht da entsprechend die Integration aus?</t>
-  </si>
-  <si>
-    <t>Bei Sentron 1000 anscheinend nur in begrenztem Rahmen was die Features angeht, wie sieht das da aus?</t>
-  </si>
-  <si>
-    <t>Findet die Visualisierung im Objektmodell statt oder in Desigo CC? Ist das Teil der Aufgabe?</t>
-  </si>
-  <si>
-    <t>Automatische DGUV-Prüfung muss möglich sein über Desigo CC, diese Prüfung muss in Desigo CC dokumentiert werden.</t>
-  </si>
-  <si>
-    <t>Wie könnte das aussehen?</t>
-  </si>
-  <si>
-    <t>Es muss möglich sein, Statusmeldungen und Alarme in Desigo CC zu empfangen, anzeigen zu lassen, zu bearbeiten und zu quittieren. Das Verhalten soll hierbei gleich zu anderen Alarmen sein.</t>
-  </si>
-  <si>
-    <t>Die Alarme sollen den verschiedenen in Desigo CC vorhandenen Stufen passend zugeordnet werden.</t>
-  </si>
-  <si>
-    <t>Die initiale Konfiguration soll weiterhin über SENTRON Powerconfig möglich sein.</t>
-  </si>
-  <si>
-    <t>Software fehlt bei mir im Moment noch</t>
-  </si>
-  <si>
-    <t>Messwerte und Zustände der Geräte müssen in Dashboards visualisiert werden können. Historische Daten sollen aufgezeichnet werden und abrufbar sein.</t>
-  </si>
-  <si>
     <t>NFA-01</t>
   </si>
   <si>
-    <t>Der gesamte Integrationsprozess muss vollständig dokumentiert sein</t>
+    <t>Der gesamte Integrationsprozess muss vollständig dokumentiert sein.</t>
   </si>
   <si>
     <t>NFA-02</t>
   </si>
   <si>
+    <t>Es muss eine Anleitung zur Integration des entwickelten Modells für Desigo CC geben. Diese Anleitung soll für sowohl technisches Personal, welches die Anlagen installiert, als auch administratives Personal, welches die Konfiguration in Desigo CC vornimmt, geeignet sein.</t>
+  </si>
+  <si>
+    <t>Zusätzlich zu Bachelorarbeit</t>
+  </si>
+  <si>
     <t>NFA-03</t>
   </si>
   <si>
+    <t>Das Modell muss modular aufgebaut sein, sodass einzelne Datenpunkte oder Funktionen ohne vollständige Neuerstellung angepasst werden können.</t>
+  </si>
+  <si>
     <t>NFA-04</t>
   </si>
   <si>
+    <t xml:space="preserve">Das Objektmodell muss mit der Desigo CC Version 9.0 kompatibel sein. </t>
+  </si>
+  <si>
     <t>NFA-05</t>
   </si>
   <si>
+    <t>Das Modell muss für den Einsatz mit mehreren ECPD-Instanzen erweiterbar sein.</t>
+  </si>
+  <si>
     <t>NFA-06</t>
   </si>
   <si>
@@ -289,33 +314,33 @@
     <t>NFA-41</t>
   </si>
   <si>
-    <t>Bei Kommunikationsunterbrechung muss ein Alarm ausgelöst werden.</t>
-  </si>
-  <si>
-    <t>Desigo CC oder in ECPD Konfig?</t>
-  </si>
-  <si>
-    <t>Es muss eine Anleitung zur Integration des entwickelten Modells für Desigo CC geben.</t>
-  </si>
-  <si>
-    <t>Zusätzlich zu Bachelorarbeit</t>
-  </si>
-  <si>
-    <t>Das gesamte Modell muss so gestaltet sein, dass es bei Updates einfach angepasst werden kann.</t>
-  </si>
-  <si>
     <t>RB-01</t>
   </si>
   <si>
+    <t>Zur Einrichtung: Installation der SENTRON Powerconfig Software und Desigo CC mit Konfigurationsrechten</t>
+  </si>
+  <si>
     <t>RB-02</t>
   </si>
   <si>
+    <t>Verfügbarkeit eines Powercenters 1100 oder 2000 mit einem Sentron ECPD, vorausgesetzt die Funktionsweise im Powercenter 2000 ist der des Powercenters 1100 gleich</t>
+  </si>
+  <si>
+    <t>Unklar ob Powercenter 1000 die benötigten Funktionalitäten bereitstellt</t>
+  </si>
+  <si>
     <t>RB-03</t>
   </si>
   <si>
+    <t>Netzwerkverbindung zum Powercenter mit entsprechenden Protokoll, Verbindung von ECPD und Powercenter mit Bluetooth LE wie in der Installationsanleitung beschrieben</t>
+  </si>
+  <si>
     <t>RB-04</t>
   </si>
   <si>
+    <t>Für die Testumgebung steht ein Powercenter 1100 und eine ECPD Anlage zur Verfügung, auf dessen Grundlage das Objektmodell entwickelt wird.</t>
+  </si>
+  <si>
     <t>RB-05</t>
   </si>
   <si>
@@ -427,23 +452,869 @@
     <t>RB-41</t>
   </si>
   <si>
-    <t>Zur Einrichtung: Installation der SENTRON Powerconfig Software und Desigo CC mit Konfigurationsrechten</t>
-  </si>
-  <si>
-    <t>Verfügbarkeit eines Powercenters 1100 oder 2000 mit einem Sentron ECPD</t>
-  </si>
-  <si>
-    <t>Netzwerkverbindung zum Powercenter mit entsprechenden Protokoll, Verbindung von ECPD und Powercenter mit Bluetooth LE</t>
-  </si>
-  <si>
-    <t>Unklar ob Powercenter 1000 die benötigten Funktionalitäten bereitstellt</t>
+    <t>Register</t>
+  </si>
+  <si>
+    <t>Länge</t>
+  </si>
+  <si>
+    <t>Gruppe</t>
+  </si>
+  <si>
+    <t>Bezeichnung</t>
+  </si>
+  <si>
+    <t>Format</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>Bemerkung</t>
+  </si>
+  <si>
+    <t>Einheit</t>
+  </si>
+  <si>
+    <t>Zugriff</t>
+  </si>
+  <si>
+    <t>Schreibbar nur als Superuser</t>
+  </si>
+  <si>
+    <t>Kommentar Malte</t>
+  </si>
+  <si>
+    <t>Diagnose</t>
+  </si>
+  <si>
+    <t>Alarm Zustand</t>
+  </si>
+  <si>
+    <t>U32</t>
+  </si>
+  <si>
+    <t>Bitwert  0 = inaktiv, 1 = aktiv.
+Bitfeld:
+0: Alarm Betriebsstunden mit Belastungsstrom
+1: Alarm Betriebsstunden, 2: Alarm Schaltspiele
+3: Alarm Auslösezähler, 4: Alarm Temperaturüberschreitung
+5: Alarm 1 Überstrom, 6: Alarm 2 Überstrom
+7: Alarm 1 Unterstrom,8: Alarm 2 Unterstrom
+9: Alarm 1 Überspannung, 10: Alarm 2 Überspannung
+11 : Alarm 1 Unterspannung, 12 : Alarm 2 Unterspannung
+13: Schalter ausgelöst, 14: Auslösung Fehlerlichtbogen
+15 : Auslösung Überspannung, 16: Alarm  Kurzschlussauslösezähler
+17: Alarm: AFDD Tripschwelle Unterschreitung. 18: Selbsttest fehlgeschlagen 
+19: Auslösung Unterspannung, 20: Auslösung Fehlerstrom
+24-31: Geräte spezifisch.
+RCA: 24: RCD Test Zähler Alarm, 25: ARD Fehler, 26: RCD Test fehlgeschlagen, 27: IR Test fehlgeschlagen, 28: IR Test Warnung
+MCB RCM: 24: RCM AC Voralarm, 25: RCM AC Alarm, 26: RCM RMS Voralarm, 27: RCM RMS Alarm
+MSP: 24: Überlastauslösung Alarm, 25: Kurzschlussauslösung Alarm
+ECPD: 24: RCM Vorlarm, 25: RCM Alarm, 26: Verzögerte Auslösung, 27: Unverzögerte Auslösung, 28: ARD fehlgeschlagen, 29: Übertemperaturabschaltung, 30: Alarm für verzögerte Auslösungen, 31: Alarm EIN blockiert</t>
+  </si>
+  <si>
+    <t>RO</t>
+  </si>
+  <si>
+    <t>Betriebsstundenzähler gesamt</t>
+  </si>
+  <si>
+    <t>FP64</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>FP64: gerada als float drin</t>
+  </si>
+  <si>
+    <t>BLE Empfangssignalstärke RSSI</t>
+  </si>
+  <si>
+    <t>S16</t>
+  </si>
+  <si>
+    <t>dBm</t>
+  </si>
+  <si>
+    <t>S16: als INT drin</t>
+  </si>
+  <si>
+    <t>Zeit- und Synchronisationsstatus</t>
+  </si>
+  <si>
+    <t>U8[8]</t>
+  </si>
+  <si>
+    <t>{uint32_t PARAM_DATE_TIME, 
+uint32_t SYNC_STATUS}</t>
+  </si>
+  <si>
+    <t>nicht hinzugefügt</t>
+  </si>
+  <si>
+    <t>Aktiver Funkkanal</t>
+  </si>
+  <si>
+    <t>U16</t>
+  </si>
+  <si>
+    <t>Messwerte</t>
+  </si>
+  <si>
+    <t>Temperatur</t>
+  </si>
+  <si>
+    <t>FP32</t>
+  </si>
+  <si>
+    <t>NaN</t>
+  </si>
+  <si>
+    <t>°C</t>
+  </si>
+  <si>
+    <t>Mittelwert Temperatur</t>
+  </si>
+  <si>
+    <t>Identifikation</t>
+  </si>
+  <si>
+    <t>Hersteller ID</t>
+  </si>
+  <si>
+    <t>0x2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> = 42 = Siemens</t>
+  </si>
+  <si>
+    <t>Artikelnummer</t>
+  </si>
+  <si>
+    <t>UCHAR[20]</t>
+  </si>
+  <si>
+    <t>ASCII-Zeichen</t>
+  </si>
+  <si>
+    <t>Seriennummer</t>
+  </si>
+  <si>
+    <t>UCHAR[16]</t>
+  </si>
+  <si>
+    <t>Hardware Version</t>
+  </si>
+  <si>
+    <t>Software Version</t>
+  </si>
+  <si>
+    <t>UCHAR[4]</t>
+  </si>
+  <si>
+    <t>Anlagenkennzeichen (Name)</t>
+  </si>
+  <si>
+    <t>UCHAR[32]</t>
+  </si>
+  <si>
+    <t>RW</t>
+  </si>
+  <si>
+    <t>Einbauort</t>
+  </si>
+  <si>
+    <t>UCHAR[22]</t>
+  </si>
+  <si>
+    <t>Installationsdatum</t>
+  </si>
+  <si>
+    <t>Zielmarkt</t>
+  </si>
+  <si>
+    <t>1= IEC, 2=UL, 3=IEC+UL</t>
+  </si>
+  <si>
+    <t>Blinkmodus zur Grätelokalisierung</t>
+  </si>
+  <si>
+    <t>0 = Blinken stoppen, 1 = Blinken für 10 Sekunden</t>
+  </si>
+  <si>
+    <t>CMD</t>
+  </si>
+  <si>
+    <t>Hardware Ausgabestand</t>
+  </si>
+  <si>
+    <t>0 = nicht verfügbar, 1 = Stand 1 usw.</t>
+  </si>
+  <si>
+    <t>Gerätevariante</t>
+  </si>
+  <si>
+    <t>0xFFFE</t>
+  </si>
+  <si>
+    <t>0 = unbekannt, 
+1 = 5ST3 COM AS+FC, 2 = 3NA3 COM Fuse, 3 = 5SL6 COM MCB, 4 = 5SV6 COM AFDD,
+5 = 5ST3 COM RCA Standard, 6 = 5ST3 COM RCA mit RCD/IR Test, 7 = 5SL6 COM MCB RCM,
+8 = 5SV8 COM RCM, 9 = 3RV2 COM MSP, 10 = 5SV8 COM RCM (1 Kanal),
+11= 5TY1 COM ECPD, 14 = POC1100, 16 = POC2000, 
+18 = 5TT4 COM DIDO, 19 = 3NA6 COM Fuse</t>
+  </si>
+  <si>
+    <t>Vollständige Version des Parametersets</t>
+  </si>
+  <si>
+    <t>U64</t>
+  </si>
+  <si>
+    <t>Hauptversion des Parametersets</t>
+  </si>
+  <si>
+    <t>U8[4]</t>
+  </si>
+  <si>
+    <t>Beispiel: 0x56 0x01 0x00 0x00 "V100"; wird gelesen als "V1.0.0"</t>
+  </si>
+  <si>
+    <t>Diagnose Parameter</t>
+  </si>
+  <si>
+    <t>Alarm der Betriebsstunden ein/aus</t>
+  </si>
+  <si>
+    <t>0 = aus, 1 = ein</t>
+  </si>
+  <si>
+    <t>Grenzwert Betriebsstunden</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Zeitperiode für die Mittelwertbildung der Temperatur</t>
+  </si>
+  <si>
+    <t>Temperatur Alarm ein/aus</t>
+  </si>
+  <si>
+    <t>Grenzwert Temperaturüberschreitung</t>
+  </si>
+  <si>
+    <t>110
+3NA COM: 120
+Powercenter: 85</t>
+  </si>
+  <si>
+    <t>105
+3NA COM: 115
+Powercenter: 80</t>
+  </si>
+  <si>
+    <t>Hysterese Temperatur Alarm</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Letzte Diagnose Log OID</t>
+  </si>
+  <si>
+    <t>Letzte Message Log OID</t>
+  </si>
+  <si>
+    <t>IP Parameter</t>
+  </si>
+  <si>
+    <t>Ethernet MAC Adresse</t>
+  </si>
+  <si>
+    <t>UCHAR[6]</t>
+  </si>
+  <si>
+    <t>!</t>
+  </si>
+  <si>
+    <t>DHCP (automatische IP Vergabe) ein/aus</t>
+  </si>
+  <si>
+    <t>0 = DHCP aus, 1 = DHCP ein</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>SNTP Server IP-Adresse</t>
+  </si>
+  <si>
+    <t>0xFFFFFFFF</t>
+  </si>
+  <si>
+    <t>0.0.0.0</t>
+  </si>
+  <si>
+    <t>SNTP Client Mode</t>
+  </si>
+  <si>
+    <t>0 = aus, 1 = aktiv, 2 = broadcast</t>
+  </si>
+  <si>
+    <t>Firewall ein/aus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP Port Nummer </t>
+  </si>
+  <si>
+    <t>0xFFFF</t>
+  </si>
+  <si>
+    <t>Statische IP-Adresse</t>
+  </si>
+  <si>
+    <t>Statische Subnetzmaske</t>
+  </si>
+  <si>
+    <t>255.255.255.0</t>
+  </si>
+  <si>
+    <t>Statisches Gateway</t>
+  </si>
+  <si>
+    <t>Aktuelle IP-Adresse</t>
+  </si>
+  <si>
+    <t>Aktuelle Subnetzmaske</t>
+  </si>
+  <si>
+    <t>Aktuelle Gateway Adresse</t>
+  </si>
+  <si>
+    <t>BLE Parameter</t>
+  </si>
+  <si>
+    <t>Bluetooth Steuerung</t>
+  </si>
+  <si>
+    <t>1= BLE ein, 2 = BLE aus, 3 = Passkey zurücksetzen</t>
+  </si>
+  <si>
+    <t>Bluetooth Status</t>
+  </si>
+  <si>
+    <t>Bluetooth Sendeleistung</t>
+  </si>
+  <si>
+    <t>Bluetooth Geräteadresse</t>
+  </si>
+  <si>
+    <t>U8[6]</t>
+  </si>
+  <si>
+    <t>Bluetooth Passkey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funk Parameter </t>
+  </si>
+  <si>
+    <t>Datum/Zeit (UTC)</t>
+  </si>
+  <si>
+    <t>UNIX_TS seit 01.01.1970</t>
+  </si>
+  <si>
+    <t>Funk Sendeleistung</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 1</t>
+  </si>
+  <si>
+    <t>Zählt hoch, wenn am Endgerät einen Parameter verändert wird</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 2</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 3</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 4</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 5</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 6</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 7</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 8</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 9</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 10</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 11</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 12</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 13</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 14</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 15</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 16</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 17</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 18</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 19</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 20</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 21</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 22</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 23</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Endgerät 24</t>
+  </si>
+  <si>
+    <t>Zähler Parameteränderung Powercenter</t>
+  </si>
+  <si>
+    <t>Zählt hoch, wenn am Powercenter einen Parameter verändert wird</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 1</t>
+  </si>
+  <si>
+    <t>0 = unbekannt, 1 = AUS, 2 = EIN, 3 = Ausgelöst, 4= reserve, 5 = Standby</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 2</t>
+  </si>
+  <si>
+    <t>siehe Registernr. 1201</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 3</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 4</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 5</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 6</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 7</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 8</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 9</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 10</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 11</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 12</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 13</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 14</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 15</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 16</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 17</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 18</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 19</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 20</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 21</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 22</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 23</t>
+  </si>
+  <si>
+    <t>Schalter Status Endgerät 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manuelle Funkkanalauswahl ein/aus </t>
+  </si>
+  <si>
+    <t>0 = aus, 1 = ein
+Nur vor 1. Pairing einstellbar
+Ab Version 2.0 verfügbar</t>
+  </si>
+  <si>
+    <t>Funkkanalauswahl</t>
+  </si>
+  <si>
+    <t>Nur vor 1. Pairing einstellbar
+Ab Version 2.0 verfügbar</t>
+  </si>
+  <si>
+    <t>Pairing Status (1)</t>
+  </si>
+  <si>
+    <t>0 = nicht verfügbar (MAC/Installationscode fehlen)
+1 = Pairing läuft
+2 = Pairing abgeschlossen
+4 = Pairing fehlgeschlagen
+5 = Pairing Timeout
+9 = Entfernen läuft
+11 = Entfernen timeout</t>
+  </si>
+  <si>
+    <t>Pairing Status (2)</t>
+  </si>
+  <si>
+    <t>siehe Registernr. 16384</t>
+  </si>
+  <si>
+    <t>Pairing Status (3)</t>
+  </si>
+  <si>
+    <t>Pairing Status (4)</t>
+  </si>
+  <si>
+    <t>Pairing Status (5)</t>
+  </si>
+  <si>
+    <t>Pairing Status (6)</t>
+  </si>
+  <si>
+    <t>Pairing Status (7)</t>
+  </si>
+  <si>
+    <t>Pairing Status (8)</t>
+  </si>
+  <si>
+    <t>Pairing Status (9)</t>
+  </si>
+  <si>
+    <t>Pairing Status (10)</t>
+  </si>
+  <si>
+    <t>Pairing Status (11)</t>
+  </si>
+  <si>
+    <t>Pairing Status (12)</t>
+  </si>
+  <si>
+    <t>Pairing Status (13)</t>
+  </si>
+  <si>
+    <t>Pairing Status (14)</t>
+  </si>
+  <si>
+    <t>Pairing Status (15)</t>
+  </si>
+  <si>
+    <t>Pairing Status (16)</t>
+  </si>
+  <si>
+    <t>Pairing Status (17)</t>
+  </si>
+  <si>
+    <t>Pairing Status (18)</t>
+  </si>
+  <si>
+    <t>Pairing Status (19)</t>
+  </si>
+  <si>
+    <t>Pairing Status (20)</t>
+  </si>
+  <si>
+    <t>Pairing Status (21)</t>
+  </si>
+  <si>
+    <t>Pairing Status (22)</t>
+  </si>
+  <si>
+    <t>Pairing Status (23)</t>
+  </si>
+  <si>
+    <t>Pairing Status (24)</t>
+  </si>
+  <si>
+    <t>Device Status (1)</t>
+  </si>
+  <si>
+    <t>0 = IDLE (Kein Endgerät gepaired)
+1 = Offline, 2 = Verbinden läuft,  3 = Verbunden</t>
+  </si>
+  <si>
+    <t>Device Status (2)</t>
+  </si>
+  <si>
+    <t>siehe Registernr. 16484</t>
+  </si>
+  <si>
+    <t>Device Status (3)</t>
+  </si>
+  <si>
+    <t>Device Status (4)</t>
+  </si>
+  <si>
+    <t>Device Status (5)</t>
+  </si>
+  <si>
+    <t>Device Status (6)</t>
+  </si>
+  <si>
+    <t>Device Status (7)</t>
+  </si>
+  <si>
+    <t>Device Status (8)</t>
+  </si>
+  <si>
+    <t>Device Status (9)</t>
+  </si>
+  <si>
+    <t>Device Status (10)</t>
+  </si>
+  <si>
+    <t>Device Status (11)</t>
+  </si>
+  <si>
+    <t>Device Status (12)</t>
+  </si>
+  <si>
+    <t>Device Status (13)</t>
+  </si>
+  <si>
+    <t>Device Status (14)</t>
+  </si>
+  <si>
+    <t>Device Status (15)</t>
+  </si>
+  <si>
+    <t>Device Status (16)</t>
+  </si>
+  <si>
+    <t>Device Status (17)</t>
+  </si>
+  <si>
+    <t>Device Status (18)</t>
+  </si>
+  <si>
+    <t>Device Status (19)</t>
+  </si>
+  <si>
+    <t>Device Status (20)</t>
+  </si>
+  <si>
+    <t>Device Status (21)</t>
+  </si>
+  <si>
+    <t>Device Status (22)</t>
+  </si>
+  <si>
+    <t>Device Status (23)</t>
+  </si>
+  <si>
+    <t>Device Status (24)</t>
+  </si>
+  <si>
+    <t>Koppeln/Entfernen des Endgeräts</t>
+  </si>
+  <si>
+    <t>U8[100]</t>
+  </si>
+  <si>
+    <t>0 = Keine Aktion, 1 = Start Pairing, 3 = Gerät entfernen/Pairing abbrechen
+(Beispiel: Pairing starten für End Gerät 1 und 3: Byte 1 &amp; 3 auf den Wert 1 setzen, die anderen sind 0)</t>
+  </si>
+  <si>
+    <t>Identifikation Status (1)</t>
+  </si>
+  <si>
+    <t>0 = Initial, 1 = Gerät unbekannt, 2 = Fehler bitte Gerät entfernen, 3 = Gerät erkannt</t>
+  </si>
+  <si>
+    <t>Identifikation Status (2)</t>
+  </si>
+  <si>
+    <t>siehe Registernr. 17934</t>
+  </si>
+  <si>
+    <t>Identifikation Status (3)</t>
+  </si>
+  <si>
+    <t>Identifikation Status (4)</t>
+  </si>
+  <si>
+    <t>Identifikation Status (5)</t>
+  </si>
+  <si>
+    <t>Identifikation Status (6)</t>
+  </si>
+  <si>
+    <t>Identifikation Status (7)</t>
+  </si>
+  <si>
+    <t>Identifikation Status (8)</t>
+  </si>
+  <si>
+    <t>Identifikation Status (9)</t>
+  </si>
+  <si>
+    <t>Identifikation Status (10)</t>
+  </si>
+  <si>
+    <t>Identifikation Status (11)</t>
+  </si>
+  <si>
+    <t>Identifikation Status (12)</t>
+  </si>
+  <si>
+    <t>Identifikation Status (13)</t>
+  </si>
+  <si>
+    <t>Identifikation Status (14)</t>
+  </si>
+  <si>
+    <t>Identifikation Status (15)</t>
+  </si>
+  <si>
+    <t>Identifikation Status (16)</t>
+  </si>
+  <si>
+    <t>Identifikation Status (17)</t>
+  </si>
+  <si>
+    <t>Identifikation Status (18)</t>
+  </si>
+  <si>
+    <t>Identifikation Status (19)</t>
+  </si>
+  <si>
+    <t>Identifikation Status (20)</t>
+  </si>
+  <si>
+    <t>Identifikation Status (21)</t>
+  </si>
+  <si>
+    <t>Identifikation Status (22)</t>
+  </si>
+  <si>
+    <t>Identifikation Status (23)</t>
+  </si>
+  <si>
+    <t>Identifikation Status (24)</t>
+  </si>
+  <si>
+    <t>Delayed ACK</t>
+  </si>
+  <si>
+    <t>Status der aktuellen Delayed-Acknowledge-Anfrage</t>
+  </si>
+  <si>
+    <t>0x00000000: Idle. Kein Schreib-Prozess laufend, Warten auf Prozess 
+0x00000001: Läuft. Endgerät beschäftigt. Schhreibanfrage wird abgelehnt.  
+0x00000002: Erfolg: Schhreibanfrage wird abgelehnt bis in IDLE State versetzt. 
+0x00000003: Fehlgeschlagen. Schhreibanfrage wird abgelehnt bis in IDLE State versetzt.</t>
+  </si>
+  <si>
+    <t>Delayed Response Log Information</t>
+  </si>
+  <si>
+    <t>UCHAR[242]</t>
+  </si>
+  <si>
+    <t>Status der aktuellen Delayed-Acknowledge Read Log Anfrage</t>
+  </si>
+  <si>
+    <t>0x00000000: Idle. Kein Lese-Prozess laufend, Warten auf Prozess 
+0x00000001: Läuft. Endgerät beschäftigt. Schhreibanfrage wird abgelehnt.  
+0x00000002: Erfolg: Schhreibanfrage wird abgelehnt bis in IDLE State versetzt. 
+0x00000003: Fehlgeschlagen. Schhreibanfrage wird abgelehnt bis in IDLE State versetzt.</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Status lokales Usermanagement</t>
+  </si>
+  <si>
+    <t>U8</t>
+  </si>
+  <si>
+    <t>Bitwert: 0=nein, 1 =ja
+Bitfeld:
+0: Mind. 1 Superuser angelegt?</t>
+  </si>
+  <si>
+    <t>Schreibschutz Status</t>
+  </si>
+  <si>
+    <t>Bitwert: 0=deaktiviert, 1 =aktiviert
+Bitfeld:
+0: Mechanischer Schreibschutz</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -457,19 +1328,65 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -478,10 +1395,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -818,13 +1753,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A47F84-D45D-4D83-8E6F-A400BE206714}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="48.7109375" customWidth="1"/>
     <col min="3" max="3" width="38.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -832,192 +1767,195 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="60">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="45">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:3" ht="45">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3" ht="60">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="45">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="45">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="60">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="45">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="30">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="30">
+      <c r="A11" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="1"/>
-    </row>
-    <row r="5" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="1" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>12</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1031,13 +1969,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B85D5878-C431-4350-AFD6-92309A5E1C15}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="48.7109375" customWidth="1"/>
     <col min="3" max="3" width="38.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1045,298 +1983,302 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="30">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="90">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="60">
       <c r="A4" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="30">
       <c r="A5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="30">
       <c r="A6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="1"/>
+        <v>52</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3">
       <c r="A37" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="A38" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="A39" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3">
       <c r="A40" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C40" s="1"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3">
       <c r="A41" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C41" s="1"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3">
       <c r="A42" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C42" s="1"/>
     </row>
@@ -1349,13 +2291,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECA61290-7F82-4B5E-94C7-2D8A84275AA6}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="48.7109375" customWidth="1"/>
     <col min="3" max="3" width="38.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1363,303 +2305,5669 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="45">
       <c r="A2" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="60">
       <c r="A3" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="60">
       <c r="A4" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="45">
       <c r="A5" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B5" s="1"/>
+        <v>97</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3">
       <c r="A37" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="A38" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="A39" s="1" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3">
       <c r="A40" s="1" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C40" s="1"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3">
       <c r="A41" s="1" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C41" s="1"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3">
       <c r="A42" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C42" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8095803C-CDA8-41F7-A088-EC9632D8B9F6}">
+  <dimension ref="A1:M178"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="57" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="45">
+      <c r="A1" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="405">
+      <c r="A2" s="3">
+        <v>2560</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L2" s="6"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="3">
+        <v>2578</v>
+      </c>
+      <c r="B3" s="3">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L3" s="6"/>
+      <c r="M3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="3">
+        <v>2621</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F4" s="3">
+        <v>-127</v>
+      </c>
+      <c r="G4" s="3">
+        <v>20</v>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L4" s="6"/>
+      <c r="M4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="30">
+      <c r="A5" s="3">
+        <v>2629</v>
+      </c>
+      <c r="B5" s="3">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3">
+        <v>946684800</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L5" s="6"/>
+      <c r="M5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="3">
+        <v>2633</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>26</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L6" s="6"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="3">
+        <v>3072</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L7" s="6"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="3">
+        <v>3074</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L8" s="6"/>
+      <c r="M8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="30">
+      <c r="A9" s="3">
+        <v>2</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L9" s="6"/>
+    </row>
+    <row r="10" spans="1:13" ht="30">
+      <c r="A10" s="3">
+        <v>3</v>
+      </c>
+      <c r="B10" s="3">
+        <v>10</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L10" s="6"/>
+    </row>
+    <row r="11" spans="1:13" ht="30">
+      <c r="A11" s="3">
+        <v>13</v>
+      </c>
+      <c r="B11" s="3">
+        <v>8</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L11" s="6"/>
+    </row>
+    <row r="12" spans="1:13" ht="30">
+      <c r="A12" s="3">
+        <v>21</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L12" s="6"/>
+    </row>
+    <row r="13" spans="1:13" ht="30">
+      <c r="A13" s="3">
+        <v>22</v>
+      </c>
+      <c r="B13" s="3">
+        <v>2</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L13" s="6"/>
+    </row>
+    <row r="14" spans="1:13" ht="30">
+      <c r="A14" s="3">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3">
+        <v>16</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L14" s="6"/>
+    </row>
+    <row r="15" spans="1:13" ht="30">
+      <c r="A15" s="3">
+        <v>45</v>
+      </c>
+      <c r="B15" s="3">
+        <v>11</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L15" s="6"/>
+    </row>
+    <row r="16" spans="1:13" ht="30">
+      <c r="A16" s="3">
+        <v>56</v>
+      </c>
+      <c r="B16" s="3">
+        <v>8</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L16" s="6"/>
+    </row>
+    <row r="17" spans="1:12" ht="30">
+      <c r="A17" s="3">
+        <v>94</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1</v>
+      </c>
+      <c r="G17" s="3">
+        <v>3</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L17" s="6"/>
+    </row>
+    <row r="18" spans="1:12" ht="30">
+      <c r="A18" s="3">
+        <v>97</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="L18" s="6"/>
+    </row>
+    <row r="19" spans="1:12" ht="30">
+      <c r="A19" s="3">
+        <v>109</v>
+      </c>
+      <c r="B19" s="3">
+        <v>1</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3">
+        <v>10</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L19" s="6"/>
+    </row>
+    <row r="20" spans="1:12" ht="135">
+      <c r="A20" s="3">
+        <v>112</v>
+      </c>
+      <c r="B20" s="3">
+        <v>1</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L20" s="6"/>
+    </row>
+    <row r="21" spans="1:12" ht="30">
+      <c r="A21" s="3">
+        <v>170</v>
+      </c>
+      <c r="B21" s="3">
+        <v>4</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L21" s="6"/>
+    </row>
+    <row r="22" spans="1:12" ht="30">
+      <c r="A22" s="3">
+        <v>174</v>
+      </c>
+      <c r="B22" s="3">
+        <v>2</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L22" s="6"/>
+    </row>
+    <row r="23" spans="1:12" ht="30">
+      <c r="A23" s="3">
+        <v>2582</v>
+      </c>
+      <c r="B23" s="3">
+        <v>1</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
+        <v>1</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L23" s="6"/>
+    </row>
+    <row r="24" spans="1:12" ht="30">
+      <c r="A24" s="3">
+        <v>2583</v>
+      </c>
+      <c r="B24" s="3">
+        <v>4</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F24" s="3">
+        <v>60</v>
+      </c>
+      <c r="G24" s="3">
+        <v>864000000</v>
+      </c>
+      <c r="H24" s="3">
+        <v>158000000</v>
+      </c>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L24" s="6"/>
+    </row>
+    <row r="25" spans="1:12" ht="30">
+      <c r="A25" s="3">
+        <v>3586</v>
+      </c>
+      <c r="B25" s="3">
+        <v>2</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F25" s="3">
+        <v>60</v>
+      </c>
+      <c r="G25" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H25" s="3">
+        <v>600</v>
+      </c>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L25" s="6"/>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="3">
+        <v>3588</v>
+      </c>
+      <c r="B26" s="3">
+        <v>1</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
+        <v>1</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L26" s="6"/>
+    </row>
+    <row r="27" spans="1:12" ht="90">
+      <c r="A27" s="3">
+        <v>3589</v>
+      </c>
+      <c r="B27" s="3">
+        <v>2</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F27" s="3">
+        <v>20</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L27" s="6"/>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="3">
+        <v>3591</v>
+      </c>
+      <c r="B28" s="3">
+        <v>2</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F28" s="3">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3">
+        <v>10</v>
+      </c>
+      <c r="H28" s="3">
+        <v>10</v>
+      </c>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L28" s="6"/>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="3">
+        <v>3593</v>
+      </c>
+      <c r="B29" s="3">
+        <v>2</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L29" s="6"/>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="3">
+        <v>3672</v>
+      </c>
+      <c r="B30" s="3">
+        <v>2</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L30" s="6"/>
+    </row>
+    <row r="31" spans="1:12" ht="30">
+      <c r="A31" s="2">
+        <v>512</v>
+      </c>
+      <c r="B31" s="3">
+        <v>3</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L31" s="6"/>
+    </row>
+    <row r="32" spans="1:12" ht="30">
+      <c r="A32" s="2">
+        <v>513</v>
+      </c>
+      <c r="B32" s="3">
+        <v>2</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>1</v>
+      </c>
+      <c r="H32" s="3">
+        <v>1</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="30">
+      <c r="A33" s="2">
+        <v>514</v>
+      </c>
+      <c r="B33" s="3">
+        <v>2</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="30">
+      <c r="A34" s="2">
+        <v>515</v>
+      </c>
+      <c r="B34" s="3">
+        <v>2</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F34" s="3">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3">
+        <v>2</v>
+      </c>
+      <c r="H34" s="3">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="30">
+      <c r="A35" s="2">
+        <v>516</v>
+      </c>
+      <c r="B35" s="3">
+        <v>2</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
+        <v>1</v>
+      </c>
+      <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="30">
+      <c r="A36" s="2">
+        <v>517</v>
+      </c>
+      <c r="B36" s="3">
+        <v>2</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F36" s="3">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H36" s="3">
+        <v>502</v>
+      </c>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="30">
+      <c r="A37" s="2">
+        <v>518</v>
+      </c>
+      <c r="B37" s="3">
+        <v>2</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F37" s="3">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="30">
+      <c r="A38" s="2">
+        <v>519</v>
+      </c>
+      <c r="B38" s="3">
+        <v>2</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F38" s="3">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="30">
+      <c r="A39" s="2">
+        <v>520</v>
+      </c>
+      <c r="B39" s="3">
+        <v>2</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F39" s="3">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="30">
+      <c r="A40" s="2">
+        <v>528</v>
+      </c>
+      <c r="B40" s="3">
+        <v>2</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L40" s="2"/>
+    </row>
+    <row r="41" spans="1:12" ht="30">
+      <c r="A41" s="2">
+        <v>529</v>
+      </c>
+      <c r="B41" s="3">
+        <v>2</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L41" s="2"/>
+    </row>
+    <row r="42" spans="1:12" ht="30">
+      <c r="A42" s="2">
+        <v>530</v>
+      </c>
+      <c r="B42" s="3">
+        <v>2</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L42" s="2"/>
+    </row>
+    <row r="43" spans="1:12" ht="30">
+      <c r="A43" s="2">
+        <v>768</v>
+      </c>
+      <c r="B43" s="3">
+        <v>1</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F43" s="3">
+        <v>1</v>
+      </c>
+      <c r="G43" s="3">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="30">
+      <c r="A44" s="2">
+        <v>769</v>
+      </c>
+      <c r="B44" s="3">
+        <v>1</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L44" s="2"/>
+    </row>
+    <row r="45" spans="1:12" ht="30">
+      <c r="A45" s="2">
+        <v>770</v>
+      </c>
+      <c r="B45" s="3">
+        <v>1</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F45" s="3">
+        <v>-18</v>
+      </c>
+      <c r="G45" s="3">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3">
+        <v>2</v>
+      </c>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="30">
+      <c r="A46" s="2">
+        <v>771</v>
+      </c>
+      <c r="B46" s="3">
+        <v>3</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L46" s="2"/>
+    </row>
+    <row r="47" spans="1:12" ht="30">
+      <c r="A47" s="2">
+        <v>772</v>
+      </c>
+      <c r="B47" s="3">
+        <v>2</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="30">
+      <c r="A48" s="2">
+        <v>1024</v>
+      </c>
+      <c r="B48" s="3">
+        <v>2</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F48" s="3">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H48" s="3">
+        <v>946684800</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L48" s="2"/>
+    </row>
+    <row r="49" spans="1:12" ht="30">
+      <c r="A49" s="2">
+        <v>1049</v>
+      </c>
+      <c r="B49" s="3">
+        <v>1</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F49" s="3">
+        <v>-18</v>
+      </c>
+      <c r="G49" s="3">
+        <v>2</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="30">
+      <c r="A50" s="2">
+        <v>1099</v>
+      </c>
+      <c r="B50" s="3">
+        <v>1</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F50" s="3">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H50" s="3">
+        <v>0</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L50" s="2"/>
+    </row>
+    <row r="51" spans="1:12" ht="30">
+      <c r="A51" s="2">
+        <v>1100</v>
+      </c>
+      <c r="B51" s="3">
+        <v>1</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F51" s="3">
+        <v>0</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H51" s="3">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L51" s="2"/>
+    </row>
+    <row r="52" spans="1:12" ht="30">
+      <c r="A52" s="2">
+        <v>1101</v>
+      </c>
+      <c r="B52" s="3">
+        <v>1</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L52" s="2"/>
+    </row>
+    <row r="53" spans="1:12" ht="30">
+      <c r="A53" s="2">
+        <v>1102</v>
+      </c>
+      <c r="B53" s="3">
+        <v>1</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F53" s="3">
+        <v>0</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H53" s="3">
+        <v>0</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L53" s="2"/>
+    </row>
+    <row r="54" spans="1:12" ht="30">
+      <c r="A54" s="2">
+        <v>1103</v>
+      </c>
+      <c r="B54" s="3">
+        <v>1</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F54" s="3">
+        <v>0</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H54" s="3">
+        <v>0</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J54" s="3"/>
+      <c r="K54" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L54" s="2"/>
+    </row>
+    <row r="55" spans="1:12" ht="30">
+      <c r="A55" s="2">
+        <v>1104</v>
+      </c>
+      <c r="B55" s="3">
+        <v>1</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F55" s="3">
+        <v>0</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H55" s="3">
+        <v>0</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L55" s="2"/>
+    </row>
+    <row r="56" spans="1:12" ht="30">
+      <c r="A56" s="2">
+        <v>1105</v>
+      </c>
+      <c r="B56" s="3">
+        <v>1</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F56" s="3">
+        <v>0</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H56" s="3">
+        <v>0</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L56" s="2"/>
+    </row>
+    <row r="57" spans="1:12" ht="30">
+      <c r="A57" s="2">
+        <v>1106</v>
+      </c>
+      <c r="B57" s="3">
+        <v>1</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H57" s="3">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J57" s="3"/>
+      <c r="K57" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L57" s="2"/>
+    </row>
+    <row r="58" spans="1:12" ht="30">
+      <c r="A58" s="2">
+        <v>1107</v>
+      </c>
+      <c r="B58" s="3">
+        <v>1</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J58" s="3"/>
+      <c r="K58" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L58" s="2"/>
+    </row>
+    <row r="59" spans="1:12" ht="30">
+      <c r="A59" s="2">
+        <v>1108</v>
+      </c>
+      <c r="B59" s="3">
+        <v>1</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J59" s="3"/>
+      <c r="K59" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L59" s="2"/>
+    </row>
+    <row r="60" spans="1:12" ht="30">
+      <c r="A60" s="2">
+        <v>1109</v>
+      </c>
+      <c r="B60" s="3">
+        <v>1</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F60" s="3">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H60" s="3">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J60" s="3"/>
+      <c r="K60" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L60" s="2"/>
+    </row>
+    <row r="61" spans="1:12" ht="30">
+      <c r="A61" s="2">
+        <v>1110</v>
+      </c>
+      <c r="B61" s="3">
+        <v>1</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J61" s="3"/>
+      <c r="K61" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L61" s="2"/>
+    </row>
+    <row r="62" spans="1:12" ht="30">
+      <c r="A62" s="2">
+        <v>1111</v>
+      </c>
+      <c r="B62" s="3">
+        <v>1</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J62" s="3"/>
+      <c r="K62" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L62" s="2"/>
+    </row>
+    <row r="63" spans="1:12" ht="30">
+      <c r="A63" s="2">
+        <v>1112</v>
+      </c>
+      <c r="B63" s="3">
+        <v>1</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F63" s="3">
+        <v>0</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H63" s="3">
+        <v>0</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J63" s="3"/>
+      <c r="K63" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L63" s="2"/>
+    </row>
+    <row r="64" spans="1:12" ht="30">
+      <c r="A64" s="2">
+        <v>1113</v>
+      </c>
+      <c r="B64" s="3">
+        <v>1</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F64" s="3">
+        <v>0</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H64" s="3">
+        <v>0</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L64" s="2"/>
+    </row>
+    <row r="65" spans="1:12" ht="30">
+      <c r="A65" s="2">
+        <v>1114</v>
+      </c>
+      <c r="B65" s="3">
+        <v>1</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F65" s="3">
+        <v>0</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H65" s="3">
+        <v>0</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J65" s="3"/>
+      <c r="K65" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L65" s="2"/>
+    </row>
+    <row r="66" spans="1:12" ht="30">
+      <c r="A66" s="2">
+        <v>1115</v>
+      </c>
+      <c r="B66" s="3">
+        <v>1</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F66" s="3">
+        <v>0</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H66" s="3">
+        <v>0</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J66" s="3"/>
+      <c r="K66" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L66" s="2"/>
+    </row>
+    <row r="67" spans="1:12" ht="30">
+      <c r="A67" s="2">
+        <v>1116</v>
+      </c>
+      <c r="B67" s="3">
+        <v>1</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F67" s="3">
+        <v>0</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H67" s="3">
+        <v>0</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J67" s="3"/>
+      <c r="K67" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L67" s="2"/>
+    </row>
+    <row r="68" spans="1:12" ht="30">
+      <c r="A68" s="2">
+        <v>1117</v>
+      </c>
+      <c r="B68" s="3">
+        <v>1</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F68" s="3">
+        <v>0</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H68" s="3">
+        <v>0</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J68" s="3"/>
+      <c r="K68" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L68" s="2"/>
+    </row>
+    <row r="69" spans="1:12" ht="30">
+      <c r="A69" s="2">
+        <v>1118</v>
+      </c>
+      <c r="B69" s="3">
+        <v>1</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F69" s="3">
+        <v>0</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H69" s="3">
+        <v>0</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L69" s="2"/>
+    </row>
+    <row r="70" spans="1:12" ht="30">
+      <c r="A70" s="2">
+        <v>1119</v>
+      </c>
+      <c r="B70" s="3">
+        <v>1</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F70" s="3">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J70" s="3"/>
+      <c r="K70" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L70" s="2"/>
+    </row>
+    <row r="71" spans="1:12" ht="30">
+      <c r="A71" s="2">
+        <v>1120</v>
+      </c>
+      <c r="B71" s="3">
+        <v>1</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F71" s="3">
+        <v>0</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H71" s="3">
+        <v>0</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J71" s="3"/>
+      <c r="K71" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L71" s="2"/>
+    </row>
+    <row r="72" spans="1:12" ht="30">
+      <c r="A72" s="2">
+        <v>1121</v>
+      </c>
+      <c r="B72" s="3">
+        <v>1</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F72" s="3">
+        <v>0</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H72" s="3">
+        <v>0</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L72" s="2"/>
+    </row>
+    <row r="73" spans="1:12" ht="30">
+      <c r="A73" s="2">
+        <v>1122</v>
+      </c>
+      <c r="B73" s="3">
+        <v>1</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F73" s="3">
+        <v>0</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H73" s="3">
+        <v>0</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J73" s="3"/>
+      <c r="K73" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L73" s="2"/>
+    </row>
+    <row r="74" spans="1:12" ht="30">
+      <c r="A74" s="2">
+        <v>1123</v>
+      </c>
+      <c r="B74" s="3">
+        <v>1</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F74" s="3">
+        <v>0</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H74" s="3">
+        <v>0</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="J74" s="3"/>
+      <c r="K74" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L74" s="2"/>
+    </row>
+    <row r="75" spans="1:12" ht="30">
+      <c r="A75" s="2">
+        <v>1200</v>
+      </c>
+      <c r="B75" s="3">
+        <v>1</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="J75" s="3"/>
+      <c r="K75" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L75" s="2"/>
+    </row>
+    <row r="76" spans="1:12" ht="30">
+      <c r="A76" s="2">
+        <v>1201</v>
+      </c>
+      <c r="B76" s="3">
+        <v>1</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J76" s="3"/>
+      <c r="K76" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L76" s="2"/>
+    </row>
+    <row r="77" spans="1:12" ht="30">
+      <c r="A77" s="2">
+        <v>1202</v>
+      </c>
+      <c r="B77" s="3">
+        <v>1</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J77" s="3"/>
+      <c r="K77" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L77" s="2"/>
+    </row>
+    <row r="78" spans="1:12" ht="30">
+      <c r="A78" s="2">
+        <v>1203</v>
+      </c>
+      <c r="B78" s="3">
+        <v>1</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J78" s="3"/>
+      <c r="K78" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L78" s="2"/>
+    </row>
+    <row r="79" spans="1:12" ht="30">
+      <c r="A79" s="2">
+        <v>1204</v>
+      </c>
+      <c r="B79" s="3">
+        <v>1</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J79" s="3"/>
+      <c r="K79" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L79" s="2"/>
+    </row>
+    <row r="80" spans="1:12" ht="30">
+      <c r="A80" s="2">
+        <v>1205</v>
+      </c>
+      <c r="B80" s="3">
+        <v>1</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J80" s="3"/>
+      <c r="K80" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="1:12" ht="30">
+      <c r="A81" s="2">
+        <v>1206</v>
+      </c>
+      <c r="B81" s="3">
+        <v>1</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3"/>
+      <c r="I81" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J81" s="3"/>
+      <c r="K81" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L81" s="2"/>
+    </row>
+    <row r="82" spans="1:12" ht="30">
+      <c r="A82" s="2">
+        <v>1207</v>
+      </c>
+      <c r="B82" s="3">
+        <v>1</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+      <c r="H82" s="3"/>
+      <c r="I82" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J82" s="3"/>
+      <c r="K82" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L82" s="2"/>
+    </row>
+    <row r="83" spans="1:12" ht="30">
+      <c r="A83" s="2">
+        <v>1208</v>
+      </c>
+      <c r="B83" s="3">
+        <v>1</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
+      <c r="H83" s="3"/>
+      <c r="I83" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J83" s="3"/>
+      <c r="K83" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L83" s="2"/>
+    </row>
+    <row r="84" spans="1:12" ht="30">
+      <c r="A84" s="2">
+        <v>1209</v>
+      </c>
+      <c r="B84" s="3">
+        <v>1</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="H84" s="3"/>
+      <c r="I84" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J84" s="3"/>
+      <c r="K84" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L84" s="2"/>
+    </row>
+    <row r="85" spans="1:12" ht="30">
+      <c r="A85" s="2">
+        <v>1210</v>
+      </c>
+      <c r="B85" s="3">
+        <v>1</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
+      <c r="H85" s="3"/>
+      <c r="I85" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J85" s="3"/>
+      <c r="K85" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L85" s="2"/>
+    </row>
+    <row r="86" spans="1:12" ht="30">
+      <c r="A86" s="2">
+        <v>1211</v>
+      </c>
+      <c r="B86" s="3">
+        <v>1</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3"/>
+      <c r="I86" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J86" s="3"/>
+      <c r="K86" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L86" s="2"/>
+    </row>
+    <row r="87" spans="1:12" ht="30">
+      <c r="A87" s="2">
+        <v>1212</v>
+      </c>
+      <c r="B87" s="3">
+        <v>1</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+      <c r="I87" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J87" s="3"/>
+      <c r="K87" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L87" s="2"/>
+    </row>
+    <row r="88" spans="1:12" ht="30">
+      <c r="A88" s="2">
+        <v>1213</v>
+      </c>
+      <c r="B88" s="3">
+        <v>1</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
+      <c r="I88" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J88" s="3"/>
+      <c r="K88" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L88" s="2"/>
+    </row>
+    <row r="89" spans="1:12" ht="30">
+      <c r="A89" s="2">
+        <v>1214</v>
+      </c>
+      <c r="B89" s="3">
+        <v>1</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="H89" s="3"/>
+      <c r="I89" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J89" s="3"/>
+      <c r="K89" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L89" s="2"/>
+    </row>
+    <row r="90" spans="1:12" ht="30">
+      <c r="A90" s="2">
+        <v>1215</v>
+      </c>
+      <c r="B90" s="3">
+        <v>1</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
+      <c r="I90" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J90" s="3"/>
+      <c r="K90" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L90" s="2"/>
+    </row>
+    <row r="91" spans="1:12" ht="30">
+      <c r="A91" s="2">
+        <v>1216</v>
+      </c>
+      <c r="B91" s="3">
+        <v>1</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+      <c r="I91" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J91" s="3"/>
+      <c r="K91" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L91" s="2"/>
+    </row>
+    <row r="92" spans="1:12" ht="30">
+      <c r="A92" s="2">
+        <v>1217</v>
+      </c>
+      <c r="B92" s="3">
+        <v>1</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
+      <c r="I92" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J92" s="3"/>
+      <c r="K92" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L92" s="2"/>
+    </row>
+    <row r="93" spans="1:12" ht="30">
+      <c r="A93" s="2">
+        <v>1218</v>
+      </c>
+      <c r="B93" s="3">
+        <v>1</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
+      <c r="I93" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J93" s="3"/>
+      <c r="K93" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L93" s="2"/>
+    </row>
+    <row r="94" spans="1:12" ht="30">
+      <c r="A94" s="2">
+        <v>1219</v>
+      </c>
+      <c r="B94" s="3">
+        <v>1</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3"/>
+      <c r="I94" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J94" s="3"/>
+      <c r="K94" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L94" s="2"/>
+    </row>
+    <row r="95" spans="1:12" ht="30">
+      <c r="A95" s="2">
+        <v>1220</v>
+      </c>
+      <c r="B95" s="3">
+        <v>1</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J95" s="3"/>
+      <c r="K95" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L95" s="2"/>
+    </row>
+    <row r="96" spans="1:12" ht="30">
+      <c r="A96" s="2">
+        <v>1221</v>
+      </c>
+      <c r="B96" s="3">
+        <v>1</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J96" s="3"/>
+      <c r="K96" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L96" s="2"/>
+    </row>
+    <row r="97" spans="1:12" ht="30">
+      <c r="A97" s="2">
+        <v>1222</v>
+      </c>
+      <c r="B97" s="3">
+        <v>1</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3"/>
+      <c r="I97" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J97" s="3"/>
+      <c r="K97" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L97" s="2"/>
+    </row>
+    <row r="98" spans="1:12" ht="30">
+      <c r="A98" s="2">
+        <v>1223</v>
+      </c>
+      <c r="B98" s="3">
+        <v>1</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J98" s="3"/>
+      <c r="K98" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L98" s="2"/>
+    </row>
+    <row r="99" spans="1:12" ht="45">
+      <c r="A99" s="2">
+        <v>1585</v>
+      </c>
+      <c r="B99" s="3">
+        <v>1</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F99" s="3">
+        <v>0</v>
+      </c>
+      <c r="G99" s="3">
+        <v>1</v>
+      </c>
+      <c r="H99" s="3">
+        <v>0</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="J99" s="3"/>
+      <c r="K99" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="30">
+      <c r="A100" s="2">
+        <v>1586</v>
+      </c>
+      <c r="B100" s="3">
+        <v>1</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F100" s="3">
+        <v>11</v>
+      </c>
+      <c r="G100" s="3">
+        <v>26</v>
+      </c>
+      <c r="H100" s="3">
+        <v>11</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="J100" s="3"/>
+      <c r="K100" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L100" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="105">
+      <c r="A101" s="2">
+        <v>16384</v>
+      </c>
+      <c r="B101" s="3">
+        <v>1</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3"/>
+      <c r="I101" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="J101" s="3"/>
+      <c r="K101" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L101" s="2"/>
+    </row>
+    <row r="102" spans="1:12" ht="30">
+      <c r="A102" s="2">
+        <v>16385</v>
+      </c>
+      <c r="B102" s="3">
+        <v>1</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J102" s="3"/>
+      <c r="K102" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L102" s="2"/>
+    </row>
+    <row r="103" spans="1:12" ht="30">
+      <c r="A103" s="2">
+        <v>16386</v>
+      </c>
+      <c r="B103" s="3">
+        <v>1</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
+      <c r="H103" s="3"/>
+      <c r="I103" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J103" s="3"/>
+      <c r="K103" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L103" s="2"/>
+    </row>
+    <row r="104" spans="1:12" ht="30">
+      <c r="A104" s="2">
+        <v>16387</v>
+      </c>
+      <c r="B104" s="3">
+        <v>1</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3"/>
+      <c r="H104" s="3"/>
+      <c r="I104" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J104" s="3"/>
+      <c r="K104" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L104" s="2"/>
+    </row>
+    <row r="105" spans="1:12" ht="30">
+      <c r="A105" s="2">
+        <v>16388</v>
+      </c>
+      <c r="B105" s="3">
+        <v>1</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3"/>
+      <c r="H105" s="3"/>
+      <c r="I105" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J105" s="3"/>
+      <c r="K105" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L105" s="2"/>
+    </row>
+    <row r="106" spans="1:12" ht="30">
+      <c r="A106" s="2">
+        <v>16389</v>
+      </c>
+      <c r="B106" s="3">
+        <v>1</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
+      <c r="H106" s="3"/>
+      <c r="I106" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J106" s="3"/>
+      <c r="K106" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L106" s="2"/>
+    </row>
+    <row r="107" spans="1:12" ht="30">
+      <c r="A107" s="2">
+        <v>16390</v>
+      </c>
+      <c r="B107" s="3">
+        <v>1</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
+      <c r="H107" s="3"/>
+      <c r="I107" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J107" s="3"/>
+      <c r="K107" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L107" s="2"/>
+    </row>
+    <row r="108" spans="1:12" ht="30">
+      <c r="A108" s="2">
+        <v>16391</v>
+      </c>
+      <c r="B108" s="3">
+        <v>1</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
+      <c r="H108" s="3"/>
+      <c r="I108" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J108" s="3"/>
+      <c r="K108" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L108" s="2"/>
+    </row>
+    <row r="109" spans="1:12" ht="30">
+      <c r="A109" s="2">
+        <v>16392</v>
+      </c>
+      <c r="B109" s="3">
+        <v>1</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3"/>
+      <c r="I109" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J109" s="3"/>
+      <c r="K109" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L109" s="2"/>
+    </row>
+    <row r="110" spans="1:12" ht="30">
+      <c r="A110" s="2">
+        <v>16393</v>
+      </c>
+      <c r="B110" s="3">
+        <v>1</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
+      <c r="H110" s="3"/>
+      <c r="I110" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J110" s="3"/>
+      <c r="K110" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L110" s="2"/>
+    </row>
+    <row r="111" spans="1:12" ht="30">
+      <c r="A111" s="2">
+        <v>16394</v>
+      </c>
+      <c r="B111" s="3">
+        <v>1</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3"/>
+      <c r="H111" s="3"/>
+      <c r="I111" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J111" s="3"/>
+      <c r="K111" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L111" s="2"/>
+    </row>
+    <row r="112" spans="1:12" ht="30">
+      <c r="A112" s="2">
+        <v>16395</v>
+      </c>
+      <c r="B112" s="3">
+        <v>1</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3"/>
+      <c r="H112" s="3"/>
+      <c r="I112" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J112" s="3"/>
+      <c r="K112" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L112" s="2"/>
+    </row>
+    <row r="113" spans="1:12" ht="30">
+      <c r="A113" s="2">
+        <v>16396</v>
+      </c>
+      <c r="B113" s="3">
+        <v>1</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3"/>
+      <c r="H113" s="3"/>
+      <c r="I113" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J113" s="3"/>
+      <c r="K113" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L113" s="2"/>
+    </row>
+    <row r="114" spans="1:12" ht="30">
+      <c r="A114" s="2">
+        <v>16397</v>
+      </c>
+      <c r="B114" s="3">
+        <v>1</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3"/>
+      <c r="H114" s="3"/>
+      <c r="I114" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J114" s="3"/>
+      <c r="K114" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L114" s="2"/>
+    </row>
+    <row r="115" spans="1:12" ht="30">
+      <c r="A115" s="2">
+        <v>16398</v>
+      </c>
+      <c r="B115" s="3">
+        <v>1</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3"/>
+      <c r="H115" s="3"/>
+      <c r="I115" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J115" s="3"/>
+      <c r="K115" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L115" s="2"/>
+    </row>
+    <row r="116" spans="1:12" ht="30">
+      <c r="A116" s="2">
+        <v>16399</v>
+      </c>
+      <c r="B116" s="3">
+        <v>1</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3"/>
+      <c r="H116" s="3"/>
+      <c r="I116" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J116" s="3"/>
+      <c r="K116" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L116" s="2"/>
+    </row>
+    <row r="117" spans="1:12" ht="30">
+      <c r="A117" s="2">
+        <v>16400</v>
+      </c>
+      <c r="B117" s="3">
+        <v>1</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3"/>
+      <c r="H117" s="3"/>
+      <c r="I117" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J117" s="3"/>
+      <c r="K117" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L117" s="2"/>
+    </row>
+    <row r="118" spans="1:12" ht="30">
+      <c r="A118" s="2">
+        <v>16401</v>
+      </c>
+      <c r="B118" s="3">
+        <v>1</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3"/>
+      <c r="H118" s="3"/>
+      <c r="I118" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J118" s="3"/>
+      <c r="K118" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L118" s="2"/>
+    </row>
+    <row r="119" spans="1:12" ht="30">
+      <c r="A119" s="2">
+        <v>16402</v>
+      </c>
+      <c r="B119" s="3">
+        <v>1</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F119" s="3"/>
+      <c r="G119" s="3"/>
+      <c r="H119" s="3"/>
+      <c r="I119" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J119" s="3"/>
+      <c r="K119" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L119" s="2"/>
+    </row>
+    <row r="120" spans="1:12" ht="30">
+      <c r="A120" s="2">
+        <v>16403</v>
+      </c>
+      <c r="B120" s="3">
+        <v>1</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F120" s="3"/>
+      <c r="G120" s="3"/>
+      <c r="H120" s="3"/>
+      <c r="I120" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J120" s="3"/>
+      <c r="K120" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L120" s="2"/>
+    </row>
+    <row r="121" spans="1:12" ht="30">
+      <c r="A121" s="2">
+        <v>16404</v>
+      </c>
+      <c r="B121" s="3">
+        <v>1</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F121" s="3"/>
+      <c r="G121" s="3"/>
+      <c r="H121" s="3"/>
+      <c r="I121" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J121" s="3"/>
+      <c r="K121" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L121" s="2"/>
+    </row>
+    <row r="122" spans="1:12" ht="30">
+      <c r="A122" s="2">
+        <v>16405</v>
+      </c>
+      <c r="B122" s="3">
+        <v>1</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F122" s="3"/>
+      <c r="G122" s="3"/>
+      <c r="H122" s="3"/>
+      <c r="I122" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J122" s="3"/>
+      <c r="K122" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L122" s="2"/>
+    </row>
+    <row r="123" spans="1:12" ht="30">
+      <c r="A123" s="2">
+        <v>16406</v>
+      </c>
+      <c r="B123" s="3">
+        <v>1</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F123" s="3"/>
+      <c r="G123" s="3"/>
+      <c r="H123" s="3"/>
+      <c r="I123" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J123" s="3"/>
+      <c r="K123" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L123" s="2"/>
+    </row>
+    <row r="124" spans="1:12" ht="30">
+      <c r="A124" s="2">
+        <v>16407</v>
+      </c>
+      <c r="B124" s="3">
+        <v>1</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F124" s="3"/>
+      <c r="G124" s="3"/>
+      <c r="H124" s="3"/>
+      <c r="I124" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J124" s="3"/>
+      <c r="K124" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L124" s="2"/>
+    </row>
+    <row r="125" spans="1:12" ht="30">
+      <c r="A125" s="2">
+        <v>16484</v>
+      </c>
+      <c r="B125" s="3">
+        <v>1</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F125" s="3"/>
+      <c r="G125" s="3"/>
+      <c r="H125" s="3"/>
+      <c r="I125" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="J125" s="3"/>
+      <c r="K125" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L125" s="2"/>
+    </row>
+    <row r="126" spans="1:12" ht="30">
+      <c r="A126" s="2">
+        <v>16485</v>
+      </c>
+      <c r="B126" s="3">
+        <v>1</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F126" s="3"/>
+      <c r="G126" s="3"/>
+      <c r="H126" s="3"/>
+      <c r="I126" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J126" s="3"/>
+      <c r="K126" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L126" s="2"/>
+    </row>
+    <row r="127" spans="1:12" ht="30">
+      <c r="A127" s="2">
+        <v>16486</v>
+      </c>
+      <c r="B127" s="3">
+        <v>1</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F127" s="3"/>
+      <c r="G127" s="3"/>
+      <c r="H127" s="3"/>
+      <c r="I127" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J127" s="3"/>
+      <c r="K127" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L127" s="2"/>
+    </row>
+    <row r="128" spans="1:12" ht="30">
+      <c r="A128" s="2">
+        <v>16487</v>
+      </c>
+      <c r="B128" s="3">
+        <v>1</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F128" s="3"/>
+      <c r="G128" s="3"/>
+      <c r="H128" s="3"/>
+      <c r="I128" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J128" s="3"/>
+      <c r="K128" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L128" s="2"/>
+    </row>
+    <row r="129" spans="1:12" ht="30">
+      <c r="A129" s="2">
+        <v>16488</v>
+      </c>
+      <c r="B129" s="3">
+        <v>1</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F129" s="3"/>
+      <c r="G129" s="3"/>
+      <c r="H129" s="3"/>
+      <c r="I129" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J129" s="3"/>
+      <c r="K129" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L129" s="2"/>
+    </row>
+    <row r="130" spans="1:12" ht="30">
+      <c r="A130" s="2">
+        <v>16489</v>
+      </c>
+      <c r="B130" s="3">
+        <v>1</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F130" s="3"/>
+      <c r="G130" s="3"/>
+      <c r="H130" s="3"/>
+      <c r="I130" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J130" s="3"/>
+      <c r="K130" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L130" s="2"/>
+    </row>
+    <row r="131" spans="1:12" ht="30">
+      <c r="A131" s="2">
+        <v>16490</v>
+      </c>
+      <c r="B131" s="3">
+        <v>1</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F131" s="3"/>
+      <c r="G131" s="3"/>
+      <c r="H131" s="3"/>
+      <c r="I131" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J131" s="3"/>
+      <c r="K131" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L131" s="2"/>
+    </row>
+    <row r="132" spans="1:12" ht="30">
+      <c r="A132" s="2">
+        <v>16491</v>
+      </c>
+      <c r="B132" s="3">
+        <v>1</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F132" s="3"/>
+      <c r="G132" s="3"/>
+      <c r="H132" s="3"/>
+      <c r="I132" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J132" s="3"/>
+      <c r="K132" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L132" s="2"/>
+    </row>
+    <row r="133" spans="1:12" ht="30">
+      <c r="A133" s="2">
+        <v>16492</v>
+      </c>
+      <c r="B133" s="3">
+        <v>1</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F133" s="3"/>
+      <c r="G133" s="3"/>
+      <c r="H133" s="3"/>
+      <c r="I133" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J133" s="3"/>
+      <c r="K133" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L133" s="2"/>
+    </row>
+    <row r="134" spans="1:12" ht="30">
+      <c r="A134" s="2">
+        <v>16493</v>
+      </c>
+      <c r="B134" s="3">
+        <v>1</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F134" s="3"/>
+      <c r="G134" s="3"/>
+      <c r="H134" s="3"/>
+      <c r="I134" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J134" s="3"/>
+      <c r="K134" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L134" s="2"/>
+    </row>
+    <row r="135" spans="1:12" ht="30">
+      <c r="A135" s="2">
+        <v>16494</v>
+      </c>
+      <c r="B135" s="3">
+        <v>1</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F135" s="3"/>
+      <c r="G135" s="3"/>
+      <c r="H135" s="3"/>
+      <c r="I135" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J135" s="3"/>
+      <c r="K135" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L135" s="2"/>
+    </row>
+    <row r="136" spans="1:12" ht="30">
+      <c r="A136" s="2">
+        <v>16495</v>
+      </c>
+      <c r="B136" s="3">
+        <v>1</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F136" s="3"/>
+      <c r="G136" s="3"/>
+      <c r="H136" s="3"/>
+      <c r="I136" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J136" s="3"/>
+      <c r="K136" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L136" s="2"/>
+    </row>
+    <row r="137" spans="1:12" ht="30">
+      <c r="A137" s="2">
+        <v>16496</v>
+      </c>
+      <c r="B137" s="3">
+        <v>1</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F137" s="3"/>
+      <c r="G137" s="3"/>
+      <c r="H137" s="3"/>
+      <c r="I137" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J137" s="3"/>
+      <c r="K137" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L137" s="2"/>
+    </row>
+    <row r="138" spans="1:12" ht="30">
+      <c r="A138" s="2">
+        <v>16497</v>
+      </c>
+      <c r="B138" s="3">
+        <v>1</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F138" s="3"/>
+      <c r="G138" s="3"/>
+      <c r="H138" s="3"/>
+      <c r="I138" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J138" s="3"/>
+      <c r="K138" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L138" s="2"/>
+    </row>
+    <row r="139" spans="1:12" ht="30">
+      <c r="A139" s="2">
+        <v>16498</v>
+      </c>
+      <c r="B139" s="3">
+        <v>1</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F139" s="3"/>
+      <c r="G139" s="3"/>
+      <c r="H139" s="3"/>
+      <c r="I139" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J139" s="3"/>
+      <c r="K139" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L139" s="2"/>
+    </row>
+    <row r="140" spans="1:12" ht="30">
+      <c r="A140" s="2">
+        <v>16499</v>
+      </c>
+      <c r="B140" s="3">
+        <v>1</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F140" s="3"/>
+      <c r="G140" s="3"/>
+      <c r="H140" s="3"/>
+      <c r="I140" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J140" s="3"/>
+      <c r="K140" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L140" s="2"/>
+    </row>
+    <row r="141" spans="1:12" ht="30">
+      <c r="A141" s="2">
+        <v>16500</v>
+      </c>
+      <c r="B141" s="3">
+        <v>1</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F141" s="3"/>
+      <c r="G141" s="3"/>
+      <c r="H141" s="3"/>
+      <c r="I141" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J141" s="3"/>
+      <c r="K141" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L141" s="2"/>
+    </row>
+    <row r="142" spans="1:12" ht="30">
+      <c r="A142" s="2">
+        <v>16501</v>
+      </c>
+      <c r="B142" s="3">
+        <v>1</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F142" s="3"/>
+      <c r="G142" s="3"/>
+      <c r="H142" s="3"/>
+      <c r="I142" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J142" s="3"/>
+      <c r="K142" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L142" s="2"/>
+    </row>
+    <row r="143" spans="1:12" ht="30">
+      <c r="A143" s="2">
+        <v>16502</v>
+      </c>
+      <c r="B143" s="3">
+        <v>1</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F143" s="3"/>
+      <c r="G143" s="3"/>
+      <c r="H143" s="3"/>
+      <c r="I143" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J143" s="3"/>
+      <c r="K143" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L143" s="2"/>
+    </row>
+    <row r="144" spans="1:12" ht="30">
+      <c r="A144" s="2">
+        <v>16503</v>
+      </c>
+      <c r="B144" s="3">
+        <v>1</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F144" s="3"/>
+      <c r="G144" s="3"/>
+      <c r="H144" s="3"/>
+      <c r="I144" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J144" s="3"/>
+      <c r="K144" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L144" s="2"/>
+    </row>
+    <row r="145" spans="1:12" ht="30">
+      <c r="A145" s="2">
+        <v>16504</v>
+      </c>
+      <c r="B145" s="3">
+        <v>1</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F145" s="3"/>
+      <c r="G145" s="3"/>
+      <c r="H145" s="3"/>
+      <c r="I145" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J145" s="3"/>
+      <c r="K145" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L145" s="2"/>
+    </row>
+    <row r="146" spans="1:12" ht="30">
+      <c r="A146" s="2">
+        <v>16505</v>
+      </c>
+      <c r="B146" s="3">
+        <v>1</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F146" s="3"/>
+      <c r="G146" s="3"/>
+      <c r="H146" s="3"/>
+      <c r="I146" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J146" s="3"/>
+      <c r="K146" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L146" s="2"/>
+    </row>
+    <row r="147" spans="1:12" ht="30">
+      <c r="A147" s="2">
+        <v>16506</v>
+      </c>
+      <c r="B147" s="3">
+        <v>1</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F147" s="3"/>
+      <c r="G147" s="3"/>
+      <c r="H147" s="3"/>
+      <c r="I147" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J147" s="3"/>
+      <c r="K147" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L147" s="2"/>
+    </row>
+    <row r="148" spans="1:12" ht="30">
+      <c r="A148" s="2">
+        <v>16507</v>
+      </c>
+      <c r="B148" s="3">
+        <v>1</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F148" s="3"/>
+      <c r="G148" s="3"/>
+      <c r="H148" s="3"/>
+      <c r="I148" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J148" s="3"/>
+      <c r="K148" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L148" s="2"/>
+    </row>
+    <row r="149" spans="1:12" ht="60">
+      <c r="A149" s="2">
+        <v>16784</v>
+      </c>
+      <c r="B149" s="3">
+        <v>50</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="F149" s="3">
+        <v>0</v>
+      </c>
+      <c r="G149" s="3">
+        <v>3</v>
+      </c>
+      <c r="H149" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="I149" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="J149" s="3"/>
+      <c r="K149" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="L149" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" ht="30">
+      <c r="A150" s="2">
+        <v>16785</v>
+      </c>
+      <c r="B150" s="3">
+        <v>2</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F150" s="3"/>
+      <c r="G150" s="3"/>
+      <c r="H150" s="3"/>
+      <c r="I150" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="J150" s="3"/>
+      <c r="K150" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L150" s="2"/>
+    </row>
+    <row r="151" spans="1:12" ht="30">
+      <c r="A151" s="2">
+        <v>16786</v>
+      </c>
+      <c r="B151" s="3">
+        <v>2</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F151" s="3"/>
+      <c r="G151" s="3"/>
+      <c r="H151" s="3"/>
+      <c r="I151" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J151" s="3"/>
+      <c r="K151" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L151" s="2"/>
+    </row>
+    <row r="152" spans="1:12" ht="30">
+      <c r="A152" s="2">
+        <v>16787</v>
+      </c>
+      <c r="B152" s="3">
+        <v>2</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F152" s="3"/>
+      <c r="G152" s="3"/>
+      <c r="H152" s="3"/>
+      <c r="I152" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J152" s="3"/>
+      <c r="K152" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L152" s="2"/>
+    </row>
+    <row r="153" spans="1:12" ht="30">
+      <c r="A153" s="2">
+        <v>16788</v>
+      </c>
+      <c r="B153" s="3">
+        <v>2</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F153" s="3"/>
+      <c r="G153" s="3"/>
+      <c r="H153" s="3"/>
+      <c r="I153" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J153" s="3"/>
+      <c r="K153" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L153" s="2"/>
+    </row>
+    <row r="154" spans="1:12" ht="30">
+      <c r="A154" s="2">
+        <v>16789</v>
+      </c>
+      <c r="B154" s="3">
+        <v>2</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F154" s="3"/>
+      <c r="G154" s="3"/>
+      <c r="H154" s="3"/>
+      <c r="I154" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J154" s="3"/>
+      <c r="K154" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L154" s="2"/>
+    </row>
+    <row r="155" spans="1:12" ht="30">
+      <c r="A155" s="2">
+        <v>16790</v>
+      </c>
+      <c r="B155" s="3">
+        <v>2</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F155" s="3"/>
+      <c r="G155" s="3"/>
+      <c r="H155" s="3"/>
+      <c r="I155" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J155" s="3"/>
+      <c r="K155" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L155" s="2"/>
+    </row>
+    <row r="156" spans="1:12" ht="30">
+      <c r="A156" s="2">
+        <v>16791</v>
+      </c>
+      <c r="B156" s="3">
+        <v>2</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F156" s="3"/>
+      <c r="G156" s="3"/>
+      <c r="H156" s="3"/>
+      <c r="I156" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J156" s="3"/>
+      <c r="K156" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L156" s="2"/>
+    </row>
+    <row r="157" spans="1:12" ht="30">
+      <c r="A157" s="2">
+        <v>16792</v>
+      </c>
+      <c r="B157" s="3">
+        <v>2</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F157" s="3"/>
+      <c r="G157" s="3"/>
+      <c r="H157" s="3"/>
+      <c r="I157" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J157" s="3"/>
+      <c r="K157" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L157" s="2"/>
+    </row>
+    <row r="158" spans="1:12" ht="30">
+      <c r="A158" s="2">
+        <v>16793</v>
+      </c>
+      <c r="B158" s="3">
+        <v>2</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F158" s="3"/>
+      <c r="G158" s="3"/>
+      <c r="H158" s="3"/>
+      <c r="I158" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J158" s="3"/>
+      <c r="K158" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L158" s="2"/>
+    </row>
+    <row r="159" spans="1:12" ht="30">
+      <c r="A159" s="2">
+        <v>16794</v>
+      </c>
+      <c r="B159" s="3">
+        <v>2</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F159" s="3"/>
+      <c r="G159" s="3"/>
+      <c r="H159" s="3"/>
+      <c r="I159" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J159" s="3"/>
+      <c r="K159" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L159" s="2"/>
+    </row>
+    <row r="160" spans="1:12" ht="30">
+      <c r="A160" s="2">
+        <v>16795</v>
+      </c>
+      <c r="B160" s="3">
+        <v>2</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F160" s="3"/>
+      <c r="G160" s="3"/>
+      <c r="H160" s="3"/>
+      <c r="I160" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J160" s="3"/>
+      <c r="K160" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L160" s="2"/>
+    </row>
+    <row r="161" spans="1:12" ht="30">
+      <c r="A161" s="2">
+        <v>16796</v>
+      </c>
+      <c r="B161" s="3">
+        <v>2</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F161" s="3"/>
+      <c r="G161" s="3"/>
+      <c r="H161" s="3"/>
+      <c r="I161" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J161" s="3"/>
+      <c r="K161" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L161" s="2"/>
+    </row>
+    <row r="162" spans="1:12" ht="30">
+      <c r="A162" s="2">
+        <v>16797</v>
+      </c>
+      <c r="B162" s="3">
+        <v>2</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F162" s="3"/>
+      <c r="G162" s="3"/>
+      <c r="H162" s="3"/>
+      <c r="I162" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J162" s="3"/>
+      <c r="K162" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L162" s="2"/>
+    </row>
+    <row r="163" spans="1:12" ht="30">
+      <c r="A163" s="2">
+        <v>16798</v>
+      </c>
+      <c r="B163" s="3">
+        <v>2</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F163" s="3"/>
+      <c r="G163" s="3"/>
+      <c r="H163" s="3"/>
+      <c r="I163" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J163" s="3"/>
+      <c r="K163" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L163" s="2"/>
+    </row>
+    <row r="164" spans="1:12" ht="30">
+      <c r="A164" s="2">
+        <v>16799</v>
+      </c>
+      <c r="B164" s="3">
+        <v>2</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F164" s="3"/>
+      <c r="G164" s="3"/>
+      <c r="H164" s="3"/>
+      <c r="I164" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J164" s="3"/>
+      <c r="K164" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L164" s="2"/>
+    </row>
+    <row r="165" spans="1:12" ht="30">
+      <c r="A165" s="2">
+        <v>16800</v>
+      </c>
+      <c r="B165" s="3">
+        <v>2</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F165" s="3"/>
+      <c r="G165" s="3"/>
+      <c r="H165" s="3"/>
+      <c r="I165" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J165" s="3"/>
+      <c r="K165" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L165" s="2"/>
+    </row>
+    <row r="166" spans="1:12" ht="30">
+      <c r="A166" s="2">
+        <v>16801</v>
+      </c>
+      <c r="B166" s="3">
+        <v>2</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F166" s="3"/>
+      <c r="G166" s="3"/>
+      <c r="H166" s="3"/>
+      <c r="I166" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J166" s="3"/>
+      <c r="K166" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L166" s="2"/>
+    </row>
+    <row r="167" spans="1:12" ht="30">
+      <c r="A167" s="2">
+        <v>16802</v>
+      </c>
+      <c r="B167" s="3">
+        <v>2</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F167" s="3"/>
+      <c r="G167" s="3"/>
+      <c r="H167" s="3"/>
+      <c r="I167" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J167" s="3"/>
+      <c r="K167" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L167" s="2"/>
+    </row>
+    <row r="168" spans="1:12" ht="30">
+      <c r="A168" s="2">
+        <v>16803</v>
+      </c>
+      <c r="B168" s="3">
+        <v>2</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F168" s="3"/>
+      <c r="G168" s="3"/>
+      <c r="H168" s="3"/>
+      <c r="I168" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J168" s="3"/>
+      <c r="K168" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L168" s="2"/>
+    </row>
+    <row r="169" spans="1:12" ht="30">
+      <c r="A169" s="2">
+        <v>16804</v>
+      </c>
+      <c r="B169" s="3">
+        <v>2</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F169" s="3"/>
+      <c r="G169" s="3"/>
+      <c r="H169" s="3"/>
+      <c r="I169" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J169" s="3"/>
+      <c r="K169" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L169" s="2"/>
+    </row>
+    <row r="170" spans="1:12" ht="30">
+      <c r="A170" s="2">
+        <v>16805</v>
+      </c>
+      <c r="B170" s="3">
+        <v>2</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F170" s="3"/>
+      <c r="G170" s="3"/>
+      <c r="H170" s="3"/>
+      <c r="I170" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J170" s="3"/>
+      <c r="K170" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L170" s="2"/>
+    </row>
+    <row r="171" spans="1:12" ht="30">
+      <c r="A171" s="2">
+        <v>16806</v>
+      </c>
+      <c r="B171" s="3">
+        <v>2</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F171" s="3"/>
+      <c r="G171" s="3"/>
+      <c r="H171" s="3"/>
+      <c r="I171" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J171" s="3"/>
+      <c r="K171" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L171" s="2"/>
+    </row>
+    <row r="172" spans="1:12" ht="30">
+      <c r="A172" s="2">
+        <v>16807</v>
+      </c>
+      <c r="B172" s="3">
+        <v>2</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F172" s="3"/>
+      <c r="G172" s="3"/>
+      <c r="H172" s="3"/>
+      <c r="I172" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J172" s="3"/>
+      <c r="K172" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L172" s="2"/>
+    </row>
+    <row r="173" spans="1:12" ht="30">
+      <c r="A173" s="2">
+        <v>16808</v>
+      </c>
+      <c r="B173" s="3">
+        <v>2</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E173" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F173" s="3"/>
+      <c r="G173" s="3"/>
+      <c r="H173" s="3"/>
+      <c r="I173" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J173" s="3"/>
+      <c r="K173" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L173" s="2"/>
+    </row>
+    <row r="174" spans="1:12" ht="120">
+      <c r="A174" s="2">
+        <v>4096</v>
+      </c>
+      <c r="B174" s="3">
+        <v>2</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="E174" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F174" s="3"/>
+      <c r="G174" s="3"/>
+      <c r="H174" s="3"/>
+      <c r="I174" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="J174" s="3"/>
+      <c r="K174" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L174" s="2"/>
+    </row>
+    <row r="175" spans="1:12" ht="30">
+      <c r="A175" s="2">
+        <v>4097</v>
+      </c>
+      <c r="B175" s="3">
+        <v>121</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="F175" s="3"/>
+      <c r="G175" s="3"/>
+      <c r="H175" s="3"/>
+      <c r="I175" s="3"/>
+      <c r="J175" s="3"/>
+      <c r="K175" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L175" s="2"/>
+    </row>
+    <row r="176" spans="1:12" ht="120">
+      <c r="A176" s="2">
+        <v>4098</v>
+      </c>
+      <c r="B176" s="3">
+        <v>2</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F176" s="3"/>
+      <c r="G176" s="3"/>
+      <c r="H176" s="3"/>
+      <c r="I176" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="J176" s="3"/>
+      <c r="K176" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L176" s="2"/>
+    </row>
+    <row r="177" spans="1:12" ht="45">
+      <c r="A177" s="2">
+        <v>18944</v>
+      </c>
+      <c r="B177" s="2">
+        <v>1</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="F177" s="2"/>
+      <c r="G177" s="2"/>
+      <c r="H177" s="2">
+        <v>0</v>
+      </c>
+      <c r="I177" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="J177" s="2"/>
+      <c r="K177" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="L177" s="2"/>
+    </row>
+    <row r="178" spans="1:12" ht="45">
+      <c r="A178" s="2">
+        <v>18946</v>
+      </c>
+      <c r="B178" s="2">
+        <v>1</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="F178" s="2"/>
+      <c r="G178" s="2"/>
+      <c r="H178" s="2">
+        <v>0</v>
+      </c>
+      <c r="I178" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="J178" s="2"/>
+      <c r="K178" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="L178" s="2"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Requirements.xlsx
+++ b/Requirements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://siemens-my.sharepoint.com/personal/malte-benedikt_schroeter_siemens_com/Documents/BA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{BE626DFE-17E3-4385-820A-E055A2D8DF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9B29EE0-D38F-4F1D-B759-2F0BA8708561}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="13_ncr:1_{BE626DFE-17E3-4385-820A-E055A2D8DF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{994C1A64-CD78-4B0E-9E1F-02F417DD50C7}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-1845" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{9AFE01D9-9480-4035-82AC-131C794FF07E}"/>
+    <workbookView xWindow="-28920" yWindow="-1860" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{9AFE01D9-9480-4035-82AC-131C794FF07E}"/>
   </bookViews>
   <sheets>
     <sheet name="Funktional" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="595">
   <si>
     <t>ID</t>
   </si>
@@ -1920,9 +1920,6 @@
     <t>Anfrage QModMaster</t>
   </si>
   <si>
-    <t xml:space="preserve">Blinkmodus tut nicht, Qmodmaster fragt 96 statt 97 ab trotz 1 offset, funktioniert. </t>
-  </si>
-  <si>
     <t>Anfrage Desigo ohne Offset</t>
   </si>
   <si>
@@ -1930,6 +1927,69 @@
   </si>
   <si>
     <t>weird wegen mischung ascii und uint, funktioniert im Moment noch nicht</t>
+  </si>
+  <si>
+    <t>blink_mode</t>
+  </si>
+  <si>
+    <t>asset_identifier</t>
+  </si>
+  <si>
+    <t>Write kann nur Bool und Zahlen, Strings gehen nicht :(</t>
+  </si>
+  <si>
+    <t>installation_location</t>
+  </si>
+  <si>
+    <t>installation_date</t>
+  </si>
+  <si>
+    <t>gibt 0 aus, sinnvoll?</t>
+  </si>
+  <si>
+    <t>redundant</t>
+  </si>
+  <si>
+    <t>rated_residual_current</t>
+  </si>
+  <si>
+    <t>ECPD gibt es nur mit 1Pol+N</t>
+  </si>
+  <si>
+    <t>ist immer typ F</t>
+  </si>
+  <si>
+    <t>ist immer 75 kA</t>
+  </si>
+  <si>
+    <t>ist immer 230, keine Ahnung ob in anderen Märkten bspw 120V Versionen vertrieben werden</t>
+  </si>
+  <si>
+    <t>immer rechts</t>
+  </si>
+  <si>
+    <t>immer verfügbar</t>
+  </si>
+  <si>
+    <t>Prüfen mit Last!</t>
+  </si>
+  <si>
+    <t>illegal data adress</t>
+  </si>
+  <si>
+    <t>operating_hours_with_load_current_alarm_on_off(_write)</t>
+  </si>
+  <si>
+    <t>min_current_operating_houzrs_counter(_write)</t>
+  </si>
+  <si>
+    <t>threshold_operating_hours_with_load_current(_write), write tut noch nicht</t>
+  </si>
+  <si>
+    <t>operating_hours_alarm_on_off(_write)</t>
+  </si>
+  <si>
+    <t>threshold_operating_hours(_write), write tut noch nicht</t>
   </si>
 </sst>
 </file>
@@ -2051,7 +2111,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2072,6 +2132,55 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>44823</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>247620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>44744</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>223329</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Grafik 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{852A987B-FD88-F47E-F29E-0221266F803E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16136470" y="1581120"/>
+          <a:ext cx="2285921" cy="1499709"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -8757,9 +8866,9 @@
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.42578125" customWidth="1"/>
     <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
     <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="57" bestFit="1" customWidth="1"/>
@@ -8962,7 +9071,7 @@
       </c>
       <c r="L6" s="2"/>
       <c r="M6" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -8992,6 +9101,9 @@
         <v>187</v>
       </c>
       <c r="L7" s="2"/>
+      <c r="M7" t="s">
+        <v>575</v>
+      </c>
     </row>
     <row r="8" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
@@ -9020,6 +9132,9 @@
         <v>187</v>
       </c>
       <c r="L8" s="2"/>
+      <c r="M8" t="s">
+        <v>577</v>
+      </c>
     </row>
     <row r="9" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
@@ -9048,6 +9163,9 @@
         <v>187</v>
       </c>
       <c r="L9" s="2"/>
+      <c r="M9" t="s">
+        <v>578</v>
+      </c>
     </row>
     <row r="10" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
@@ -9150,6 +9268,9 @@
         <v>195</v>
       </c>
       <c r="L12" s="2"/>
+      <c r="M12" t="s">
+        <v>574</v>
+      </c>
     </row>
     <row r="13" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
@@ -9184,6 +9305,9 @@
         <v>153</v>
       </c>
       <c r="L13" s="2"/>
+      <c r="M13" t="s">
+        <v>579</v>
+      </c>
     </row>
     <row r="14" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
@@ -9218,6 +9342,9 @@
         <v>153</v>
       </c>
       <c r="L14" s="2"/>
+      <c r="M14" t="s">
+        <v>580</v>
+      </c>
     </row>
     <row r="15" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
@@ -9246,6 +9373,9 @@
         <v>153</v>
       </c>
       <c r="L15" s="2"/>
+      <c r="M15" t="s">
+        <v>581</v>
+      </c>
     </row>
     <row r="16" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
@@ -9280,8 +9410,11 @@
         <v>153</v>
       </c>
       <c r="L16" s="2"/>
-    </row>
-    <row r="17" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="M16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>139</v>
       </c>
@@ -9314,8 +9447,11 @@
         <v>153</v>
       </c>
       <c r="L17" s="2"/>
-    </row>
-    <row r="18" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="M17" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>140</v>
       </c>
@@ -9342,8 +9478,11 @@
         <v>153</v>
       </c>
       <c r="L18" s="2"/>
-    </row>
-    <row r="19" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="M18" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>142</v>
       </c>
@@ -9370,8 +9509,11 @@
         <v>153</v>
       </c>
       <c r="L19" s="2"/>
-    </row>
-    <row r="20" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="M19" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>143</v>
       </c>
@@ -9404,8 +9546,11 @@
         <v>153</v>
       </c>
       <c r="L20" s="2"/>
-    </row>
-    <row r="21" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="M20" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>144</v>
       </c>
@@ -9438,8 +9583,11 @@
         <v>153</v>
       </c>
       <c r="L21" s="2"/>
-    </row>
-    <row r="22" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="M21" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>145</v>
       </c>
@@ -9472,8 +9620,11 @@
         <v>187</v>
       </c>
       <c r="L22" s="2"/>
-    </row>
-    <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="M22" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>170</v>
       </c>
@@ -9500,8 +9651,11 @@
         <v>153</v>
       </c>
       <c r="L23" s="2"/>
-    </row>
-    <row r="24" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="M23" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>174</v>
       </c>
@@ -9530,8 +9684,11 @@
         <v>153</v>
       </c>
       <c r="L24" s="2"/>
-    </row>
-    <row r="25" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="M24" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>2566</v>
       </c>
@@ -9564,8 +9721,11 @@
         <v>187</v>
       </c>
       <c r="L25" s="2"/>
-    </row>
-    <row r="26" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="M25" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>2567</v>
       </c>
@@ -9598,8 +9758,11 @@
         <v>187</v>
       </c>
       <c r="L26" s="2"/>
-    </row>
-    <row r="27" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="M26" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>2568</v>
       </c>
@@ -9632,8 +9795,11 @@
         <v>187</v>
       </c>
       <c r="L27" s="2"/>
-    </row>
-    <row r="28" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="M27" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>2582</v>
       </c>
@@ -9666,8 +9832,11 @@
         <v>187</v>
       </c>
       <c r="L28" s="2"/>
-    </row>
-    <row r="29" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="M28" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>2583</v>
       </c>
@@ -9700,8 +9869,11 @@
         <v>187</v>
       </c>
       <c r="L29" s="2"/>
-    </row>
-    <row r="30" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="M29" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>2595</v>
       </c>
@@ -9735,7 +9907,7 @@
       </c>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>2596</v>
       </c>
@@ -9767,7 +9939,7 @@
       </c>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>2604</v>
       </c>
@@ -10223,7 +10395,7 @@
       </c>
       <c r="L45" s="2"/>
     </row>
-    <row r="46" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>3597</v>
       </c>
@@ -10257,7 +10429,7 @@
       </c>
       <c r="L46" s="2"/>
     </row>
-    <row r="47" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>3598</v>
       </c>
@@ -10291,7 +10463,7 @@
       </c>
       <c r="L47" s="2"/>
     </row>
-    <row r="48" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>3599</v>
       </c>
@@ -10327,7 +10499,7 @@
       </c>
       <c r="L48" s="2"/>
     </row>
-    <row r="49" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>3601</v>
       </c>
@@ -10361,7 +10533,7 @@
       </c>
       <c r="L49" s="2"/>
     </row>
-    <row r="50" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>3607</v>
       </c>
@@ -10395,7 +10567,7 @@
       </c>
       <c r="L50" s="2"/>
     </row>
-    <row r="51" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>3608</v>
       </c>
@@ -10429,7 +10601,7 @@
       </c>
       <c r="L51" s="2"/>
     </row>
-    <row r="52" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>3610</v>
       </c>
@@ -10463,7 +10635,7 @@
       </c>
       <c r="L52" s="2"/>
     </row>
-    <row r="53" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>3616</v>
       </c>
@@ -10497,7 +10669,7 @@
       </c>
       <c r="L53" s="2"/>
     </row>
-    <row r="54" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>3617</v>
       </c>
@@ -10531,7 +10703,7 @@
       </c>
       <c r="L54" s="2"/>
     </row>
-    <row r="55" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>3619</v>
       </c>
@@ -10565,7 +10737,7 @@
       </c>
       <c r="L55" s="2"/>
     </row>
-    <row r="56" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>3625</v>
       </c>
@@ -10599,7 +10771,7 @@
       </c>
       <c r="L56" s="2"/>
     </row>
-    <row r="57" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>3626</v>
       </c>
@@ -10635,7 +10807,7 @@
       </c>
       <c r="L57" s="2"/>
     </row>
-    <row r="58" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>3628</v>
       </c>
@@ -10669,7 +10841,7 @@
       </c>
       <c r="L58" s="2"/>
     </row>
-    <row r="59" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>3634</v>
       </c>
@@ -10703,7 +10875,7 @@
       </c>
       <c r="L59" s="2"/>
     </row>
-    <row r="60" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>3635</v>
       </c>
@@ -10737,7 +10909,7 @@
       </c>
       <c r="L60" s="2"/>
     </row>
-    <row r="61" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>3637</v>
       </c>
@@ -10771,7 +10943,7 @@
       </c>
       <c r="L61" s="2"/>
     </row>
-    <row r="62" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>3643</v>
       </c>
@@ -10805,7 +10977,7 @@
       </c>
       <c r="L62" s="2"/>
     </row>
-    <row r="63" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>3644</v>
       </c>
@@ -10839,7 +11011,7 @@
       </c>
       <c r="L63" s="2"/>
     </row>
-    <row r="64" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>3646</v>
       </c>
@@ -10873,7 +11045,7 @@
       </c>
       <c r="L64" s="2"/>
     </row>
-    <row r="65" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>3652</v>
       </c>
@@ -10907,7 +11079,7 @@
       </c>
       <c r="L65" s="2"/>
     </row>
-    <row r="66" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>3653</v>
       </c>
@@ -10941,7 +11113,7 @@
       </c>
       <c r="L66" s="2"/>
     </row>
-    <row r="67" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>3655</v>
       </c>
@@ -10975,7 +11147,7 @@
       </c>
       <c r="L67" s="2"/>
     </row>
-    <row r="68" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>3661</v>
       </c>
@@ -11009,7 +11181,7 @@
       </c>
       <c r="L68" s="2"/>
     </row>
-    <row r="69" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>3662</v>
       </c>
@@ -11043,7 +11215,7 @@
       </c>
       <c r="L69" s="2"/>
     </row>
-    <row r="70" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>3664</v>
       </c>
@@ -11129,7 +11301,7 @@
       </c>
       <c r="L72" s="2"/>
     </row>
-    <row r="73" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>3675</v>
       </c>
@@ -11163,7 +11335,7 @@
       </c>
       <c r="L73" s="2"/>
     </row>
-    <row r="74" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>3692</v>
       </c>
@@ -11189,7 +11361,7 @@
         <v>223</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>470</v>
+        <v>439</v>
       </c>
       <c r="J74" s="3"/>
       <c r="K74" s="3" t="s">
@@ -14383,6 +14555,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -14411,7 +14584,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -14421,12 +14594,12 @@
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
   </sheetData>

--- a/Requirements.xlsx
+++ b/Requirements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://siemens-my.sharepoint.com/personal/malte-benedikt_schroeter_siemens_com/Documents/BA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3997" documentId="13_ncr:1_{BE626DFE-17E3-4385-820A-E055A2D8DF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B75F60E-6674-4828-9D54-62824FE12247}"/>
+  <xr:revisionPtr revIDLastSave="4004" documentId="13_ncr:1_{BE626DFE-17E3-4385-820A-E055A2D8DF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0262D64-1273-4F98-BCB8-0E10557AC108}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="5" xr2:uid="{9AFE01D9-9480-4035-82AC-131C794FF07E}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3160" uniqueCount="1035">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3161" uniqueCount="1036">
   <si>
     <t>ID</t>
   </si>
@@ -3344,10 +3344,13 @@
     <t>[Anpassung 06.08.2026] Nicht in den Katalog aufgenommen: Die Nachvollziehbarkeit von Änderungen an geschützten Geräteparametern (UC-12) wird nicht als Anforderung geführt. Die ID bleibt reserviert.</t>
   </si>
   <si>
-    <t>Kann man schreiben von Daten mit einer Registerabfrage validieren?</t>
-  </si>
-  <si>
-    <t>Thema  Polling-Geschwindigkeit?</t>
+    <t>In Kontakt mit EP Product Support (Stefan Baier, Sebastian Winklmann-Roehricht)</t>
+  </si>
+  <si>
+    <t>Arbeit: Analyse solider Anfang, mache ich bis zum Urlaub fertig</t>
+  </si>
+  <si>
+    <t>Objektmodell: bereits mit Andreas Ulmer im Kontakt, manche Dinge funktionieren noch nicht, teilweise liegt es am Gerät, das gilt es jetzt aber noch final herauszufinden</t>
   </si>
 </sst>
 </file>
@@ -3971,6 +3974,50 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>562904</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>19638</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Grafik 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9677014A-30CC-6D7E-99DA-42FCB45BB090}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6162675" y="16573500"/>
+          <a:ext cx="6658904" cy="4210638"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -17140,6 +17187,11 @@
         <v>1034</v>
       </c>
     </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1035</v>
+      </c>
+    </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>560</v>

--- a/Requirements.xlsx
+++ b/Requirements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://siemens-my.sharepoint.com/personal/malte-benedikt_schroeter_siemens_com/Documents/BA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4005" documentId="13_ncr:1_{BE626DFE-17E3-4385-820A-E055A2D8DF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC2A6305-33B6-4086-8EC9-3F3D1F979EE5}"/>
+  <xr:revisionPtr revIDLastSave="4008" documentId="13_ncr:1_{BE626DFE-17E3-4385-820A-E055A2D8DF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{862F0123-41EC-4C67-A1D9-0A64F92C0FC3}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="31530" yWindow="3030" windowWidth="21600" windowHeight="11295" xr2:uid="{9AFE01D9-9480-4035-82AC-131C794FF07E}"/>
+    <workbookView minimized="1" xWindow="5685" yWindow="4005" windowWidth="21600" windowHeight="11295" xr2:uid="{9AFE01D9-9480-4035-82AC-131C794FF07E}"/>
   </bookViews>
   <sheets>
     <sheet name="Funktional" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3161" uniqueCount="1036">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3162" uniqueCount="1037">
   <si>
     <t>ID</t>
   </si>
@@ -3350,7 +3350,10 @@
     <t>Objektmodell: bereits mit Andreas Ulmer im Kontakt, manche Dinge funktionieren noch nicht, teilweise liegt es am Gerät, das gilt es jetzt aber noch final herauszufinden</t>
   </si>
   <si>
-    <t>y</t>
+    <t xml:space="preserve">Anfrage elektronisches Schalten funktioniert mit </t>
+  </si>
+  <si>
+    <t>Die Kommunikation muss zyklisch erfolgen und Datenpunkte zyklisch übermitteln. Die Frequenz soll konfigurierbar sein.</t>
   </si>
 </sst>
 </file>
@@ -4018,6 +4021,50 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>113</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>44316</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>37784</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Grafik 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7DA5BCB-34E4-E4DF-D0DB-C4B4EE2EBFCD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6158962" y="21891356"/>
+          <a:ext cx="14460968" cy="2362530"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4371,12 +4418,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C3" s="1"/>
     </row>
@@ -17166,7 +17213,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07379391-C6A2-4A97-9B7F-58688E513D59}">
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="92.42578125" customWidth="1"/>
@@ -17210,6 +17257,11 @@
     <row r="62" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>1015</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B113" t="s">
+        <v>1035</v>
       </c>
     </row>
   </sheetData>

--- a/Requirements.xlsx
+++ b/Requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://siemens-my.sharepoint.com/personal/malte-benedikt_schroeter_siemens_com/Documents/BA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4012" documentId="13_ncr:1_{BE626DFE-17E3-4385-820A-E055A2D8DF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D3784B1-E90A-4A37-BCA6-0CABC44A9992}"/>
+  <xr:revisionPtr revIDLastSave="4546" documentId="13_ncr:1_{BE626DFE-17E3-4385-820A-E055A2D8DF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B29399F-DBED-452F-96FA-4666E7F9FCBB}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{9AFE01D9-9480-4035-82AC-131C794FF07E}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="5" activeTab="8" xr2:uid="{9AFE01D9-9480-4035-82AC-131C794FF07E}"/>
   </bookViews>
   <sheets>
     <sheet name="Funktional" sheetId="1" r:id="rId1"/>
@@ -21,10 +21,12 @@
     <sheet name="Themen" sheetId="10" r:id="rId6"/>
     <sheet name="Datenpunkte Powercenter" sheetId="14" r:id="rId7"/>
     <sheet name="Datenpunkte ECPD" sheetId="16" r:id="rId8"/>
+    <sheet name="Implementierung ECPD" sheetId="17" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Datenpunkte ECPD'!$A$6:$K$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Datenpunkte ECPD'!$A$6:$K$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Datenpunkte Powercenter'!$A$6:$K$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Implementierung ECPD'!$A$9:$N$46</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -50,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3163" uniqueCount="1038">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3617" uniqueCount="1199">
   <si>
     <t>ID</t>
   </si>
@@ -2639,9 +2641,6 @@
     <t xml:space="preserve">   reduziert</t>
   </si>
   <si>
-    <t>905 Datenpunkte</t>
-  </si>
-  <si>
     <t xml:space="preserve">   davon im schnellen Zyklus (5–10 s)</t>
   </si>
   <si>
@@ -2753,9 +2752,6 @@
     <t>Ändert sich ausschließlich bei einer Auslösung. Dient als Trigger, um gezielt das Trip-Log mit Zeitstempel und Messwert zum Auslösezeitpunkt nachzulesen, statt Logs dauerhaft zu pollen.</t>
   </si>
   <si>
-    <t>2   NICHT AUFGENOMMEN – bewusst ausgeschlossen (171 von 208 Datenpunkten)</t>
-  </si>
-  <si>
     <t>Gruppen 'Diagnose Parameter' (14), 'Parameter' (36) und 'RCM Parameter' (11): je Alarm die Trias Ein/Aus + Grenzwert + Hysterese, dazu Mittelungszeiträume (3586, 3597), Extremwert-Reset (3675) und Zeitkonfiguration (3700, 3701)</t>
   </si>
   <si>
@@ -2765,12 +2761,6 @@
     <t>Redundante bzw. abgeleitete Messwerte</t>
   </si>
   <si>
-    <t>3074 (Mittelwert Temperatur), 3078 (Mittelwert Strom), 3084 (Netzfrequenz), 3088 (Scheinleistung), 3090 (Blindleistung), 3114 (Sperrzustand), 3115/3116 (Status Ein-/Ausgänge), 3138 (Lokale Zeitinformation), 3338 (Differenzstrom Grundfrequenz)</t>
-  </si>
-  <si>
-    <t>Mittelwerte bildet Desigo CC im Archiv selbst. Die Netzfrequenz ist ein netzweiter Wert und muss nicht 24-fach je Powercenter erfasst werden. Schein- und Blindleistung sind aus Wirkleistung und Leistungsfaktor ableitbar. Die digitalen Ein-/Ausgänge sind nur relevant, wenn die AUX-Funktion (Reg. 5419/5421) tatsächlich beschaltet ist – dann gezielt nachrüsten.</t>
-  </si>
-  <si>
     <t>Hochrechnung 24 Endgeräte – unreduziert</t>
   </si>
   <si>
@@ -3248,9 +3238,6 @@
     <t>Bit 14 und 17 gehören zum AFDD (5SV6 COM AFDD, Gerätevariante 4). Der ECPD ist Gerätevariante 11 und besitzt keinerlei AFDD-Register – die Bits können bei ihm nicht gesetzt werden. Bit 21 bis 23 sind in der Bitfeld-Beschreibung nicht vergeben.</t>
   </si>
   <si>
-    <t>37 Register  (Reduktion um 82 %)</t>
-  </si>
-  <si>
     <t>abgeleitete Alarm-Datenpunkte aus Register 2560</t>
   </si>
   <si>
@@ -3258,12 +3245,6 @@
   </si>
   <si>
     <t>Datenpunkte je ECPD in Desigo CC gesamt</t>
-  </si>
-  <si>
-    <t>64  (37 Register + 27 Alarmbits)</t>
-  </si>
-  <si>
-    <t>888 Register bzw. 1.536 Datenpunkte inkl. Alarmbits</t>
   </si>
   <si>
     <t>Alle 27 im Bitfeld von Register 2560 für den ECPD belegten Alarme sind aufgenommen. Nicht enthalten sind Bit 14 und 17 (gehören zum AFDD, nicht zum ECPD) sowie Bit 21 bis 23 (in der Bitfeld-Beschreibung nicht vergeben) – siehe letzte Zeile in Abschnitt 2.</t>
@@ -3357,6 +3338,510 @@
   </si>
   <si>
     <t>[Anpassung 24.08.2026] Auf die Desktop-Variante präzisiert. Die mobile Anwendung erwies sich in Vorversuchen vor Beginn der Bearbeitung als nicht verlässlich, da das Hinzufügen des Powercenters wiederholt fehlschlug und ein bereits hinzugefügtes ECPD häufig nicht mehr angezeigt wurde. Zudem riet die fachliche Betreuung (Andreas Ulmer, Siemens AG) von ihrem Einsatz ab.</t>
+  </si>
+  <si>
+    <t>line_frequency</t>
+  </si>
+  <si>
+    <t>FP32 / Hz</t>
+  </si>
+  <si>
+    <t>Aufgenommen zur Erfuellung von FA-03, das die Sichtbarkeit saemtlicher Messwerte fordert. Ergaenzt die Spannung um die zweite Kenngroesse der Netzqualitaet. Der Wert ist ueber die Abgaenge eines Strangs hinweg nahezu identisch, fuer die Auswertung genuegt daher ein Geraet je Strang.</t>
+  </si>
+  <si>
+    <t>2   NICHT AUFGENOMMEN – bewusst ausgeschlossen (170 von 208 Datenpunkten)</t>
+  </si>
+  <si>
+    <t>3074 (Mittelwert Temperatur), 3078 (Mittelwert Strom), 3088 (Scheinleistung), 3090 (Blindleistung), 3114 (Sperrzustand), 3115/3116 (Status Ein-/Ausgänge), 3138 (Lokale Zeitinformation), 3338 (Differenzstrom Grundfrequenz)</t>
+  </si>
+  <si>
+    <t>Mittelwerte bildet Desigo CC im Archiv selbst. Schein- und Blindleistung sind aus Wirkleistung und Leistungsfaktor ableitbar. Die digitalen Ein-/Ausgänge sind nur relevant, wenn die AUX-Funktion (Reg. 5419/5421) tatsächlich beschaltet ist – dann gezielt nachrüsten.</t>
+  </si>
+  <si>
+    <t>38 Register  (Reduktion um 82 %)</t>
+  </si>
+  <si>
+    <t>65  (38 Register + 27 Alarmbits)</t>
+  </si>
+  <si>
+    <t>912 Register bzw. 1.560 Datenpunkte inkl. Alarmbits</t>
+  </si>
+  <si>
+    <t>929 Datenpunkte</t>
+  </si>
+  <si>
+    <t>Umgesetzte Datenpunkte des ECPD im Objektmodell für Desigo CC</t>
+  </si>
+  <si>
+    <t>Grundlage ist das Blatt „Datenpunkte ECPD". Jenes Blatt begründet die Auswahl, dieses Blatt gibt wieder, was in der Typbeschreibung des PDE tatsächlich angelegt ist.</t>
+  </si>
+  <si>
+    <t>Abweichung 1: Register 22 (Software Version) ist wegen gemischter ASCII- und uint-Kodierung nicht dekodierbar und entfällt nach K-06. Damit 37 statt 38 Register.</t>
+  </si>
+  <si>
+    <t>Abweichung 2: Das Bitfeld aus Register 2560 lässt sich nicht in 27 Einzeldatenpunkte zerlegen. Weder der Datentyp BLOB mit BOOL-Messpunkten noch BOOLEAN mit Subindex wird beim Import in Desigo CC angenommen. Der Alarmzustand wird deshalb als eine Zahl übertragen, die Bitbelegung ist im Blatt „Datenpunkte ECPD" dokumentiert.</t>
+  </si>
+  <si>
+    <t>Ergebnis: 37 Register und 37 Datenpunkte je ECPD, zuvor waren 38 Register und 65 Datenpunkte vorgesehen. Je Strang mit 24 Endgeräten sind es 905 Register statt 929.</t>
+  </si>
+  <si>
+    <t>Der Funktionscode ist nicht Teil der Registerkarte. Gelesen wird mit FC3, geschrieben mit FC6. Diese Zuordnung ist am Modell zu bestätigen.</t>
+  </si>
+  <si>
+    <t>Richtung: R lesend, W fest bedeutet Write Value mit im PDE hinterlegtem Wert, W dynamisch bedeutet Write Value mit erst in Desigo CC vergebenem Wert.</t>
+  </si>
+  <si>
+    <t>Variablenname (Property im PDE)</t>
+  </si>
+  <si>
+    <t>Gruppe im PDE</t>
+  </si>
+  <si>
+    <t>Länge (Reg.)</t>
+  </si>
+  <si>
+    <t>Richtung</t>
+  </si>
+  <si>
+    <t>Datentyp im Modell</t>
+  </si>
+  <si>
+    <t>Faktor</t>
+  </si>
+  <si>
+    <t>Werte und Kodierung</t>
+  </si>
+  <si>
+    <t>Anwendungsfall</t>
+  </si>
+  <si>
+    <t>Voraussetzung in Powerconfig</t>
+  </si>
+  <si>
+    <t>Anmerkung</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>2560</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>UINT 4 Byte</t>
+  </si>
+  <si>
+    <t>Bitfeld, Bitbelegung siehe Blatt „Datenpunkte ECPD"</t>
+  </si>
+  <si>
+    <t>UC-03</t>
+  </si>
+  <si>
+    <t>13 der 27 Alarmbits sind ab Werk deaktiviert und müssen eingeschaltet werden</t>
+  </si>
+  <si>
+    <t>Eine Zerlegung in 27 Einzeldatenpunkte ist nicht möglich, siehe Kopfzeilen</t>
+  </si>
+  <si>
+    <t>3110</t>
+  </si>
+  <si>
+    <t>UINT 2 Byte</t>
+  </si>
+  <si>
+    <t>0=unbekannt, 1=AUS, 2=EIN, 3=Ausgelöst, 4=Ausgelöst und Hebel blockiert, 5=Standby, 6=Standby tripped</t>
+  </si>
+  <si>
+    <t>UC-02</t>
+  </si>
+  <si>
+    <t>Kernfrage des Betreibers, trennt planmäßiges Ausschalten vom Auslösen</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>3113</t>
+  </si>
+  <si>
+    <t>0=ON, 1=ON Fehler, 2=STBY, 3=STBY Fehler, 4=OFF, 5=OFF Fehler</t>
+  </si>
+  <si>
+    <t>UC-06</t>
+  </si>
+  <si>
+    <t>Lesende Hälfte zu command_electronic_switching</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>0=IDLE, 1=Offline, 2=Verbinden, 3=Verbunden</t>
+  </si>
+  <si>
+    <t>UC-04</t>
+  </si>
+  <si>
+    <t>n ist der Index des Endgeräts am Powercenter und läuft von 1 bis 24</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>2622</t>
+  </si>
+  <si>
+    <t>INT 2 Byte</t>
+  </si>
+  <si>
+    <t>Macht eine sich verschlechternde Funkstrecke sichtbar, bevor sie abreißt</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Value / Current</t>
+  </si>
+  <si>
+    <t>3076</t>
+  </si>
+  <si>
+    <t>FLOAT 4 Byte</t>
+  </si>
+  <si>
+    <t>UC-02, UC-05</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>3080</t>
+  </si>
+  <si>
+    <t>UC-05</t>
+  </si>
+  <si>
+    <t>Vom Gerät gespeicherter Extremwert, nach K-05 nicht ableitbar</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Value / Voltage</t>
+  </si>
+  <si>
+    <t>3082</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Value / Frequency</t>
+  </si>
+  <si>
+    <t>3084</t>
+  </si>
+  <si>
+    <t>Je Strang bis zu 24-fach erfasst, die Doppelung ist bewusst in Kauf genommen</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Value / Power</t>
+  </si>
+  <si>
+    <t>3086</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Value / Power Factor</t>
+  </si>
+  <si>
+    <t>3092</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Value / Temperature</t>
+  </si>
+  <si>
+    <t>3072</t>
+  </si>
+  <si>
+    <t>UC-02, UC-08</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Value / Others</t>
+  </si>
+  <si>
+    <t>3330</t>
+  </si>
+  <si>
+    <t>UC-08</t>
+  </si>
+  <si>
+    <t>Ablage noch offen, das Werkzeug hat keine passende Untergruppe für den Differenzstrom</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Value / Counter</t>
+  </si>
+  <si>
+    <t>2578</t>
+  </si>
+  <si>
+    <t>FLOAT 8 Byte</t>
+  </si>
+  <si>
+    <t>In Sekunden übernommen, der Faktor 1/3600 ist mit drei Dezimalstellen nicht darstellbar</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>2562</t>
+  </si>
+  <si>
+    <t>wie Nr. 14</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>2593</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>2602</t>
+  </si>
+  <si>
+    <t>Eine Häufung weist auf ein Problem der Anlage hin, nicht auf einen Gerätefehler</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>2624</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>2673</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>2726</t>
+  </si>
+  <si>
+    <t>Macht Eingriffe sichtbar, ohne die geschützten Parameter selbst abzubilden</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>2679</t>
+  </si>
+  <si>
+    <t>0=unbekannt, 1=erfolgreich, 2=fehlgeschlagen, 3=nicht durchgeführt, 4=abgebrochen</t>
+  </si>
+  <si>
+    <t>UC-07</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>2635</t>
+  </si>
+  <si>
+    <t>0 bis 12, Fehlercode</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>2680</t>
+  </si>
+  <si>
+    <t>0=unbekannt, 1=ARD aktiv</t>
+  </si>
+  <si>
+    <t>Erklärt dem Betreiber, weshalb ein Abgang selbsttätig zurückgekehrt ist</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Command</t>
+  </si>
+  <si>
+    <t>3693</t>
+  </si>
+  <si>
+    <t>W dynamisch</t>
+  </si>
+  <si>
+    <t>0=STANDBY, 1=ON</t>
+  </si>
+  <si>
+    <t>Fernschalten über Modbus muss freigeschaltet sein</t>
+  </si>
+  <si>
+    <t>Ohne diese Freischaltung weist das Gerät den Schreibzugriff ab</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>3692</t>
+  </si>
+  <si>
+    <t>W fest</t>
+  </si>
+  <si>
+    <t>fester Wert 0x0815</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>5225</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>2678</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>0=stopp, 1=10 s blinken</t>
+  </si>
+  <si>
+    <t>UC-09</t>
+  </si>
+  <si>
+    <t>Ein Servicetechniker findet im Verteiler bis zu 24 baugleiche Geräte vor</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>3694</t>
+  </si>
+  <si>
+    <t>Nicht rückstellbar, ein Register für das mechanische Einschalten existiert nicht</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>STRING</t>
+  </si>
+  <si>
+    <t>UC-10</t>
+  </si>
+  <si>
+    <t>Wird in Powerconfig gesetzt</t>
+  </si>
+  <si>
+    <t>Im Modell nur lesend, Zeichenketten sind nicht beschreibbar</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>wie Nr. 30</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>0=nicht vergeben, 1=L1, 2=L2, 3=L3</t>
+  </si>
+  <si>
+    <t>Wird bei der Inbetriebnahme vergeben</t>
+  </si>
+  <si>
+    <t>Erlaubt die Betrachtung der Schieflast über alle Abgänge eines Verteilers</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>5376</t>
+  </si>
+  <si>
+    <t>0,001</t>
+  </si>
+  <si>
+    <t>16000 entspricht 16 A</t>
+  </si>
+  <si>
+    <t>Zwingend erforderlich, da die Stromgrenzwerte in Prozent des Nennstroms angegeben sind</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>5425</t>
+  </si>
+  <si>
+    <t>0=inaktiv, 1=aktiv</t>
+  </si>
+  <si>
+    <t>Diagnosemerkmal, erklärt einen wirkungslos bleibenden Schaltbefehl</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>3671</t>
+  </si>
+  <si>
+    <t>UC-03, UC-08</t>
+  </si>
+  <si>
+    <t>Zeigt eine hinzugekommene Auslösung an, auch wenn der Alarm noch ansteht</t>
   </si>
 </sst>
 </file>
@@ -3444,7 +3929,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3517,6 +4002,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -3571,7 +4062,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3735,6 +4226,29 @@
     </xf>
     <xf numFmtId="49" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4426,7 +4940,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
       <c r="C3" s="1"/>
     </row>
@@ -4466,10 +4980,10 @@
         <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1015</v>
+        <v>1008</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1023</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="150" x14ac:dyDescent="0.25">
@@ -4478,7 +4992,7 @@
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
-        <v>1029</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -4486,10 +5000,10 @@
         <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1021</v>
+        <v>1014</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1022</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -4508,10 +5022,10 @@
         <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1024</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="90" x14ac:dyDescent="0.25">
@@ -4520,7 +5034,7 @@
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
-        <v>1030</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -4678,10 +5192,10 @@
         <v>45</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1025</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -4957,10 +5471,10 @@
         <v>81</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1036</v>
+        <v>1029</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1037</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.25">
@@ -4997,10 +5511,10 @@
         <v>89</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1018</v>
+        <v>1011</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1026</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="90" x14ac:dyDescent="0.25">
@@ -5008,10 +5522,10 @@
         <v>90</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1019</v>
+        <v>1012</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1027</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -5019,10 +5533,10 @@
         <v>91</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1020</v>
+        <v>1013</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1028</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -17231,17 +17745,17 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1031</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1032</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1033</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -17261,12 +17775,12 @@
     </row>
     <row r="62" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>1014</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="113" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>1034</v>
+        <v>1027</v>
       </c>
     </row>
   </sheetData>
@@ -17305,7 +17819,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -17325,10 +17839,10 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>584</v>
@@ -17360,10 +17874,10 @@
     </row>
     <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="50" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="C7" s="21">
         <v>1</v>
@@ -17395,10 +17909,10 @@
     </row>
     <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="C8" s="23">
         <v>2</v>
@@ -17430,10 +17944,10 @@
     </row>
     <row r="9" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A9" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="C9" s="23">
         <v>3</v>
@@ -17465,10 +17979,10 @@
     </row>
     <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="50" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="C10" s="21">
         <v>4</v>
@@ -17500,10 +18014,10 @@
     </row>
     <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="50" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B11" s="42" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="C11" s="21">
         <v>5</v>
@@ -17535,10 +18049,10 @@
     </row>
     <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="50" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B12" s="42" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="C12" s="21">
         <v>6</v>
@@ -17570,10 +18084,10 @@
     </row>
     <row r="13" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A13" s="52" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B13" s="44" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="C13" s="27">
         <v>7</v>
@@ -17605,10 +18119,10 @@
     </row>
     <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="52" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B14" s="44" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="C14" s="27">
         <v>8</v>
@@ -17640,10 +18154,10 @@
     </row>
     <row r="15" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A15" s="53" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B15" s="45" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="C15" s="25">
         <v>9</v>
@@ -17675,10 +18189,10 @@
     </row>
     <row r="16" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A16" s="53" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B16" s="45" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C16" s="25">
         <v>10</v>
@@ -17710,10 +18224,10 @@
     </row>
     <row r="17" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A17" s="53" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B17" s="45" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="C17" s="25">
         <v>11</v>
@@ -17745,10 +18259,10 @@
     </row>
     <row r="18" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A18" s="53" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B18" s="45" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="C18" s="25">
         <v>12</v>
@@ -17780,10 +18294,10 @@
     </row>
     <row r="19" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="53" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B19" s="45" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="C19" s="25">
         <v>13</v>
@@ -17815,10 +18329,10 @@
     </row>
     <row r="20" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="54" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B20" s="46" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="C20" s="33">
         <v>14</v>
@@ -17850,7 +18364,7 @@
     </row>
     <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="55" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B21" s="47" t="s">
         <v>563</v>
@@ -17885,7 +18399,7 @@
     </row>
     <row r="22" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A22" s="55" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B22" s="47" t="s">
         <v>564</v>
@@ -17920,7 +18434,7 @@
     </row>
     <row r="23" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A23" s="55" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B23" s="47" t="s">
         <v>555</v>
@@ -17955,7 +18469,7 @@
     </row>
     <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="55" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B24" s="47" t="s">
         <v>554</v>
@@ -17985,15 +18499,15 @@
         <v>638</v>
       </c>
       <c r="K24" s="32" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A25" s="55" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B25" s="47" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="C25" s="31">
         <v>19</v>
@@ -18465,7 +18979,7 @@
       </c>
       <c r="D50" s="15"/>
       <c r="E50" s="38" t="s">
-        <v>799</v>
+        <v>1040</v>
       </c>
       <c r="F50" s="15"/>
       <c r="G50" s="15"/>
@@ -18478,11 +18992,11 @@
       <c r="A51" s="15"/>
       <c r="B51" s="15"/>
       <c r="C51" s="38" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D51" s="15"/>
       <c r="E51" s="38" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="F51" s="15"/>
       <c r="G51" s="15"/>
@@ -18523,7 +19037,7 @@
       <c r="A54" s="15"/>
       <c r="B54" s="15"/>
       <c r="C54" s="18" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D54" s="15"/>
       <c r="E54" s="15"/>
@@ -18538,7 +19052,7 @@
       <c r="A55" s="15"/>
       <c r="B55" s="15"/>
       <c r="C55" s="18" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D55" s="15"/>
       <c r="E55" s="15"/>
@@ -18553,7 +19067,7 @@
       <c r="A56" s="15"/>
       <c r="B56" s="15"/>
       <c r="C56" s="18" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="D56" s="15"/>
       <c r="E56" s="15"/>
@@ -18568,7 +19082,7 @@
       <c r="A57" s="15"/>
       <c r="B57" s="15"/>
       <c r="C57" s="18" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D57" s="15"/>
       <c r="E57" s="15"/>
@@ -18583,7 +19097,7 @@
       <c r="A58" s="15"/>
       <c r="B58" s="15"/>
       <c r="C58" s="18" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D58" s="15"/>
       <c r="E58" s="15"/>
@@ -18598,7 +19112,7 @@
       <c r="A59" s="15"/>
       <c r="B59" s="15"/>
       <c r="C59" s="18" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D59" s="15"/>
       <c r="E59" s="15"/>
@@ -18629,7 +19143,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB8EDA5B-3056-480A-AA43-F447F580627A}">
-  <dimension ref="A1:K111"/>
+  <dimension ref="A1:K112"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -18652,12 +19166,12 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -18677,10 +19191,10 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>584</v>
@@ -18712,10 +19226,10 @@
     </row>
     <row r="7" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="50" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="C7" s="21">
         <v>1</v>
@@ -18747,10 +19261,10 @@
     </row>
     <row r="8" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="50" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="C8" s="21">
         <v>2</v>
@@ -18768,7 +19282,7 @@
         <v>143</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="I8" s="21" t="s">
         <v>593</v>
@@ -18777,15 +19291,15 @@
         <v>594</v>
       </c>
       <c r="K8" s="22" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="50" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="C9" s="21">
         <v>3</v>
@@ -18797,30 +19311,30 @@
         <v>3113</v>
       </c>
       <c r="F9" s="22" t="s">
+        <v>809</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="H9" s="22" t="s">
         <v>810</v>
       </c>
-      <c r="G9" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="H9" s="22" t="s">
+      <c r="I9" s="21" t="s">
         <v>811</v>
-      </c>
-      <c r="I9" s="21" t="s">
-        <v>812</v>
       </c>
       <c r="J9" s="21" t="s">
         <v>594</v>
       </c>
       <c r="K9" s="22" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="50" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="C10" s="21">
         <v>4</v>
@@ -18847,15 +19361,15 @@
         <v>594</v>
       </c>
       <c r="K10" s="22" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="50" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B11" s="42" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="C11" s="21">
         <v>5</v>
@@ -18873,7 +19387,7 @@
         <v>143</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="I11" s="21" t="s">
         <v>747</v>
@@ -18882,15 +19396,15 @@
         <v>594</v>
       </c>
       <c r="K11" s="22" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="C12" s="23">
         <v>6</v>
@@ -18899,10 +19413,10 @@
         <v>600</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="G12" s="23" t="s">
         <v>143</v>
@@ -18917,15 +19431,15 @@
         <v>594</v>
       </c>
       <c r="K12" s="24" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="C13" s="23">
         <v>7</v>
@@ -18952,15 +19466,15 @@
         <v>594</v>
       </c>
       <c r="K13" s="24" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="C14" s="23">
         <v>8</v>
@@ -18969,10 +19483,10 @@
         <v>600</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="G14" s="23" t="s">
         <v>143</v>
@@ -18987,15 +19501,15 @@
         <v>594</v>
       </c>
       <c r="K14" s="24" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B15" s="43" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="C15" s="23">
         <v>9</v>
@@ -19004,10 +19518,10 @@
         <v>600</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="G15" s="23" t="s">
         <v>143</v>
@@ -19022,15 +19536,15 @@
         <v>594</v>
       </c>
       <c r="K15" s="24" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="C16" s="23">
         <v>10</v>
@@ -19042,7 +19556,7 @@
         <v>739</v>
       </c>
       <c r="F16" s="43" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="G16" s="23" t="s">
         <v>143</v>
@@ -19057,15 +19571,15 @@
         <v>594</v>
       </c>
       <c r="K16" s="24" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="C17" s="23">
         <v>11</v>
@@ -19074,10 +19588,10 @@
         <v>600</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="G17" s="23" t="s">
         <v>143</v>
@@ -19092,15 +19606,15 @@
         <v>594</v>
       </c>
       <c r="K17" s="24" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B18" s="43" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="C18" s="23">
         <v>12</v>
@@ -19109,10 +19623,10 @@
         <v>600</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="G18" s="23" t="s">
         <v>143</v>
@@ -19127,15 +19641,15 @@
         <v>594</v>
       </c>
       <c r="K18" s="24" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="C19" s="23">
         <v>13</v>
@@ -19144,10 +19658,10 @@
         <v>600</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="F19" s="24" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="G19" s="23" t="s">
         <v>143</v>
@@ -19162,15 +19676,15 @@
         <v>594</v>
       </c>
       <c r="K19" s="24" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A20" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="C20" s="23">
         <v>14</v>
@@ -19179,10 +19693,10 @@
         <v>600</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="F20" s="24" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="G20" s="23" t="s">
         <v>143</v>
@@ -19197,15 +19711,15 @@
         <v>594</v>
       </c>
       <c r="K20" s="24" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="C21" s="23">
         <v>15</v>
@@ -19214,10 +19728,10 @@
         <v>600</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="F21" s="24" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="G21" s="23" t="s">
         <v>143</v>
@@ -19232,15 +19746,15 @@
         <v>594</v>
       </c>
       <c r="K21" s="24" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A22" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="C22" s="23">
         <v>16</v>
@@ -19249,10 +19763,10 @@
         <v>600</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="F22" s="24" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="G22" s="23" t="s">
         <v>143</v>
@@ -19267,15 +19781,15 @@
         <v>594</v>
       </c>
       <c r="K22" s="24" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B23" s="43" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="C23" s="23">
         <v>17</v>
@@ -19284,10 +19798,10 @@
         <v>600</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="F23" s="24" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="G23" s="23" t="s">
         <v>143</v>
@@ -19302,15 +19816,15 @@
         <v>594</v>
       </c>
       <c r="K23" s="24" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B24" s="43" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="C24" s="23">
         <v>18</v>
@@ -19319,10 +19833,10 @@
         <v>600</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="F24" s="24" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="G24" s="23" t="s">
         <v>143</v>
@@ -19337,15 +19851,15 @@
         <v>594</v>
       </c>
       <c r="K24" s="24" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C25" s="23">
         <v>19</v>
@@ -19372,15 +19886,15 @@
         <v>594</v>
       </c>
       <c r="K25" s="24" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="C26" s="23">
         <v>20</v>
@@ -19407,15 +19921,15 @@
         <v>594</v>
       </c>
       <c r="K26" s="24" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="C27" s="23">
         <v>21</v>
@@ -19424,10 +19938,10 @@
         <v>600</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="F27" s="24" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="G27" s="23" t="s">
         <v>143</v>
@@ -19442,15 +19956,15 @@
         <v>594</v>
       </c>
       <c r="K27" s="24" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="C28" s="23">
         <v>22</v>
@@ -19477,15 +19991,15 @@
         <v>594</v>
       </c>
       <c r="K28" s="24" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A29" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B29" s="43" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="C29" s="23">
         <v>23</v>
@@ -19512,15 +20026,15 @@
         <v>594</v>
       </c>
       <c r="K29" s="24" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="C30" s="23">
         <v>24</v>
@@ -19547,15 +20061,15 @@
         <v>594</v>
       </c>
       <c r="K30" s="24" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B31" s="43" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="C31" s="23">
         <v>25</v>
@@ -19582,15 +20096,15 @@
         <v>594</v>
       </c>
       <c r="K31" s="24" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B32" s="43" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="C32" s="23">
         <v>26</v>
@@ -19617,15 +20131,15 @@
         <v>594</v>
       </c>
       <c r="K32" s="24" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B33" s="43" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="C33" s="23">
         <v>27</v>
@@ -19634,10 +20148,10 @@
         <v>600</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="F33" s="24" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="G33" s="23" t="s">
         <v>143</v>
@@ -19652,15 +20166,15 @@
         <v>594</v>
       </c>
       <c r="K33" s="24" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B34" s="43" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="C34" s="23">
         <v>28</v>
@@ -19669,10 +20183,10 @@
         <v>600</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="F34" s="24" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="G34" s="23" t="s">
         <v>143</v>
@@ -19687,15 +20201,15 @@
         <v>594</v>
       </c>
       <c r="K34" s="24" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B35" s="43" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="C35" s="23">
         <v>29</v>
@@ -19722,15 +20236,15 @@
         <v>594</v>
       </c>
       <c r="K35" s="24" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A36" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B36" s="43" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="C36" s="23">
         <v>30</v>
@@ -19757,15 +20271,15 @@
         <v>594</v>
       </c>
       <c r="K36" s="24" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B37" s="43" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="C37" s="23">
         <v>31</v>
@@ -19774,10 +20288,10 @@
         <v>600</v>
       </c>
       <c r="E37" s="24" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="F37" s="24" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="G37" s="23" t="s">
         <v>143</v>
@@ -19792,15 +20306,15 @@
         <v>594</v>
       </c>
       <c r="K37" s="24" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A38" s="51" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B38" s="43" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="C38" s="23">
         <v>32</v>
@@ -19827,15 +20341,15 @@
         <v>594</v>
       </c>
       <c r="K38" s="24" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="53" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B39" s="45" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="C39" s="25">
         <v>33</v>
@@ -19867,10 +20381,10 @@
     </row>
     <row r="40" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="53" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B40" s="45" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="C40" s="25">
         <v>34</v>
@@ -19897,15 +20411,15 @@
         <v>157</v>
       </c>
       <c r="K40" s="26" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A41" s="53" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B41" s="45" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="C41" s="25">
         <v>35</v>
@@ -19935,12 +20449,12 @@
         <v>628</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A42" s="53" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B42" s="45" t="s">
-        <v>887</v>
+        <v>1031</v>
       </c>
       <c r="C42" s="25">
         <v>36</v>
@@ -19949,33 +20463,33 @@
         <v>623</v>
       </c>
       <c r="E42" s="26">
-        <v>3086</v>
+        <v>3084</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="G42" s="25" t="s">
         <v>143</v>
       </c>
       <c r="H42" s="26" t="s">
-        <v>629</v>
+        <v>1032</v>
       </c>
       <c r="I42" s="25" t="s">
-        <v>625</v>
+        <v>747</v>
       </c>
       <c r="J42" s="25" t="s">
         <v>157</v>
       </c>
       <c r="K42" s="26" t="s">
-        <v>818</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="53" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B43" s="45" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="C43" s="25">
         <v>37</v>
@@ -19984,33 +20498,33 @@
         <v>623</v>
       </c>
       <c r="E43" s="26">
-        <v>3092</v>
+        <v>3086</v>
       </c>
       <c r="F43" s="26" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="G43" s="25" t="s">
         <v>143</v>
       </c>
       <c r="H43" s="26" t="s">
-        <v>159</v>
+        <v>629</v>
       </c>
       <c r="I43" s="25" t="s">
-        <v>747</v>
+        <v>625</v>
       </c>
       <c r="J43" s="25" t="s">
         <v>157</v>
       </c>
       <c r="K43" s="26" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="53" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B44" s="45" t="s">
-        <v>856</v>
+        <v>884</v>
       </c>
       <c r="C44" s="25">
         <v>38</v>
@@ -20019,33 +20533,33 @@
         <v>623</v>
       </c>
       <c r="E44" s="26">
-        <v>3072</v>
+        <v>3092</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>158</v>
+        <v>720</v>
       </c>
       <c r="G44" s="25" t="s">
         <v>143</v>
       </c>
       <c r="H44" s="26" t="s">
-        <v>630</v>
+        <v>159</v>
       </c>
       <c r="I44" s="25" t="s">
-        <v>625</v>
+        <v>747</v>
       </c>
       <c r="J44" s="25" t="s">
         <v>157</v>
       </c>
       <c r="K44" s="26" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="53" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B45" s="45" t="s">
-        <v>889</v>
+        <v>852</v>
       </c>
       <c r="C45" s="25">
         <v>39</v>
@@ -20054,16 +20568,16 @@
         <v>623</v>
       </c>
       <c r="E45" s="26">
-        <v>3330</v>
+        <v>3072</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>820</v>
+        <v>158</v>
       </c>
       <c r="G45" s="25" t="s">
         <v>143</v>
       </c>
       <c r="H45" s="26" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="I45" s="25" t="s">
         <v>625</v>
@@ -20072,50 +20586,50 @@
         <v>157</v>
       </c>
       <c r="K45" s="26" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="52" t="s">
-        <v>910</v>
-      </c>
-      <c r="B46" s="44" t="s">
-        <v>859</v>
-      </c>
-      <c r="C46" s="27">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A46" s="53" t="s">
+        <v>906</v>
+      </c>
+      <c r="B46" s="45" t="s">
+        <v>885</v>
+      </c>
+      <c r="C46" s="25">
         <v>40</v>
       </c>
-      <c r="D46" s="27" t="s">
-        <v>632</v>
-      </c>
-      <c r="E46" s="28">
-        <v>2578</v>
-      </c>
-      <c r="F46" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="G46" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="H46" s="28" t="s">
-        <v>633</v>
-      </c>
-      <c r="I46" s="27" t="s">
-        <v>634</v>
-      </c>
-      <c r="J46" s="27" t="s">
-        <v>635</v>
-      </c>
-      <c r="K46" s="28" t="s">
-        <v>985</v>
+      <c r="D46" s="25" t="s">
+        <v>623</v>
+      </c>
+      <c r="E46" s="26">
+        <v>3330</v>
+      </c>
+      <c r="F46" s="26" t="s">
+        <v>819</v>
+      </c>
+      <c r="G46" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="H46" s="26" t="s">
+        <v>624</v>
+      </c>
+      <c r="I46" s="25" t="s">
+        <v>625</v>
+      </c>
+      <c r="J46" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="K46" s="26" t="s">
+        <v>980</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="52" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B47" s="44" t="s">
-        <v>890</v>
+        <v>855</v>
       </c>
       <c r="C47" s="27">
         <v>41</v>
@@ -20124,10 +20638,10 @@
         <v>632</v>
       </c>
       <c r="E47" s="28">
-        <v>2562</v>
+        <v>2578</v>
       </c>
       <c r="F47" s="28" t="s">
-        <v>695</v>
+        <v>144</v>
       </c>
       <c r="G47" s="27" t="s">
         <v>143</v>
@@ -20142,15 +20656,15 @@
         <v>635</v>
       </c>
       <c r="K47" s="28" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="52" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B48" s="44" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="C48" s="27">
         <v>42</v>
@@ -20159,16 +20673,16 @@
         <v>632</v>
       </c>
       <c r="E48" s="28">
-        <v>2593</v>
+        <v>2562</v>
       </c>
       <c r="F48" s="28" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="G48" s="27" t="s">
         <v>143</v>
       </c>
       <c r="H48" s="28" t="s">
-        <v>159</v>
+        <v>633</v>
       </c>
       <c r="I48" s="27" t="s">
         <v>634</v>
@@ -20177,15 +20691,15 @@
         <v>635</v>
       </c>
       <c r="K48" s="28" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A49" s="52" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B49" s="44" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="C49" s="27">
         <v>43</v>
@@ -20194,10 +20708,10 @@
         <v>632</v>
       </c>
       <c r="E49" s="28">
-        <v>2602</v>
+        <v>2593</v>
       </c>
       <c r="F49" s="28" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="G49" s="27" t="s">
         <v>143</v>
@@ -20212,15 +20726,15 @@
         <v>635</v>
       </c>
       <c r="K49" s="28" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="52" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B50" s="44" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="C50" s="27">
         <v>44</v>
@@ -20229,10 +20743,10 @@
         <v>632</v>
       </c>
       <c r="E50" s="28">
-        <v>2624</v>
+        <v>2602</v>
       </c>
       <c r="F50" s="28" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="G50" s="27" t="s">
         <v>143</v>
@@ -20247,15 +20761,15 @@
         <v>635</v>
       </c>
       <c r="K50" s="28" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="52" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B51" s="44" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="C51" s="27">
         <v>45</v>
@@ -20264,10 +20778,10 @@
         <v>632</v>
       </c>
       <c r="E51" s="28">
-        <v>2673</v>
+        <v>2624</v>
       </c>
       <c r="F51" s="28" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="G51" s="27" t="s">
         <v>143</v>
@@ -20282,15 +20796,15 @@
         <v>635</v>
       </c>
       <c r="K51" s="28" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="52" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B52" s="44" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="C52" s="27">
         <v>46</v>
@@ -20299,16 +20813,16 @@
         <v>632</v>
       </c>
       <c r="E52" s="28">
-        <v>2726</v>
+        <v>2673</v>
       </c>
       <c r="F52" s="28" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="G52" s="27" t="s">
         <v>143</v>
       </c>
       <c r="H52" s="28" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I52" s="27" t="s">
         <v>634</v>
@@ -20317,173 +20831,173 @@
         <v>635</v>
       </c>
       <c r="K52" s="28" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A53" s="56" t="s">
-        <v>910</v>
-      </c>
-      <c r="B53" s="48" t="s">
-        <v>896</v>
-      </c>
-      <c r="C53" s="40">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="52" t="s">
+        <v>906</v>
+      </c>
+      <c r="B53" s="44" t="s">
+        <v>891</v>
+      </c>
+      <c r="C53" s="27">
         <v>47</v>
       </c>
-      <c r="D53" s="40" t="s">
-        <v>822</v>
-      </c>
-      <c r="E53" s="41">
-        <v>2679</v>
-      </c>
-      <c r="F53" s="41" t="s">
-        <v>703</v>
-      </c>
-      <c r="G53" s="40" t="s">
-        <v>143</v>
-      </c>
-      <c r="H53" s="41" t="s">
-        <v>823</v>
-      </c>
-      <c r="I53" s="40" t="s">
-        <v>824</v>
-      </c>
-      <c r="J53" s="40" t="s">
-        <v>825</v>
-      </c>
-      <c r="K53" s="41" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="D53" s="27" t="s">
+        <v>632</v>
+      </c>
+      <c r="E53" s="28">
+        <v>2726</v>
+      </c>
+      <c r="F53" s="28" t="s">
+        <v>707</v>
+      </c>
+      <c r="G53" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="H53" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="I53" s="27" t="s">
+        <v>634</v>
+      </c>
+      <c r="J53" s="27" t="s">
+        <v>635</v>
+      </c>
+      <c r="K53" s="28" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="56" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B54" s="48" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="C54" s="40">
         <v>48</v>
       </c>
       <c r="D54" s="40" t="s">
+        <v>821</v>
+      </c>
+      <c r="E54" s="41">
+        <v>2679</v>
+      </c>
+      <c r="F54" s="41" t="s">
+        <v>703</v>
+      </c>
+      <c r="G54" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="H54" s="41" t="s">
         <v>822</v>
       </c>
-      <c r="E54" s="41">
-        <v>2635</v>
-      </c>
-      <c r="F54" s="41" t="s">
-        <v>700</v>
-      </c>
-      <c r="G54" s="40" t="s">
-        <v>143</v>
-      </c>
-      <c r="H54" s="41" t="s">
-        <v>826</v>
-      </c>
       <c r="I54" s="40" t="s">
+        <v>823</v>
+      </c>
+      <c r="J54" s="40" t="s">
         <v>824</v>
       </c>
-      <c r="J54" s="40" t="s">
-        <v>825</v>
-      </c>
       <c r="K54" s="41" t="s">
-        <v>827</v>
+        <v>987</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="56" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B55" s="48" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="C55" s="40">
         <v>49</v>
       </c>
       <c r="D55" s="40" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E55" s="41">
+        <v>2635</v>
+      </c>
+      <c r="F55" s="41" t="s">
+        <v>700</v>
+      </c>
+      <c r="G55" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="H55" s="41" t="s">
+        <v>825</v>
+      </c>
+      <c r="I55" s="40" t="s">
+        <v>823</v>
+      </c>
+      <c r="J55" s="40" t="s">
+        <v>824</v>
+      </c>
+      <c r="K55" s="41" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A56" s="56" t="s">
+        <v>906</v>
+      </c>
+      <c r="B56" s="48" t="s">
+        <v>894</v>
+      </c>
+      <c r="C56" s="40">
+        <v>50</v>
+      </c>
+      <c r="D56" s="40" t="s">
+        <v>821</v>
+      </c>
+      <c r="E56" s="41">
         <v>2680</v>
       </c>
-      <c r="F55" s="41" t="s">
+      <c r="F56" s="41" t="s">
+        <v>827</v>
+      </c>
+      <c r="G56" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="H56" s="41" t="s">
         <v>828</v>
       </c>
-      <c r="G55" s="40" t="s">
-        <v>143</v>
-      </c>
-      <c r="H55" s="41" t="s">
-        <v>829</v>
-      </c>
-      <c r="I55" s="40" t="s">
+      <c r="I56" s="40" t="s">
         <v>747</v>
       </c>
-      <c r="J55" s="40" t="s">
+      <c r="J56" s="40" t="s">
         <v>594</v>
       </c>
-      <c r="K55" s="41" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A56" s="57" t="s">
-        <v>910</v>
-      </c>
-      <c r="B56" s="49" t="s">
-        <v>899</v>
-      </c>
-      <c r="C56" s="29">
-        <v>50</v>
-      </c>
-      <c r="D56" s="29" t="s">
-        <v>830</v>
-      </c>
-      <c r="E56" s="30">
-        <v>3693</v>
-      </c>
-      <c r="F56" s="30" t="s">
-        <v>461</v>
-      </c>
-      <c r="G56" s="29" t="s">
-        <v>185</v>
-      </c>
-      <c r="H56" s="30" t="s">
-        <v>636</v>
-      </c>
-      <c r="I56" s="29" t="s">
-        <v>637</v>
-      </c>
-      <c r="J56" s="29" t="s">
-        <v>638</v>
-      </c>
-      <c r="K56" s="30" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K56" s="41" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="57" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B57" s="49" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="C57" s="29">
         <v>51</v>
       </c>
       <c r="D57" s="29" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E57" s="30">
-        <v>3692</v>
+        <v>3693</v>
       </c>
       <c r="F57" s="30" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="G57" s="29" t="s">
         <v>185</v>
       </c>
       <c r="H57" s="30" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="I57" s="29" t="s">
         <v>637</v>
@@ -20492,27 +21006,27 @@
         <v>638</v>
       </c>
       <c r="K57" s="30" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A58" s="57" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B58" s="49" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="C58" s="29">
         <v>52</v>
       </c>
       <c r="D58" s="29" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E58" s="30">
-        <v>5225</v>
+        <v>3692</v>
       </c>
       <c r="F58" s="30" t="s">
-        <v>641</v>
+        <v>459</v>
       </c>
       <c r="G58" s="29" t="s">
         <v>185</v>
@@ -20527,27 +21041,27 @@
         <v>638</v>
       </c>
       <c r="K58" s="30" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="57" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B59" s="49" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="C59" s="29">
         <v>53</v>
       </c>
       <c r="D59" s="29" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E59" s="30">
-        <v>2678</v>
+        <v>5225</v>
       </c>
       <c r="F59" s="30" t="s">
-        <v>428</v>
+        <v>641</v>
       </c>
       <c r="G59" s="29" t="s">
         <v>185</v>
@@ -20562,33 +21076,33 @@
         <v>638</v>
       </c>
       <c r="K59" s="30" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A60" s="57" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B60" s="49" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="C60" s="29">
         <v>54</v>
       </c>
       <c r="D60" s="29" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E60" s="30">
-        <v>97</v>
+        <v>2678</v>
       </c>
       <c r="F60" s="30" t="s">
-        <v>642</v>
+        <v>428</v>
       </c>
       <c r="G60" s="29" t="s">
         <v>185</v>
       </c>
       <c r="H60" s="30" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="I60" s="29" t="s">
         <v>637</v>
@@ -20597,33 +21111,33 @@
         <v>638</v>
       </c>
       <c r="K60" s="30" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="57" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B61" s="49" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="C61" s="29">
         <v>55</v>
       </c>
       <c r="D61" s="29" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E61" s="30">
-        <v>3694</v>
+        <v>97</v>
       </c>
       <c r="F61" s="30" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="G61" s="29" t="s">
         <v>185</v>
       </c>
       <c r="H61" s="30" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="I61" s="29" t="s">
         <v>637</v>
@@ -20632,68 +21146,68 @@
         <v>638</v>
       </c>
       <c r="K61" s="30" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A62" s="57" t="s">
+        <v>906</v>
+      </c>
+      <c r="B62" s="49" t="s">
+        <v>900</v>
+      </c>
+      <c r="C62" s="29">
+        <v>56</v>
+      </c>
+      <c r="D62" s="29" t="s">
+        <v>829</v>
+      </c>
+      <c r="E62" s="30">
+        <v>3694</v>
+      </c>
+      <c r="F62" s="30" t="s">
+        <v>644</v>
+      </c>
+      <c r="G62" s="29" t="s">
+        <v>185</v>
+      </c>
+      <c r="H62" s="30" t="s">
+        <v>639</v>
+      </c>
+      <c r="I62" s="29" t="s">
+        <v>637</v>
+      </c>
+      <c r="J62" s="29" t="s">
+        <v>638</v>
+      </c>
+      <c r="K62" s="30" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A62" s="55" t="s">
-        <v>910</v>
-      </c>
-      <c r="B62" s="47" t="s">
+    <row r="63" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63" s="55" t="s">
+        <v>906</v>
+      </c>
+      <c r="B63" s="47" t="s">
         <v>563</v>
-      </c>
-      <c r="C62" s="31">
-        <v>56</v>
-      </c>
-      <c r="D62" s="31" t="s">
-        <v>833</v>
-      </c>
-      <c r="E62" s="32">
-        <v>29</v>
-      </c>
-      <c r="F62" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="G62" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="H62" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="I62" s="31" t="s">
-        <v>647</v>
-      </c>
-      <c r="J62" s="31" t="s">
-        <v>638</v>
-      </c>
-      <c r="K62" s="32" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A63" s="55" t="s">
-        <v>910</v>
-      </c>
-      <c r="B63" s="47" t="s">
-        <v>564</v>
       </c>
       <c r="C63" s="31">
         <v>57</v>
       </c>
       <c r="D63" s="31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E63" s="32">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F63" s="32" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G63" s="31" t="s">
         <v>177</v>
       </c>
       <c r="H63" s="32" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I63" s="31" t="s">
         <v>647</v>
@@ -20702,33 +21216,33 @@
         <v>638</v>
       </c>
       <c r="K63" s="32" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A64" s="55" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B64" s="47" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="C64" s="31">
         <v>58</v>
       </c>
       <c r="D64" s="31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E64" s="32">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="F64" s="32" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="G64" s="31" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="H64" s="32" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="I64" s="31" t="s">
         <v>647</v>
@@ -20737,33 +21251,33 @@
         <v>638</v>
       </c>
       <c r="K64" s="32" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A65" s="55" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B65" s="47" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C65" s="31">
         <v>59</v>
       </c>
       <c r="D65" s="31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E65" s="32">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F65" s="32" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G65" s="31" t="s">
         <v>143</v>
       </c>
       <c r="H65" s="32" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I65" s="31" t="s">
         <v>647</v>
@@ -20772,33 +21286,33 @@
         <v>638</v>
       </c>
       <c r="K65" s="32" t="s">
-        <v>995</v>
+        <v>650</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="55" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B66" s="47" t="s">
-        <v>868</v>
+        <v>554</v>
       </c>
       <c r="C66" s="31">
         <v>60</v>
       </c>
       <c r="D66" s="31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E66" s="32">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="F66" s="32" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G66" s="31" t="s">
         <v>143</v>
       </c>
       <c r="H66" s="32" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="I66" s="31" t="s">
         <v>647</v>
@@ -20807,33 +21321,33 @@
         <v>638</v>
       </c>
       <c r="K66" s="32" t="s">
-        <v>651</v>
+        <v>991</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="55" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B67" s="47" t="s">
-        <v>905</v>
+        <v>864</v>
       </c>
       <c r="C67" s="31">
         <v>61</v>
       </c>
       <c r="D67" s="31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E67" s="32">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="F67" s="32" t="s">
-        <v>411</v>
+        <v>173</v>
       </c>
       <c r="G67" s="31" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="H67" s="32" t="s">
-        <v>652</v>
+        <v>174</v>
       </c>
       <c r="I67" s="31" t="s">
         <v>647</v>
@@ -20842,33 +21356,33 @@
         <v>638</v>
       </c>
       <c r="K67" s="32" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="55" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B68" s="47" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="C68" s="31">
         <v>62</v>
       </c>
       <c r="D68" s="31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E68" s="32">
-        <v>5376</v>
+        <v>145</v>
       </c>
       <c r="F68" s="32" t="s">
-        <v>494</v>
+        <v>411</v>
       </c>
       <c r="G68" s="31" t="s">
         <v>177</v>
       </c>
       <c r="H68" s="32" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="I68" s="31" t="s">
         <v>647</v>
@@ -20877,33 +21391,33 @@
         <v>638</v>
       </c>
       <c r="K68" s="32" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="55" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B69" s="47" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="C69" s="31">
         <v>63</v>
       </c>
       <c r="D69" s="31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E69" s="32">
-        <v>5425</v>
+        <v>5376</v>
       </c>
       <c r="F69" s="32" t="s">
-        <v>655</v>
+        <v>494</v>
       </c>
       <c r="G69" s="31" t="s">
-        <v>834</v>
+        <v>177</v>
       </c>
       <c r="H69" s="32" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="I69" s="31" t="s">
         <v>647</v>
@@ -20912,125 +21426,139 @@
         <v>638</v>
       </c>
       <c r="K69" s="32" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A70" s="55" t="s">
+        <v>906</v>
+      </c>
+      <c r="B70" s="47" t="s">
+        <v>903</v>
+      </c>
+      <c r="C70" s="31">
+        <v>64</v>
+      </c>
+      <c r="D70" s="31" t="s">
+        <v>832</v>
+      </c>
+      <c r="E70" s="32">
+        <v>5425</v>
+      </c>
+      <c r="F70" s="32" t="s">
+        <v>655</v>
+      </c>
+      <c r="G70" s="31" t="s">
+        <v>833</v>
+      </c>
+      <c r="H70" s="32" t="s">
+        <v>656</v>
+      </c>
+      <c r="I70" s="31" t="s">
+        <v>647</v>
+      </c>
+      <c r="J70" s="31" t="s">
+        <v>638</v>
+      </c>
+      <c r="K70" s="32" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A70" s="54" t="s">
-        <v>910</v>
-      </c>
-      <c r="B70" s="46" t="s">
-        <v>908</v>
-      </c>
-      <c r="C70" s="33">
-        <v>64</v>
-      </c>
-      <c r="D70" s="33" t="s">
+    <row r="71" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A71" s="54" t="s">
+        <v>906</v>
+      </c>
+      <c r="B71" s="46" t="s">
+        <v>904</v>
+      </c>
+      <c r="C71" s="33">
+        <v>65</v>
+      </c>
+      <c r="D71" s="33" t="s">
+        <v>834</v>
+      </c>
+      <c r="E71" s="34">
+        <v>3671</v>
+      </c>
+      <c r="F71" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="G71" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="H71" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="I71" s="33" t="s">
+        <v>658</v>
+      </c>
+      <c r="J71" s="33" t="s">
+        <v>638</v>
+      </c>
+      <c r="K71" s="34" t="s">
         <v>835</v>
       </c>
-      <c r="E70" s="34">
-        <v>3671</v>
-      </c>
-      <c r="F70" s="34" t="s">
-        <v>457</v>
-      </c>
-      <c r="G70" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="H70" s="34" t="s">
-        <v>156</v>
-      </c>
-      <c r="I70" s="33" t="s">
-        <v>658</v>
-      </c>
-      <c r="J70" s="33" t="s">
-        <v>638</v>
-      </c>
-      <c r="K70" s="34" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71" s="15"/>
-      <c r="B71" s="15"/>
-      <c r="C71" s="15"/>
-      <c r="D71" s="15"/>
-      <c r="E71" s="18"/>
-      <c r="F71" s="15"/>
-      <c r="G71" s="15"/>
-      <c r="H71" s="15"/>
-      <c r="I71" s="15"/>
-      <c r="J71" s="15"/>
-      <c r="K71" s="18"/>
-    </row>
-    <row r="72" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="16" t="s">
-        <v>837</v>
-      </c>
-      <c r="B72" s="17"/>
-      <c r="C72" s="17"/>
-      <c r="D72" s="17"/>
-      <c r="E72" s="19"/>
-      <c r="F72" s="17"/>
-      <c r="G72" s="17"/>
-      <c r="H72" s="17"/>
-      <c r="I72" s="17"/>
-      <c r="J72" s="17"/>
-      <c r="K72" s="19"/>
-    </row>
-    <row r="73" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A73" s="14"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="20" t="s">
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="15"/>
+      <c r="B72" s="15"/>
+      <c r="C72" s="15"/>
+      <c r="D72" s="15"/>
+      <c r="E72" s="18"/>
+      <c r="F72" s="15"/>
+      <c r="G72" s="15"/>
+      <c r="H72" s="15"/>
+      <c r="I72" s="15"/>
+      <c r="J72" s="15"/>
+      <c r="K72" s="18"/>
+    </row>
+    <row r="73" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A73" s="16" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B73" s="17"/>
+      <c r="C73" s="17"/>
+      <c r="D73" s="17"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="17"/>
+      <c r="G73" s="17"/>
+      <c r="H73" s="17"/>
+      <c r="I73" s="17"/>
+      <c r="J73" s="17"/>
+      <c r="K73" s="19"/>
+    </row>
+    <row r="74" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A74" s="14"/>
+      <c r="B74" s="14"/>
+      <c r="C74" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="D73" s="20" t="s">
+      <c r="D74" s="20" t="s">
         <v>660</v>
       </c>
-      <c r="E73" s="35" t="s">
+      <c r="E74" s="35" t="s">
         <v>661</v>
       </c>
-      <c r="F73" s="20"/>
-      <c r="G73" s="20"/>
-      <c r="H73" s="20"/>
-      <c r="I73" s="20"/>
-      <c r="J73" s="20"/>
-      <c r="K73" s="35" t="s">
+      <c r="F74" s="20"/>
+      <c r="G74" s="20"/>
+      <c r="H74" s="20"/>
+      <c r="I74" s="20"/>
+      <c r="J74" s="20"/>
+      <c r="K74" s="35" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="240" x14ac:dyDescent="0.25">
-      <c r="A74" s="15"/>
-      <c r="B74" s="15"/>
-      <c r="C74" s="36" t="s">
-        <v>663</v>
-      </c>
-      <c r="D74" s="36">
-        <v>61</v>
-      </c>
-      <c r="E74" s="37" t="s">
-        <v>838</v>
-      </c>
-      <c r="F74" s="36"/>
-      <c r="G74" s="36"/>
-      <c r="H74" s="36"/>
-      <c r="I74" s="36"/>
-      <c r="J74" s="36"/>
-      <c r="K74" s="37" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" ht="135" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" ht="240" x14ac:dyDescent="0.25">
       <c r="A75" s="15"/>
       <c r="B75" s="15"/>
       <c r="C75" s="36" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="D75" s="36">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E75" s="37" t="s">
-        <v>670</v>
+        <v>836</v>
       </c>
       <c r="F75" s="36"/>
       <c r="G75" s="36"/>
@@ -21038,20 +21566,20 @@
       <c r="I75" s="36"/>
       <c r="J75" s="36"/>
       <c r="K75" s="37" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="135" x14ac:dyDescent="0.25">
       <c r="A76" s="15"/>
       <c r="B76" s="15"/>
       <c r="C76" s="36" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="D76" s="36">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="E76" s="37" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="F76" s="36"/>
       <c r="G76" s="36"/>
@@ -21059,20 +21587,20 @@
       <c r="I76" s="36"/>
       <c r="J76" s="36"/>
       <c r="K76" s="37" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A77" s="15"/>
       <c r="B77" s="15"/>
       <c r="C77" s="36" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D77" s="36">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E77" s="37" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="F77" s="36"/>
       <c r="G77" s="36"/>
@@ -21080,20 +21608,20 @@
       <c r="I77" s="36"/>
       <c r="J77" s="36"/>
       <c r="K77" s="37" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" ht="270" x14ac:dyDescent="0.25">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A78" s="15"/>
       <c r="B78" s="15"/>
       <c r="C78" s="36" t="s">
-        <v>840</v>
+        <v>666</v>
       </c>
       <c r="D78" s="36">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E78" s="37" t="s">
-        <v>841</v>
+        <v>667</v>
       </c>
       <c r="F78" s="36"/>
       <c r="G78" s="36"/>
@@ -21101,20 +21629,20 @@
       <c r="I78" s="36"/>
       <c r="J78" s="36"/>
       <c r="K78" s="37" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="240" x14ac:dyDescent="0.25">
       <c r="A79" s="15"/>
       <c r="B79" s="15"/>
       <c r="C79" s="36" t="s">
-        <v>671</v>
+        <v>838</v>
       </c>
       <c r="D79" s="36">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E79" s="37" t="s">
-        <v>672</v>
+        <v>1035</v>
       </c>
       <c r="F79" s="36"/>
       <c r="G79" s="36"/>
@@ -21122,20 +21650,20 @@
       <c r="I79" s="36"/>
       <c r="J79" s="36"/>
       <c r="K79" s="37" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="15"/>
       <c r="B80" s="15"/>
       <c r="C80" s="36" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D80" s="36">
         <v>3</v>
       </c>
       <c r="E80" s="37" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="F80" s="36"/>
       <c r="G80" s="36"/>
@@ -21143,20 +21671,20 @@
       <c r="I80" s="36"/>
       <c r="J80" s="36"/>
       <c r="K80" s="37" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A81" s="15"/>
       <c r="B81" s="15"/>
       <c r="C81" s="36" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="D81" s="36">
         <v>3</v>
       </c>
       <c r="E81" s="37" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="F81" s="36"/>
       <c r="G81" s="36"/>
@@ -21164,20 +21692,20 @@
       <c r="I81" s="36"/>
       <c r="J81" s="36"/>
       <c r="K81" s="37" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="15"/>
       <c r="B82" s="15"/>
       <c r="C82" s="36" t="s">
-        <v>999</v>
-      </c>
-      <c r="D82" s="36" t="s">
-        <v>638</v>
+        <v>677</v>
+      </c>
+      <c r="D82" s="36">
+        <v>3</v>
       </c>
       <c r="E82" s="37" t="s">
-        <v>1000</v>
+        <v>678</v>
       </c>
       <c r="F82" s="36"/>
       <c r="G82" s="36"/>
@@ -21185,63 +21713,67 @@
       <c r="I82" s="36"/>
       <c r="J82" s="36"/>
       <c r="K82" s="37" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A83" s="15"/>
       <c r="B83" s="15"/>
-      <c r="C83" s="15"/>
-      <c r="D83" s="15"/>
-      <c r="E83" s="15"/>
-      <c r="F83" s="15"/>
-      <c r="G83" s="15"/>
-      <c r="H83" s="15"/>
-      <c r="I83" s="15"/>
-      <c r="J83" s="15"/>
-      <c r="K83" s="15"/>
-    </row>
-    <row r="84" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A84" s="16" t="s">
+      <c r="C83" s="36" t="s">
+        <v>995</v>
+      </c>
+      <c r="D83" s="36" t="s">
+        <v>638</v>
+      </c>
+      <c r="E83" s="37" t="s">
+        <v>996</v>
+      </c>
+      <c r="F83" s="36"/>
+      <c r="G83" s="36"/>
+      <c r="H83" s="36"/>
+      <c r="I83" s="36"/>
+      <c r="J83" s="36"/>
+      <c r="K83" s="37" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" s="15"/>
+      <c r="B84" s="15"/>
+      <c r="C84" s="15"/>
+      <c r="D84" s="15"/>
+      <c r="E84" s="15"/>
+      <c r="F84" s="15"/>
+      <c r="G84" s="15"/>
+      <c r="H84" s="15"/>
+      <c r="I84" s="15"/>
+      <c r="J84" s="15"/>
+      <c r="K84" s="15"/>
+    </row>
+    <row r="85" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A85" s="16" t="s">
         <v>680</v>
       </c>
-      <c r="B84" s="17"/>
-      <c r="C84" s="17"/>
-      <c r="D84" s="17"/>
-      <c r="E84" s="17"/>
-      <c r="F84" s="17"/>
-      <c r="G84" s="17"/>
-      <c r="H84" s="17"/>
-      <c r="I84" s="17"/>
-      <c r="J84" s="17"/>
-      <c r="K84" s="17"/>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85" s="15"/>
-      <c r="B85" s="15"/>
-      <c r="C85" s="38" t="s">
-        <v>681</v>
-      </c>
-      <c r="D85" s="15"/>
-      <c r="E85" s="38">
-        <v>208</v>
-      </c>
-      <c r="F85" s="15"/>
-      <c r="G85" s="15"/>
-      <c r="H85" s="15"/>
-      <c r="I85" s="15"/>
-      <c r="J85" s="15"/>
-      <c r="K85" s="15"/>
+      <c r="B85" s="17"/>
+      <c r="C85" s="17"/>
+      <c r="D85" s="17"/>
+      <c r="E85" s="17"/>
+      <c r="F85" s="17"/>
+      <c r="G85" s="17"/>
+      <c r="H85" s="17"/>
+      <c r="I85" s="17"/>
+      <c r="J85" s="17"/>
+      <c r="K85" s="17"/>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="15"/>
       <c r="B86" s="15"/>
       <c r="C86" s="38" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D86" s="15"/>
-      <c r="E86" s="38" t="s">
-        <v>1002</v>
+      <c r="E86" s="38">
+        <v>208</v>
       </c>
       <c r="F86" s="15"/>
       <c r="G86" s="15"/>
@@ -21254,11 +21786,11 @@
       <c r="A87" s="15"/>
       <c r="B87" s="15"/>
       <c r="C87" s="38" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D87" s="15"/>
-      <c r="E87" s="38">
-        <v>171</v>
+      <c r="E87" s="38" t="s">
+        <v>1037</v>
       </c>
       <c r="F87" s="15"/>
       <c r="G87" s="15"/>
@@ -21271,11 +21803,11 @@
       <c r="A88" s="15"/>
       <c r="B88" s="15"/>
       <c r="C88" s="38" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D88" s="15"/>
       <c r="E88" s="38">
-        <v>23</v>
+        <v>170</v>
       </c>
       <c r="F88" s="15"/>
       <c r="G88" s="15"/>
@@ -21288,11 +21820,11 @@
       <c r="A89" s="15"/>
       <c r="B89" s="15"/>
       <c r="C89" s="38" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D89" s="15"/>
       <c r="E89" s="38">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F89" s="15"/>
       <c r="G89" s="15"/>
@@ -21305,11 +21837,11 @@
       <c r="A90" s="15"/>
       <c r="B90" s="15"/>
       <c r="C90" s="38" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D90" s="15"/>
       <c r="E90" s="38">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F90" s="15"/>
       <c r="G90" s="15"/>
@@ -21322,11 +21854,11 @@
       <c r="A91" s="15"/>
       <c r="B91" s="15"/>
       <c r="C91" s="38" t="s">
-        <v>1003</v>
+        <v>687</v>
       </c>
       <c r="D91" s="15"/>
-      <c r="E91" s="38" t="s">
-        <v>1004</v>
+      <c r="E91" s="38">
+        <v>6</v>
       </c>
       <c r="F91" s="15"/>
       <c r="G91" s="15"/>
@@ -21339,11 +21871,11 @@
       <c r="A92" s="15"/>
       <c r="B92" s="15"/>
       <c r="C92" s="38" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
       <c r="D92" s="15"/>
       <c r="E92" s="38" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="F92" s="15"/>
       <c r="G92" s="15"/>
@@ -21356,11 +21888,11 @@
       <c r="A93" s="15"/>
       <c r="B93" s="15"/>
       <c r="C93" s="38" t="s">
-        <v>843</v>
+        <v>1000</v>
       </c>
       <c r="D93" s="15"/>
       <c r="E93" s="38" t="s">
-        <v>844</v>
+        <v>1038</v>
       </c>
       <c r="F93" s="15"/>
       <c r="G93" s="15"/>
@@ -21373,11 +21905,11 @@
       <c r="A94" s="15"/>
       <c r="B94" s="15"/>
       <c r="C94" s="38" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="D94" s="15"/>
       <c r="E94" s="38" t="s">
-        <v>1007</v>
+        <v>840</v>
       </c>
       <c r="F94" s="15"/>
       <c r="G94" s="15"/>
@@ -21390,11 +21922,11 @@
       <c r="A95" s="15"/>
       <c r="B95" s="15"/>
       <c r="C95" s="38" t="s">
-        <v>689</v>
+        <v>841</v>
       </c>
       <c r="D95" s="15"/>
       <c r="E95" s="38" t="s">
-        <v>846</v>
+        <v>1039</v>
       </c>
       <c r="F95" s="15"/>
       <c r="G95" s="15"/>
@@ -21406,9 +21938,13 @@
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="15"/>
       <c r="B96" s="15"/>
-      <c r="C96" s="15"/>
+      <c r="C96" s="38" t="s">
+        <v>689</v>
+      </c>
       <c r="D96" s="15"/>
-      <c r="E96" s="15"/>
+      <c r="E96" s="38" t="s">
+        <v>842</v>
+      </c>
       <c r="F96" s="15"/>
       <c r="G96" s="15"/>
       <c r="H96" s="15"/>
@@ -21416,41 +21952,39 @@
       <c r="J96" s="15"/>
       <c r="K96" s="15"/>
     </row>
-    <row r="97" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A97" s="16" t="s">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" s="15"/>
+      <c r="B97" s="15"/>
+      <c r="C97" s="15"/>
+      <c r="D97" s="15"/>
+      <c r="E97" s="15"/>
+      <c r="F97" s="15"/>
+      <c r="G97" s="15"/>
+      <c r="H97" s="15"/>
+      <c r="I97" s="15"/>
+      <c r="J97" s="15"/>
+      <c r="K97" s="15"/>
+    </row>
+    <row r="98" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A98" s="16" t="s">
         <v>690</v>
       </c>
-      <c r="B97" s="17"/>
-      <c r="C97" s="17"/>
-      <c r="D97" s="17"/>
-      <c r="E97" s="17"/>
-      <c r="F97" s="17"/>
-      <c r="G97" s="17"/>
-      <c r="H97" s="17"/>
-      <c r="I97" s="17"/>
-      <c r="J97" s="17"/>
-      <c r="K97" s="17"/>
-    </row>
-    <row r="98" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A98" s="15"/>
-      <c r="B98" s="15"/>
-      <c r="C98" s="18" t="s">
-        <v>1008</v>
-      </c>
-      <c r="D98" s="15"/>
-      <c r="E98" s="15"/>
-      <c r="F98" s="15"/>
-      <c r="G98" s="15"/>
-      <c r="H98" s="15"/>
-      <c r="I98" s="15"/>
-      <c r="J98" s="15"/>
-      <c r="K98" s="15"/>
+      <c r="B98" s="17"/>
+      <c r="C98" s="17"/>
+      <c r="D98" s="17"/>
+      <c r="E98" s="17"/>
+      <c r="F98" s="17"/>
+      <c r="G98" s="17"/>
+      <c r="H98" s="17"/>
+      <c r="I98" s="17"/>
+      <c r="J98" s="17"/>
+      <c r="K98" s="17"/>
     </row>
     <row r="99" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A99" s="15"/>
       <c r="B99" s="15"/>
       <c r="C99" s="18" t="s">
-        <v>1009</v>
+        <v>1001</v>
       </c>
       <c r="D99" s="15"/>
       <c r="E99" s="15"/>
@@ -21465,7 +21999,7 @@
       <c r="A100" s="15"/>
       <c r="B100" s="15"/>
       <c r="C100" s="18" t="s">
-        <v>1010</v>
+        <v>1002</v>
       </c>
       <c r="D100" s="15"/>
       <c r="E100" s="15"/>
@@ -21480,7 +22014,7 @@
       <c r="A101" s="15"/>
       <c r="B101" s="15"/>
       <c r="C101" s="18" t="s">
-        <v>1011</v>
+        <v>1003</v>
       </c>
       <c r="D101" s="15"/>
       <c r="E101" s="15"/>
@@ -21495,7 +22029,7 @@
       <c r="A102" s="15"/>
       <c r="B102" s="15"/>
       <c r="C102" s="18" t="s">
-        <v>1012</v>
+        <v>1004</v>
       </c>
       <c r="D102" s="15"/>
       <c r="E102" s="15"/>
@@ -21510,7 +22044,7 @@
       <c r="A103" s="15"/>
       <c r="B103" s="15"/>
       <c r="C103" s="18" t="s">
-        <v>847</v>
+        <v>1005</v>
       </c>
       <c r="D103" s="15"/>
       <c r="E103" s="15"/>
@@ -21525,7 +22059,7 @@
       <c r="A104" s="15"/>
       <c r="B104" s="15"/>
       <c r="C104" s="18" t="s">
-        <v>1013</v>
+        <v>843</v>
       </c>
       <c r="D104" s="15"/>
       <c r="E104" s="15"/>
@@ -21540,7 +22074,7 @@
       <c r="A105" s="15"/>
       <c r="B105" s="15"/>
       <c r="C105" s="18" t="s">
-        <v>909</v>
+        <v>1006</v>
       </c>
       <c r="D105" s="15"/>
       <c r="E105" s="15"/>
@@ -21555,7 +22089,7 @@
       <c r="A106" s="15"/>
       <c r="B106" s="15"/>
       <c r="C106" s="18" t="s">
-        <v>848</v>
+        <v>905</v>
       </c>
       <c r="D106" s="15"/>
       <c r="E106" s="15"/>
@@ -21566,11 +22100,11 @@
       <c r="J106" s="15"/>
       <c r="K106" s="15"/>
     </row>
-    <row r="107" spans="1:11" ht="345" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A107" s="15"/>
       <c r="B107" s="15"/>
       <c r="C107" s="18" t="s">
-        <v>691</v>
+        <v>844</v>
       </c>
       <c r="D107" s="15"/>
       <c r="E107" s="15"/>
@@ -21581,11 +22115,11 @@
       <c r="J107" s="15"/>
       <c r="K107" s="15"/>
     </row>
-    <row r="108" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" ht="345" x14ac:dyDescent="0.25">
       <c r="A108" s="15"/>
       <c r="B108" s="15"/>
       <c r="C108" s="18" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D108" s="15"/>
       <c r="E108" s="15"/>
@@ -21596,11 +22130,11 @@
       <c r="J108" s="15"/>
       <c r="K108" s="15"/>
     </row>
-    <row r="109" spans="1:11" ht="345" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A109" s="15"/>
       <c r="B109" s="15"/>
       <c r="C109" s="18" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D109" s="15"/>
       <c r="E109" s="15"/>
@@ -21611,11 +22145,11 @@
       <c r="J109" s="15"/>
       <c r="K109" s="15"/>
     </row>
-    <row r="110" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" ht="345" x14ac:dyDescent="0.25">
       <c r="A110" s="15"/>
       <c r="B110" s="15"/>
       <c r="C110" s="18" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D110" s="15"/>
       <c r="E110" s="15"/>
@@ -21630,7 +22164,7 @@
       <c r="A111" s="15"/>
       <c r="B111" s="15"/>
       <c r="C111" s="18" t="s">
-        <v>849</v>
+        <v>694</v>
       </c>
       <c r="D111" s="15"/>
       <c r="E111" s="15"/>
@@ -21641,10 +22175,25 @@
       <c r="J111" s="15"/>
       <c r="K111" s="15"/>
     </row>
+    <row r="112" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A112" s="15"/>
+      <c r="B112" s="15"/>
+      <c r="C112" s="18" t="s">
+        <v>845</v>
+      </c>
+      <c r="D112" s="15"/>
+      <c r="E112" s="15"/>
+      <c r="F112" s="15"/>
+      <c r="G112" s="15"/>
+      <c r="H112" s="15"/>
+      <c r="I112" s="15"/>
+      <c r="J112" s="15"/>
+      <c r="K112" s="15"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A6:K70" xr:uid="{FB8EDA5B-3056-480A-AA43-F447F580627A}"/>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Abhaken" prompt="Haken setzen, wenn der Datenpunkt in Desigo CC angelegt ist." sqref="A7:A70" xr:uid="{18F9A785-CE63-4312-ADB5-134312DCB15D}">
+  <autoFilter ref="A6:K71" xr:uid="{FB8EDA5B-3056-480A-AA43-F447F580627A}"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Abhaken" prompt="Haken setzen, wenn der Datenpunkt in Desigo CC angelegt ist." sqref="A7:A71" xr:uid="{18F9A785-CE63-4312-ADB5-134312DCB15D}">
       <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
         <mc:Choice Requires="x12ac">
           <x12ac:list>"☐,☑"</x12ac:list>
@@ -21659,6 +22208,1568 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D43A343-4073-406A-86F2-4B87EF3ED65B}">
+  <dimension ref="A1:N47"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.7109375" customWidth="1"/>
+    <col min="2" max="2" width="42.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" customWidth="1"/>
+    <col min="6" max="6" width="40.7109375" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" customWidth="1"/>
+    <col min="11" max="11" width="42.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" customWidth="1"/>
+    <col min="13" max="13" width="34.7109375" customWidth="1"/>
+    <col min="14" max="14" width="52.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="58" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="60" t="s">
+        <v>584</v>
+      </c>
+      <c r="B9" s="60" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C9" s="60" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D9" s="60" t="s">
+        <v>126</v>
+      </c>
+      <c r="E9" s="60" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F9" s="60" t="s">
+        <v>129</v>
+      </c>
+      <c r="G9" s="60" t="s">
+        <v>1051</v>
+      </c>
+      <c r="H9" s="60" t="s">
+        <v>1052</v>
+      </c>
+      <c r="I9" s="60" t="s">
+        <v>135</v>
+      </c>
+      <c r="J9" s="60" t="s">
+        <v>1053</v>
+      </c>
+      <c r="K9" s="60" t="s">
+        <v>1054</v>
+      </c>
+      <c r="L9" s="60" t="s">
+        <v>1055</v>
+      </c>
+      <c r="M9" s="60" t="s">
+        <v>1056</v>
+      </c>
+      <c r="N9" s="60" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="65" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B10" s="65" t="s">
+        <v>849</v>
+      </c>
+      <c r="C10" s="65" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D10" s="65" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E10" s="65" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F10" s="66" t="s">
+        <v>591</v>
+      </c>
+      <c r="G10" s="65" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H10" s="65" t="s">
+        <v>1063</v>
+      </c>
+      <c r="I10" s="65"/>
+      <c r="J10" s="65" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K10" s="66" t="s">
+        <v>1064</v>
+      </c>
+      <c r="L10" s="65" t="s">
+        <v>1065</v>
+      </c>
+      <c r="M10" s="66" t="s">
+        <v>1066</v>
+      </c>
+      <c r="N10" s="66" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="61" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B11" s="61" t="s">
+        <v>866</v>
+      </c>
+      <c r="C11" s="61" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D11" s="61" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E11" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F11" s="62" t="s">
+        <v>721</v>
+      </c>
+      <c r="G11" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H11" s="61" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I11" s="61"/>
+      <c r="J11" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K11" s="62" t="s">
+        <v>1070</v>
+      </c>
+      <c r="L11" s="61" t="s">
+        <v>1071</v>
+      </c>
+      <c r="M11" s="62"/>
+      <c r="N11" s="62" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="61" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B12" s="61" t="s">
+        <v>867</v>
+      </c>
+      <c r="C12" s="61" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D12" s="61" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E12" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F12" s="62" t="s">
+        <v>809</v>
+      </c>
+      <c r="G12" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H12" s="61" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I12" s="61"/>
+      <c r="J12" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K12" s="62" t="s">
+        <v>1075</v>
+      </c>
+      <c r="L12" s="61" t="s">
+        <v>1076</v>
+      </c>
+      <c r="M12" s="62"/>
+      <c r="N12" s="62" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="61" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B13" s="61" t="s">
+        <v>868</v>
+      </c>
+      <c r="C13" s="61" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D13" s="61" t="s">
+        <v>596</v>
+      </c>
+      <c r="E13" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F13" s="62" t="s">
+        <v>597</v>
+      </c>
+      <c r="G13" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H13" s="61" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I13" s="61"/>
+      <c r="J13" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K13" s="62" t="s">
+        <v>1079</v>
+      </c>
+      <c r="L13" s="61" t="s">
+        <v>1080</v>
+      </c>
+      <c r="M13" s="62"/>
+      <c r="N13" s="62" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="61" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B14" s="61" t="s">
+        <v>869</v>
+      </c>
+      <c r="C14" s="61" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D14" s="61" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E14" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F14" s="62" t="s">
+        <v>698</v>
+      </c>
+      <c r="G14" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H14" s="61" t="s">
+        <v>1084</v>
+      </c>
+      <c r="I14" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="J14" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K14" s="62"/>
+      <c r="L14" s="61" t="s">
+        <v>1080</v>
+      </c>
+      <c r="M14" s="62"/>
+      <c r="N14" s="62" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="61" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>880</v>
+      </c>
+      <c r="C15" s="61" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D15" s="61" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E15" s="61" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F15" s="62" t="s">
+        <v>708</v>
+      </c>
+      <c r="G15" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H15" s="61" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I15" s="61" t="s">
+        <v>398</v>
+      </c>
+      <c r="J15" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K15" s="62"/>
+      <c r="L15" s="61" t="s">
+        <v>1090</v>
+      </c>
+      <c r="M15" s="62"/>
+      <c r="N15" s="62"/>
+    </row>
+    <row r="16" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="61" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>881</v>
+      </c>
+      <c r="C16" s="61" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D16" s="61" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E16" s="61" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F16" s="62" t="s">
+        <v>710</v>
+      </c>
+      <c r="G16" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H16" s="61" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I16" s="61" t="s">
+        <v>398</v>
+      </c>
+      <c r="J16" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K16" s="62"/>
+      <c r="L16" s="61" t="s">
+        <v>1093</v>
+      </c>
+      <c r="M16" s="62"/>
+      <c r="N16" s="62" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="61" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B17" s="61" t="s">
+        <v>882</v>
+      </c>
+      <c r="C17" s="61" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D17" s="61" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E17" s="61" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F17" s="62" t="s">
+        <v>711</v>
+      </c>
+      <c r="G17" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H17" s="61" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I17" s="61" t="s">
+        <v>406</v>
+      </c>
+      <c r="J17" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K17" s="62"/>
+      <c r="L17" s="61" t="s">
+        <v>1090</v>
+      </c>
+      <c r="M17" s="62"/>
+      <c r="N17" s="62"/>
+    </row>
+    <row r="18" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="61" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B18" s="61" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C18" s="61" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D18" s="61" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E18" s="61" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F18" s="62" t="s">
+        <v>712</v>
+      </c>
+      <c r="G18" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H18" s="61" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I18" s="61" t="s">
+        <v>713</v>
+      </c>
+      <c r="J18" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K18" s="62"/>
+      <c r="L18" s="61" t="s">
+        <v>1093</v>
+      </c>
+      <c r="M18" s="62"/>
+      <c r="N18" s="62" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="61" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B19" s="61" t="s">
+        <v>883</v>
+      </c>
+      <c r="C19" s="61" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D19" s="61" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E19" s="61" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F19" s="62" t="s">
+        <v>714</v>
+      </c>
+      <c r="G19" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H19" s="61" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I19" s="61" t="s">
+        <v>715</v>
+      </c>
+      <c r="J19" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K19" s="62"/>
+      <c r="L19" s="61" t="s">
+        <v>1093</v>
+      </c>
+      <c r="M19" s="62"/>
+      <c r="N19" s="62"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="61" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B20" s="61" t="s">
+        <v>884</v>
+      </c>
+      <c r="C20" s="61" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D20" s="61" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E20" s="61" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F20" s="62" t="s">
+        <v>720</v>
+      </c>
+      <c r="G20" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H20" s="61" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K20" s="62"/>
+      <c r="L20" s="61" t="s">
+        <v>1093</v>
+      </c>
+      <c r="M20" s="62"/>
+      <c r="N20" s="62"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="61" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B21" s="61" t="s">
+        <v>852</v>
+      </c>
+      <c r="C21" s="61" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D21" s="61" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E21" s="61" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F21" s="62" t="s">
+        <v>158</v>
+      </c>
+      <c r="G21" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H21" s="61" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I21" s="61" t="s">
+        <v>161</v>
+      </c>
+      <c r="J21" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K21" s="62"/>
+      <c r="L21" s="61" t="s">
+        <v>1111</v>
+      </c>
+      <c r="M21" s="62"/>
+      <c r="N21" s="62"/>
+    </row>
+    <row r="22" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="61" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B22" s="61" t="s">
+        <v>885</v>
+      </c>
+      <c r="C22" s="61" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D22" s="61" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E22" s="61" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F22" s="62" t="s">
+        <v>819</v>
+      </c>
+      <c r="G22" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H22" s="61" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I22" s="61" t="s">
+        <v>398</v>
+      </c>
+      <c r="J22" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K22" s="62"/>
+      <c r="L22" s="61" t="s">
+        <v>1115</v>
+      </c>
+      <c r="M22" s="62"/>
+      <c r="N22" s="62" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="61" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B23" s="61" t="s">
+        <v>855</v>
+      </c>
+      <c r="C23" s="61" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D23" s="61" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E23" s="61" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F23" s="62" t="s">
+        <v>144</v>
+      </c>
+      <c r="G23" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H23" s="61" t="s">
+        <v>1120</v>
+      </c>
+      <c r="I23" s="61" t="s">
+        <v>146</v>
+      </c>
+      <c r="J23" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K23" s="62"/>
+      <c r="L23" s="61" t="s">
+        <v>1115</v>
+      </c>
+      <c r="M23" s="62"/>
+      <c r="N23" s="62" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="61" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B24" s="61" t="s">
+        <v>886</v>
+      </c>
+      <c r="C24" s="61" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D24" s="61" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E24" s="61" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F24" s="62" t="s">
+        <v>695</v>
+      </c>
+      <c r="G24" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H24" s="61" t="s">
+        <v>1120</v>
+      </c>
+      <c r="I24" s="61" t="s">
+        <v>146</v>
+      </c>
+      <c r="J24" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K24" s="62"/>
+      <c r="L24" s="61" t="s">
+        <v>1115</v>
+      </c>
+      <c r="M24" s="62"/>
+      <c r="N24" s="62" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="61" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B25" s="61" t="s">
+        <v>887</v>
+      </c>
+      <c r="C25" s="61" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D25" s="61" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E25" s="61" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F25" s="62" t="s">
+        <v>696</v>
+      </c>
+      <c r="G25" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H25" s="61" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I25" s="61"/>
+      <c r="J25" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K25" s="62"/>
+      <c r="L25" s="61" t="s">
+        <v>1115</v>
+      </c>
+      <c r="M25" s="62"/>
+      <c r="N25" s="62"/>
+    </row>
+    <row r="26" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="61" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B26" s="61" t="s">
+        <v>888</v>
+      </c>
+      <c r="C26" s="61" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D26" s="61" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E26" s="61" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F26" s="62" t="s">
+        <v>697</v>
+      </c>
+      <c r="G26" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H26" s="61" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I26" s="61"/>
+      <c r="J26" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K26" s="62"/>
+      <c r="L26" s="61" t="s">
+        <v>1115</v>
+      </c>
+      <c r="M26" s="62"/>
+      <c r="N26" s="62" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="61" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B27" s="61" t="s">
+        <v>889</v>
+      </c>
+      <c r="C27" s="61" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D27" s="61" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E27" s="61" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F27" s="62" t="s">
+        <v>699</v>
+      </c>
+      <c r="G27" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H27" s="61" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I27" s="61"/>
+      <c r="J27" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K27" s="62"/>
+      <c r="L27" s="61" t="s">
+        <v>1115</v>
+      </c>
+      <c r="M27" s="62"/>
+      <c r="N27" s="62"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="61" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B28" s="61" t="s">
+        <v>890</v>
+      </c>
+      <c r="C28" s="61" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D28" s="61" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E28" s="61" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F28" s="62" t="s">
+        <v>702</v>
+      </c>
+      <c r="G28" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H28" s="61" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I28" s="61"/>
+      <c r="J28" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K28" s="62"/>
+      <c r="L28" s="61" t="s">
+        <v>1115</v>
+      </c>
+      <c r="M28" s="62"/>
+      <c r="N28" s="62"/>
+    </row>
+    <row r="29" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="61" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B29" s="61" t="s">
+        <v>891</v>
+      </c>
+      <c r="C29" s="61" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D29" s="61" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E29" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F29" s="62" t="s">
+        <v>707</v>
+      </c>
+      <c r="G29" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H29" s="61" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I29" s="61"/>
+      <c r="J29" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K29" s="62"/>
+      <c r="L29" s="61" t="s">
+        <v>1115</v>
+      </c>
+      <c r="M29" s="62"/>
+      <c r="N29" s="62" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="61" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B30" s="61" t="s">
+        <v>892</v>
+      </c>
+      <c r="C30" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="D30" s="61" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E30" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F30" s="62" t="s">
+        <v>703</v>
+      </c>
+      <c r="G30" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H30" s="61" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I30" s="61"/>
+      <c r="J30" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K30" s="62" t="s">
+        <v>1139</v>
+      </c>
+      <c r="L30" s="61" t="s">
+        <v>1140</v>
+      </c>
+      <c r="M30" s="62"/>
+      <c r="N30" s="62"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="61" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B31" s="61" t="s">
+        <v>893</v>
+      </c>
+      <c r="C31" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="D31" s="61" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E31" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F31" s="62" t="s">
+        <v>700</v>
+      </c>
+      <c r="G31" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H31" s="61" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I31" s="61"/>
+      <c r="J31" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K31" s="62" t="s">
+        <v>1143</v>
+      </c>
+      <c r="L31" s="61" t="s">
+        <v>1140</v>
+      </c>
+      <c r="M31" s="62"/>
+      <c r="N31" s="62"/>
+    </row>
+    <row r="32" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="61" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B32" s="61" t="s">
+        <v>894</v>
+      </c>
+      <c r="C32" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="D32" s="61" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E32" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F32" s="62" t="s">
+        <v>827</v>
+      </c>
+      <c r="G32" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H32" s="61" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I32" s="61"/>
+      <c r="J32" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K32" s="62" t="s">
+        <v>1146</v>
+      </c>
+      <c r="L32" s="61" t="s">
+        <v>1071</v>
+      </c>
+      <c r="M32" s="62"/>
+      <c r="N32" s="62" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="63" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B33" s="63" t="s">
+        <v>895</v>
+      </c>
+      <c r="C33" s="63" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D33" s="63" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E33" s="63" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F33" s="64" t="s">
+        <v>461</v>
+      </c>
+      <c r="G33" s="63" t="s">
+        <v>1151</v>
+      </c>
+      <c r="H33" s="63" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I33" s="63"/>
+      <c r="J33" s="63" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K33" s="64" t="s">
+        <v>1152</v>
+      </c>
+      <c r="L33" s="63" t="s">
+        <v>1076</v>
+      </c>
+      <c r="M33" s="64" t="s">
+        <v>1153</v>
+      </c>
+      <c r="N33" s="64" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="63" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B34" s="63" t="s">
+        <v>896</v>
+      </c>
+      <c r="C34" s="63" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D34" s="63" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E34" s="63" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F34" s="64" t="s">
+        <v>459</v>
+      </c>
+      <c r="G34" s="63" t="s">
+        <v>1157</v>
+      </c>
+      <c r="H34" s="63" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I34" s="63"/>
+      <c r="J34" s="63" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K34" s="64" t="s">
+        <v>1158</v>
+      </c>
+      <c r="L34" s="63" t="s">
+        <v>1065</v>
+      </c>
+      <c r="M34" s="64"/>
+      <c r="N34" s="64"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="63" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B35" s="63" t="s">
+        <v>897</v>
+      </c>
+      <c r="C35" s="63" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D35" s="63" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E35" s="63" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F35" s="64" t="s">
+        <v>641</v>
+      </c>
+      <c r="G35" s="63" t="s">
+        <v>1157</v>
+      </c>
+      <c r="H35" s="63" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I35" s="63"/>
+      <c r="J35" s="63" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K35" s="64" t="s">
+        <v>1158</v>
+      </c>
+      <c r="L35" s="63" t="s">
+        <v>1065</v>
+      </c>
+      <c r="M35" s="64"/>
+      <c r="N35" s="64"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="63" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B36" s="63" t="s">
+        <v>898</v>
+      </c>
+      <c r="C36" s="63" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D36" s="63" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E36" s="63" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F36" s="64" t="s">
+        <v>428</v>
+      </c>
+      <c r="G36" s="63" t="s">
+        <v>1157</v>
+      </c>
+      <c r="H36" s="63" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I36" s="63"/>
+      <c r="J36" s="63" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K36" s="64" t="s">
+        <v>1158</v>
+      </c>
+      <c r="L36" s="63" t="s">
+        <v>1140</v>
+      </c>
+      <c r="M36" s="64"/>
+      <c r="N36" s="64"/>
+    </row>
+    <row r="37" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="63" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B37" s="63" t="s">
+        <v>899</v>
+      </c>
+      <c r="C37" s="63" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D37" s="63" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E37" s="63" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F37" s="64" t="s">
+        <v>642</v>
+      </c>
+      <c r="G37" s="63" t="s">
+        <v>1151</v>
+      </c>
+      <c r="H37" s="63" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I37" s="63"/>
+      <c r="J37" s="63" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K37" s="64" t="s">
+        <v>1165</v>
+      </c>
+      <c r="L37" s="63" t="s">
+        <v>1166</v>
+      </c>
+      <c r="M37" s="64"/>
+      <c r="N37" s="64" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="63" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B38" s="63" t="s">
+        <v>900</v>
+      </c>
+      <c r="C38" s="63" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D38" s="63" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E38" s="63" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F38" s="64" t="s">
+        <v>463</v>
+      </c>
+      <c r="G38" s="63" t="s">
+        <v>1157</v>
+      </c>
+      <c r="H38" s="63" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I38" s="63"/>
+      <c r="J38" s="63" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K38" s="64" t="s">
+        <v>1158</v>
+      </c>
+      <c r="L38" s="63" t="s">
+        <v>1076</v>
+      </c>
+      <c r="M38" s="64"/>
+      <c r="N38" s="64" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="61" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B39" s="61" t="s">
+        <v>563</v>
+      </c>
+      <c r="C39" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="D39" s="61" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E39" s="61" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F39" s="62" t="s">
+        <v>175</v>
+      </c>
+      <c r="G39" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H39" s="61" t="s">
+        <v>1172</v>
+      </c>
+      <c r="I39" s="61"/>
+      <c r="J39" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K39" s="62"/>
+      <c r="L39" s="61" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M39" s="62" t="s">
+        <v>1174</v>
+      </c>
+      <c r="N39" s="62" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="61" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B40" s="61" t="s">
+        <v>564</v>
+      </c>
+      <c r="C40" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="D40" s="61" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E40" s="61" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F40" s="62" t="s">
+        <v>178</v>
+      </c>
+      <c r="G40" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H40" s="61" t="s">
+        <v>1172</v>
+      </c>
+      <c r="I40" s="61"/>
+      <c r="J40" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K40" s="62"/>
+      <c r="L40" s="61" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M40" s="62" t="s">
+        <v>1174</v>
+      </c>
+      <c r="N40" s="62" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" s="61" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B41" s="61" t="s">
+        <v>555</v>
+      </c>
+      <c r="C41" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="D41" s="61" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E41" s="61" t="s">
+        <v>1095</v>
+      </c>
+      <c r="F41" s="62" t="s">
+        <v>170</v>
+      </c>
+      <c r="G41" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H41" s="61" t="s">
+        <v>1172</v>
+      </c>
+      <c r="I41" s="61"/>
+      <c r="J41" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K41" s="62"/>
+      <c r="L41" s="61" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M41" s="62"/>
+      <c r="N41" s="62"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" s="61" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B42" s="61" t="s">
+        <v>554</v>
+      </c>
+      <c r="C42" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="D42" s="61" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E42" s="61" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F42" s="62" t="s">
+        <v>167</v>
+      </c>
+      <c r="G42" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H42" s="61" t="s">
+        <v>1172</v>
+      </c>
+      <c r="I42" s="61"/>
+      <c r="J42" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K42" s="62"/>
+      <c r="L42" s="61" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M42" s="62"/>
+      <c r="N42" s="62"/>
+    </row>
+    <row r="43" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="61" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B43" s="61" t="s">
+        <v>901</v>
+      </c>
+      <c r="C43" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="D43" s="61" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E43" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F43" s="62" t="s">
+        <v>411</v>
+      </c>
+      <c r="G43" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H43" s="61" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I43" s="61"/>
+      <c r="J43" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K43" s="62" t="s">
+        <v>1183</v>
+      </c>
+      <c r="L43" s="61" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M43" s="62" t="s">
+        <v>1184</v>
+      </c>
+      <c r="N43" s="62" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="61" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B44" s="61" t="s">
+        <v>902</v>
+      </c>
+      <c r="C44" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="D44" s="61" t="s">
+        <v>1187</v>
+      </c>
+      <c r="E44" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F44" s="62" t="s">
+        <v>494</v>
+      </c>
+      <c r="G44" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H44" s="61" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I44" s="61" t="s">
+        <v>398</v>
+      </c>
+      <c r="J44" s="61" t="s">
+        <v>1188</v>
+      </c>
+      <c r="K44" s="62" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L44" s="61" t="s">
+        <v>1093</v>
+      </c>
+      <c r="M44" s="62"/>
+      <c r="N44" s="62" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="61" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B45" s="61" t="s">
+        <v>903</v>
+      </c>
+      <c r="C45" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="D45" s="61" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E45" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F45" s="62" t="s">
+        <v>655</v>
+      </c>
+      <c r="G45" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H45" s="61" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I45" s="61"/>
+      <c r="J45" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K45" s="62" t="s">
+        <v>1193</v>
+      </c>
+      <c r="L45" s="61" t="s">
+        <v>1076</v>
+      </c>
+      <c r="M45" s="62"/>
+      <c r="N45" s="62" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="61" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B46" s="61" t="s">
+        <v>904</v>
+      </c>
+      <c r="C46" s="61" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D46" s="61" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E46" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F46" s="62" t="s">
+        <v>457</v>
+      </c>
+      <c r="G46" s="61" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H46" s="61" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I46" s="61"/>
+      <c r="J46" s="61" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K46" s="62"/>
+      <c r="L46" s="61" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M46" s="62"/>
+      <c r="N46" s="62" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" s="59"/>
+      <c r="B47" s="59"/>
+      <c r="C47" s="59"/>
+      <c r="D47" s="59"/>
+      <c r="E47" s="59"/>
+      <c r="F47" s="59"/>
+      <c r="G47" s="59"/>
+      <c r="H47" s="59"/>
+      <c r="I47" s="59"/>
+      <c r="J47" s="59"/>
+      <c r="K47" s="59"/>
+      <c r="L47" s="59"/>
+      <c r="M47" s="59"/>
+      <c r="N47" s="59"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A9:N46" xr:uid="{1D43A343-4073-406A-86F2-4B87EF3ED65B}"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{9d258917-277f-42cd-a3cd-14c4e9ee58bc}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" contentBits="0" removed="0"/>

--- a/Requirements.xlsx
+++ b/Requirements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://siemens-my.sharepoint.com/personal/malte-benedikt_schroeter_siemens_com/Documents/BA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4546" documentId="13_ncr:1_{BE626DFE-17E3-4385-820A-E055A2D8DF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B29399F-DBED-452F-96FA-4666E7F9FCBB}"/>
+  <xr:revisionPtr revIDLastSave="4549" documentId="13_ncr:1_{BE626DFE-17E3-4385-820A-E055A2D8DF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C2374D3-BD48-4875-B39E-A71289549F97}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="5" activeTab="8" xr2:uid="{9AFE01D9-9480-4035-82AC-131C794FF07E}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="5" activeTab="6" xr2:uid="{9AFE01D9-9480-4035-82AC-131C794FF07E}"/>
   </bookViews>
   <sheets>
     <sheet name="Funktional" sheetId="1" r:id="rId1"/>
@@ -18166,7 +18166,7 @@
         <v>754</v>
       </c>
       <c r="E15" s="26">
-        <v>528</v>
+        <v>669</v>
       </c>
       <c r="F15" s="26" t="s">
         <v>229</v>
@@ -18201,7 +18201,7 @@
         <v>754</v>
       </c>
       <c r="E16" s="26">
-        <v>529</v>
+        <v>671</v>
       </c>
       <c r="F16" s="26" t="s">
         <v>230</v>
@@ -18236,7 +18236,7 @@
         <v>754</v>
       </c>
       <c r="E17" s="26">
-        <v>530</v>
+        <v>673</v>
       </c>
       <c r="F17" s="26" t="s">
         <v>231</v>
@@ -19125,7 +19125,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A6:K25" xr:uid="{215D1AA0-9FFC-4039-8385-BFD3A8114B33}"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Abhaken" prompt="Haken setzen, wenn der Datenpunkt in Desigo CC angelegt ist." sqref="A7:A25" xr:uid="{B3C75486-06C8-4D45-9126-EDECCD324AA8}">
       <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
         <mc:Choice Requires="x12ac">
@@ -22192,7 +22192,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A6:K71" xr:uid="{FB8EDA5B-3056-480A-AA43-F447F580627A}"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Abhaken" prompt="Haken setzen, wenn der Datenpunkt in Desigo CC angelegt ist." sqref="A7:A71" xr:uid="{18F9A785-CE63-4312-ADB5-134312DCB15D}">
       <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
         <mc:Choice Requires="x12ac">
